--- a/TSM.xlsx
+++ b/TSM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B4529A9-FB22-4644-A7C6-C96BC73D91D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF2B32C-165D-47D9-B0B7-66739C4F40DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{D45F948B-0237-4CD1-A538-BE8EB16D26F7}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{D45F948B-0237-4CD1-A538-BE8EB16D26F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
   <si>
     <t>TSMC</t>
   </si>
@@ -221,6 +221,9 @@
   <si>
     <t>2330.TW</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
 </sst>
 </file>
 
@@ -230,13 +233,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -313,32 +322,36 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -697,7 +710,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="3">
-        <v>1740</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -720,7 +733,7 @@
       </c>
       <c r="H4" s="4">
         <f>+H2*H3</f>
-        <v>45119940</v>
+        <v>51213725</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -756,7 +769,7 @@
       </c>
       <c r="H7" s="4">
         <f>+H4-H5+H6</f>
-        <v>43044500</v>
+        <v>49138285</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -857,6 +870,9 @@
       <c r="V2" s="5" t="s">
         <v>47</v>
       </c>
+      <c r="W2" s="16" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="3" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -866,8 +882,14 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
+      <c r="G3" s="17">
+        <f>9%*G13</f>
+        <v>53337.96</v>
+      </c>
+      <c r="H3" s="17">
+        <f>15%*H13</f>
+        <v>101026.5</v>
+      </c>
       <c r="I3" s="8">
         <f>20%*I13</f>
         <v>151938.4</v>
@@ -876,7 +898,10 @@
         <f>26%*J13</f>
         <v>225799.86000000002</v>
       </c>
-      <c r="K3" s="8"/>
+      <c r="K3" s="8">
+        <f>22%*K13</f>
+        <v>184635.88</v>
+      </c>
       <c r="L3" s="8">
         <v>224110.07999999999</v>
       </c>
@@ -932,8 +957,14 @@
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
+      <c r="G4" s="8">
+        <f>37%*G13</f>
+        <v>219278.28</v>
+      </c>
+      <c r="H4" s="8">
+        <f>35%*H13</f>
+        <v>235728.49999999997</v>
+      </c>
       <c r="I4" s="8">
         <f>32%*I13</f>
         <v>243101.44</v>
@@ -942,7 +973,10 @@
         <f>34%*J13</f>
         <v>295276.74000000005</v>
       </c>
-      <c r="K4" s="8"/>
+      <c r="K4" s="8">
+        <f>36%*K13</f>
+        <v>302131.44</v>
+      </c>
       <c r="L4" s="8">
         <v>336165.12</v>
       </c>
@@ -998,8 +1032,14 @@
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="G5" s="8">
+        <f>19%*G13</f>
+        <v>112602.36</v>
+      </c>
+      <c r="H5" s="8">
+        <f>17%*H13</f>
+        <v>114496.70000000001</v>
+      </c>
       <c r="I5" s="8">
         <f>17%*I13</f>
         <v>129147.64000000001</v>
@@ -1008,7 +1048,10 @@
         <f>14%*J13</f>
         <v>121584.54000000001</v>
       </c>
-      <c r="K5" s="8"/>
+      <c r="K5" s="8">
+        <f>15%*K13</f>
+        <v>125888.09999999999</v>
+      </c>
       <c r="L5" s="8">
         <v>130730.88000000002</v>
       </c>
@@ -1064,8 +1107,14 @@
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="G6" s="8">
+        <f>+G13-SUM(G3:G5)</f>
+        <v>207425.40000000002</v>
+      </c>
+      <c r="H6" s="8">
+        <f>+H13-SUM(H3:H5)</f>
+        <v>222258.3</v>
+      </c>
       <c r="I6" s="8">
         <f>+I13-SUM(I3:I5)</f>
         <v>235504.52000000002</v>
@@ -1074,7 +1123,10 @@
         <f>+J13-SUM(J3:J5)</f>
         <v>225799.85999999987</v>
       </c>
-      <c r="K6" s="8"/>
+      <c r="K6" s="8">
+        <f>+K13-SUM(K3:K5)</f>
+        <v>226598.57999999996</v>
+      </c>
       <c r="L6" s="8">
         <v>242785.92000000004</v>
       </c>
@@ -1130,8 +1182,14 @@
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
+      <c r="G7" s="8">
+        <f>46%*G13</f>
+        <v>272616.24</v>
+      </c>
+      <c r="H7" s="8">
+        <f>52%*H13</f>
+        <v>350225.2</v>
+      </c>
       <c r="I7" s="8">
         <f>51%*I13</f>
         <v>387442.92</v>
@@ -1140,7 +1198,10 @@
         <f>53%*J13</f>
         <v>460284.33</v>
       </c>
-      <c r="K7" s="8"/>
+      <c r="K7" s="8">
+        <f>59%*K13</f>
+        <v>495159.86</v>
+      </c>
       <c r="L7" s="8">
         <v>560275.19999999995</v>
       </c>
@@ -1196,8 +1257,14 @@
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
+      <c r="G8" s="8">
+        <f>38%*G13</f>
+        <v>225204.72</v>
+      </c>
+      <c r="H8" s="8">
+        <f>33%*H13</f>
+        <v>222258.30000000002</v>
+      </c>
       <c r="I8" s="8">
         <f>34%*I13</f>
         <v>258295.28000000003</v>
@@ -1206,7 +1273,10 @@
         <f>35%*J13</f>
         <v>303961.34999999998</v>
       </c>
-      <c r="K8" s="8"/>
+      <c r="K8" s="8">
+        <f>28%*K13</f>
+        <v>234991.12000000002</v>
+      </c>
       <c r="L8" s="8">
         <v>252123.84000000003</v>
       </c>
@@ -1262,8 +1332,14 @@
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="G9" s="8">
+        <f>6%*G13</f>
+        <v>35558.639999999999</v>
+      </c>
+      <c r="H9" s="8">
+        <f>6%*H13</f>
+        <v>40410.6</v>
+      </c>
       <c r="I9" s="8">
         <f>7%*I13</f>
         <v>53178.44</v>
@@ -1272,7 +1348,10 @@
         <f>5%*J13</f>
         <v>43423.05</v>
       </c>
-      <c r="K9" s="8"/>
+      <c r="K9" s="8">
+        <f>5%*K13</f>
+        <v>41962.700000000004</v>
+      </c>
       <c r="L9" s="8">
         <v>46689.600000000006</v>
       </c>
@@ -1328,8 +1407,14 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
+      <c r="G10" s="8">
+        <f>2%*G13</f>
+        <v>11852.880000000001</v>
+      </c>
+      <c r="H10" s="8">
+        <f>5%*H13</f>
+        <v>33675.5</v>
+      </c>
       <c r="I10" s="8">
         <f>5%*I13</f>
         <v>37984.6</v>
@@ -1338,7 +1423,10 @@
         <f>4%*J13</f>
         <v>34738.44</v>
       </c>
-      <c r="K10" s="8"/>
+      <c r="K10" s="8">
+        <f>1%*K13</f>
+        <v>8392.5400000000009</v>
+      </c>
       <c r="L10" s="8">
         <v>46689.600000000006</v>
       </c>
@@ -1394,8 +1482,14 @@
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="G11" s="8">
+        <f>2%*G13</f>
+        <v>11852.880000000001</v>
+      </c>
+      <c r="H11" s="8">
+        <f>2%*H13</f>
+        <v>13470.2</v>
+      </c>
       <c r="I11" s="8">
         <f>1%*I13</f>
         <v>7596.92</v>
@@ -1404,7 +1498,10 @@
         <f>1%*J13</f>
         <v>8684.61</v>
       </c>
-      <c r="K11" s="8"/>
+      <c r="K11" s="8">
+        <f>2%*K13</f>
+        <v>16785.080000000002</v>
+      </c>
       <c r="L11" s="8">
         <v>9337.92</v>
       </c>
@@ -1460,8 +1557,14 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="G12" s="8">
+        <f>+G13-SUM(G7:G11)</f>
+        <v>35558.640000000014</v>
+      </c>
+      <c r="H12" s="8">
+        <f>2%*H13</f>
+        <v>13470.2</v>
+      </c>
       <c r="I12" s="8">
         <f>2%*I13</f>
         <v>15193.84</v>
@@ -1470,7 +1573,10 @@
         <f>2%*J13</f>
         <v>17369.22</v>
       </c>
-      <c r="K12" s="8"/>
+      <c r="K12" s="8">
+        <f>+K13-SUM(K7:K11)</f>
+        <v>41962.70000000007</v>
+      </c>
       <c r="L12" s="8">
         <v>18675.84</v>
       </c>

--- a/TSM.xlsx
+++ b/TSM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF2B32C-165D-47D9-B0B7-66739C4F40DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEF3176-1C8C-4DBF-A54C-E7571332DABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{D45F948B-0237-4CD1-A538-BE8EB16D26F7}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{D45F948B-0237-4CD1-A538-BE8EB16D26F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
   <si>
     <t>TSMC</t>
   </si>
@@ -224,6 +224,21 @@
   <si>
     <t>FY25</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Wafer Shipments</t>
+  </si>
 </sst>
 </file>
 
@@ -325,7 +340,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -348,10 +363,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -710,7 +726,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="3">
-        <v>1975</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -720,8 +736,8 @@
       <c r="H3" s="4">
         <v>25931</v>
       </c>
-      <c r="I3" s="15" t="s">
-        <v>40</v>
+      <c r="I3" s="17" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -733,7 +749,7 @@
       </c>
       <c r="H4" s="4">
         <f>+H2*H3</f>
-        <v>51213725</v>
+        <v>52639930</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -744,11 +760,11 @@
         <v>5</v>
       </c>
       <c r="H5" s="4">
-        <f>2767856+300738</f>
-        <v>3068594</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>40</v>
+        <f>3035637+347964</f>
+        <v>3383601</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -756,11 +772,11 @@
         <v>6</v>
       </c>
       <c r="H6" s="4">
-        <f>136926+856228</f>
-        <v>993154</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>40</v>
+        <f>156242+860026</f>
+        <v>1016268</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -769,7 +785,7 @@
       </c>
       <c r="H7" s="4">
         <f>+H4-H5+H6</f>
-        <v>49138285</v>
+        <v>50272597</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -797,22 +813,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6249646-B538-4C8E-8557-B9FADF837D81}">
-  <dimension ref="A1:AW198"/>
+  <dimension ref="A1:BA200"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="21.7109375" style="2" customWidth="1"/>
     <col min="3" max="13" width="9.140625" style="2"/>
     <col min="14" max="14" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="2"/>
+    <col min="15" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.2">
       <c r="C2" s="5" t="s">
         <v>11</v>
       </c>
@@ -849,71 +866,66 @@
       <c r="N2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="O2" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="P2" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="T2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="W2" s="16" t="s">
+      <c r="AA2" s="15" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
-        <v>52</v>
+    <row r="3" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="B3" s="18" t="s">
+        <v>66</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
-      <c r="G3" s="17">
-        <f>9%*G13</f>
-        <v>53337.96</v>
-      </c>
-      <c r="H3" s="17">
-        <f>15%*H13</f>
-        <v>101026.5</v>
-      </c>
-      <c r="I3" s="8">
-        <f>20%*I13</f>
-        <v>151938.4</v>
-      </c>
-      <c r="J3" s="8">
-        <f>26%*J13</f>
-        <v>225799.86000000002</v>
-      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
       <c r="K3" s="8">
-        <f>22%*K13</f>
-        <v>184635.88</v>
-      </c>
-      <c r="L3" s="8">
-        <v>224110.07999999999</v>
-      </c>
-      <c r="M3" s="8">
-        <f>23%*M13</f>
-        <v>227681.14</v>
-      </c>
+        <v>3259</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
       <c r="N3" s="8">
-        <f>28%*N13</f>
-        <v>292905.2</v>
-      </c>
-      <c r="O3" s="8"/>
+        <v>3961</v>
+      </c>
+      <c r="O3" s="8">
+        <v>4174</v>
+      </c>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
@@ -936,58 +948,30 @@
       <c r="AI3" s="8"/>
       <c r="AJ3" s="8"/>
       <c r="AK3" s="8"/>
-      <c r="AL3" s="4"/>
-      <c r="AM3" s="4"/>
-      <c r="AN3" s="4"/>
-      <c r="AO3" s="4"/>
-      <c r="AP3" s="4"/>
-      <c r="AQ3" s="4"/>
-      <c r="AR3" s="4"/>
-      <c r="AS3" s="4"/>
-      <c r="AT3" s="4"/>
-      <c r="AU3" s="4"/>
-      <c r="AV3" s="4"/>
-      <c r="AW3" s="4"/>
-    </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="B4" s="9" t="s">
-        <v>51</v>
-      </c>
+      <c r="AL3" s="8"/>
+      <c r="AM3" s="8"/>
+      <c r="AN3" s="8"/>
+      <c r="AO3" s="8"/>
+      <c r="AP3" s="8"/>
+      <c r="AQ3" s="8"/>
+      <c r="AR3" s="8"/>
+      <c r="AS3" s="8"/>
+      <c r="AT3" s="8"/>
+      <c r="AU3" s="8"/>
+    </row>
+    <row r="4" spans="1:53" x14ac:dyDescent="0.2">
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="8">
-        <f>37%*G13</f>
-        <v>219278.28</v>
-      </c>
-      <c r="H4" s="8">
-        <f>35%*H13</f>
-        <v>235728.49999999997</v>
-      </c>
-      <c r="I4" s="8">
-        <f>32%*I13</f>
-        <v>243101.44</v>
-      </c>
-      <c r="J4" s="8">
-        <f>34%*J13</f>
-        <v>295276.74000000005</v>
-      </c>
-      <c r="K4" s="8">
-        <f>36%*K13</f>
-        <v>302131.44</v>
-      </c>
-      <c r="L4" s="8">
-        <v>336165.12</v>
-      </c>
-      <c r="M4" s="8">
-        <f>37%*M13</f>
-        <v>366269.66</v>
-      </c>
-      <c r="N4" s="8">
-        <f>35%*N13</f>
-        <v>366131.5</v>
-      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
@@ -1011,59 +995,60 @@
       <c r="AI4" s="8"/>
       <c r="AJ4" s="8"/>
       <c r="AK4" s="8"/>
-      <c r="AL4" s="4"/>
-      <c r="AM4" s="4"/>
-      <c r="AN4" s="4"/>
-      <c r="AO4" s="4"/>
-      <c r="AP4" s="4"/>
-      <c r="AQ4" s="4"/>
-      <c r="AR4" s="4"/>
-      <c r="AS4" s="4"/>
-      <c r="AT4" s="4"/>
-      <c r="AU4" s="4"/>
-      <c r="AV4" s="4"/>
-      <c r="AW4" s="4"/>
-    </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AL4" s="8"/>
+      <c r="AM4" s="8"/>
+      <c r="AN4" s="8"/>
+      <c r="AO4" s="8"/>
+      <c r="AP4" s="8"/>
+      <c r="AQ4" s="8"/>
+      <c r="AR4" s="8"/>
+      <c r="AS4" s="8"/>
+      <c r="AT4" s="8"/>
+      <c r="AU4" s="8"/>
+    </row>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
-      <c r="G5" s="8">
-        <f>19%*G13</f>
-        <v>112602.36</v>
-      </c>
-      <c r="H5" s="8">
-        <f>17%*H13</f>
-        <v>114496.70000000001</v>
+      <c r="G5" s="16">
+        <f>9%*G15</f>
+        <v>53337.96</v>
+      </c>
+      <c r="H5" s="16">
+        <f>15%*H15</f>
+        <v>101026.5</v>
       </c>
       <c r="I5" s="8">
-        <f>17%*I13</f>
-        <v>129147.64000000001</v>
+        <f>20%*I15</f>
+        <v>151938.4</v>
       </c>
       <c r="J5" s="8">
-        <f>14%*J13</f>
-        <v>121584.54000000001</v>
+        <f>26%*J15</f>
+        <v>225799.86000000002</v>
       </c>
       <c r="K5" s="8">
-        <f>15%*K13</f>
-        <v>125888.09999999999</v>
+        <f>22%*K15</f>
+        <v>184635.88</v>
       </c>
       <c r="L5" s="8">
-        <v>130730.88000000002</v>
+        <v>224110.07999999999</v>
       </c>
       <c r="M5" s="8">
-        <f>14%*M13</f>
-        <v>138588.52000000002</v>
+        <f>23%*M15</f>
+        <v>227681.14</v>
       </c>
       <c r="N5" s="8">
-        <f>14%*N13</f>
-        <v>146452.6</v>
-      </c>
-      <c r="O5" s="8"/>
+        <f>28%*N15</f>
+        <v>292905.2</v>
+      </c>
+      <c r="O5" s="8">
+        <f>25%*O15</f>
+        <v>283525.75</v>
+      </c>
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
@@ -1086,10 +1071,10 @@
       <c r="AI5" s="8"/>
       <c r="AJ5" s="8"/>
       <c r="AK5" s="8"/>
-      <c r="AL5" s="4"/>
-      <c r="AM5" s="4"/>
-      <c r="AN5" s="4"/>
-      <c r="AO5" s="4"/>
+      <c r="AL5" s="8"/>
+      <c r="AM5" s="8"/>
+      <c r="AN5" s="8"/>
+      <c r="AO5" s="8"/>
       <c r="AP5" s="4"/>
       <c r="AQ5" s="4"/>
       <c r="AR5" s="4"/>
@@ -1098,47 +1083,54 @@
       <c r="AU5" s="4"/>
       <c r="AV5" s="4"/>
       <c r="AW5" s="4"/>
-    </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="B6" s="2" t="s">
-        <v>54</v>
+      <c r="AX5" s="4"/>
+      <c r="AY5" s="4"/>
+      <c r="AZ5" s="4"/>
+      <c r="BA5" s="4"/>
+    </row>
+    <row r="6" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="B6" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8">
-        <f>+G13-SUM(G3:G5)</f>
-        <v>207425.40000000002</v>
+        <f>37%*G15</f>
+        <v>219278.28</v>
       </c>
       <c r="H6" s="8">
-        <f>+H13-SUM(H3:H5)</f>
-        <v>222258.3</v>
+        <f>35%*H15</f>
+        <v>235728.49999999997</v>
       </c>
       <c r="I6" s="8">
-        <f>+I13-SUM(I3:I5)</f>
-        <v>235504.52000000002</v>
+        <f>32%*I15</f>
+        <v>243101.44</v>
       </c>
       <c r="J6" s="8">
-        <f>+J13-SUM(J3:J5)</f>
-        <v>225799.85999999987</v>
+        <f>34%*J15</f>
+        <v>295276.74000000005</v>
       </c>
       <c r="K6" s="8">
-        <f>+K13-SUM(K3:K5)</f>
-        <v>226598.57999999996</v>
+        <f>36%*K15</f>
+        <v>302131.44</v>
       </c>
       <c r="L6" s="8">
-        <v>242785.92000000004</v>
+        <v>336165.12</v>
       </c>
       <c r="M6" s="8">
-        <f>+M13-SUM(M3:M5)</f>
-        <v>257378.67999999993</v>
+        <f>37%*M15</f>
+        <v>366269.66</v>
       </c>
       <c r="N6" s="8">
-        <f>+N13-SUM(N3:N5)</f>
-        <v>240600.70000000007</v>
-      </c>
-      <c r="O6" s="8"/>
+        <f>35%*N15</f>
+        <v>366131.5</v>
+      </c>
+      <c r="O6" s="8">
+        <f>36%*O15</f>
+        <v>408277.07999999996</v>
+      </c>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
@@ -1161,10 +1153,10 @@
       <c r="AI6" s="8"/>
       <c r="AJ6" s="8"/>
       <c r="AK6" s="8"/>
-      <c r="AL6" s="4"/>
-      <c r="AM6" s="4"/>
-      <c r="AN6" s="4"/>
-      <c r="AO6" s="4"/>
+      <c r="AL6" s="8"/>
+      <c r="AM6" s="8"/>
+      <c r="AN6" s="8"/>
+      <c r="AO6" s="8"/>
       <c r="AP6" s="4"/>
       <c r="AQ6" s="4"/>
       <c r="AR6" s="4"/>
@@ -1173,47 +1165,54 @@
       <c r="AU6" s="4"/>
       <c r="AV6" s="4"/>
       <c r="AW6" s="4"/>
-    </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX6" s="4"/>
+      <c r="AY6" s="4"/>
+      <c r="AZ6" s="4"/>
+      <c r="BA6" s="4"/>
+    </row>
+    <row r="7" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8">
-        <f>46%*G13</f>
-        <v>272616.24</v>
+        <f>19%*G15</f>
+        <v>112602.36</v>
       </c>
       <c r="H7" s="8">
-        <f>52%*H13</f>
-        <v>350225.2</v>
+        <f>17%*H15</f>
+        <v>114496.70000000001</v>
       </c>
       <c r="I7" s="8">
-        <f>51%*I13</f>
-        <v>387442.92</v>
+        <f>17%*I15</f>
+        <v>129147.64000000001</v>
       </c>
       <c r="J7" s="8">
-        <f>53%*J13</f>
-        <v>460284.33</v>
+        <f>14%*J15</f>
+        <v>121584.54000000001</v>
       </c>
       <c r="K7" s="8">
-        <f>59%*K13</f>
-        <v>495159.86</v>
+        <f>15%*K15</f>
+        <v>125888.09999999999</v>
       </c>
       <c r="L7" s="8">
-        <v>560275.19999999995</v>
+        <v>130730.88000000002</v>
       </c>
       <c r="M7" s="8">
-        <f>57%*M13</f>
-        <v>564253.26</v>
+        <f>14%*M15</f>
+        <v>138588.52000000002</v>
       </c>
       <c r="N7" s="8">
-        <f>55%*N13</f>
-        <v>575349.5</v>
-      </c>
-      <c r="O7" s="8"/>
+        <f>14%*N15</f>
+        <v>146452.6</v>
+      </c>
+      <c r="O7" s="8">
+        <f>13%*O15</f>
+        <v>147433.39000000001</v>
+      </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
@@ -1236,10 +1235,10 @@
       <c r="AI7" s="8"/>
       <c r="AJ7" s="8"/>
       <c r="AK7" s="8"/>
-      <c r="AL7" s="4"/>
-      <c r="AM7" s="4"/>
-      <c r="AN7" s="4"/>
-      <c r="AO7" s="4"/>
+      <c r="AL7" s="8"/>
+      <c r="AM7" s="8"/>
+      <c r="AN7" s="8"/>
+      <c r="AO7" s="8"/>
       <c r="AP7" s="4"/>
       <c r="AQ7" s="4"/>
       <c r="AR7" s="4"/>
@@ -1248,47 +1247,54 @@
       <c r="AU7" s="4"/>
       <c r="AV7" s="4"/>
       <c r="AW7" s="4"/>
-    </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX7" s="4"/>
+      <c r="AY7" s="4"/>
+      <c r="AZ7" s="4"/>
+      <c r="BA7" s="4"/>
+    </row>
+    <row r="8" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8">
-        <f>38%*G13</f>
-        <v>225204.72</v>
+        <f>+G15-SUM(G5:G7)</f>
+        <v>207425.40000000002</v>
       </c>
       <c r="H8" s="8">
-        <f>33%*H13</f>
-        <v>222258.30000000002</v>
+        <f>+H15-SUM(H5:H7)</f>
+        <v>222258.3</v>
       </c>
       <c r="I8" s="8">
-        <f>34%*I13</f>
-        <v>258295.28000000003</v>
+        <f>+I15-SUM(I5:I7)</f>
+        <v>235504.52000000002</v>
       </c>
       <c r="J8" s="8">
-        <f>35%*J13</f>
-        <v>303961.34999999998</v>
+        <f>+J15-SUM(J5:J7)</f>
+        <v>225799.85999999987</v>
       </c>
       <c r="K8" s="8">
-        <f>28%*K13</f>
-        <v>234991.12000000002</v>
+        <f>+K15-SUM(K5:K7)</f>
+        <v>226598.57999999996</v>
       </c>
       <c r="L8" s="8">
-        <v>252123.84000000003</v>
+        <v>242785.92000000004</v>
       </c>
       <c r="M8" s="8">
-        <f>30%*M13</f>
-        <v>296975.39999999997</v>
+        <f>+M15-SUM(M5:M7)</f>
+        <v>257378.67999999993</v>
       </c>
       <c r="N8" s="8">
-        <f>32%*N13</f>
-        <v>334748.79999999999</v>
-      </c>
-      <c r="O8" s="8"/>
+        <f>+N15-SUM(N5:N7)</f>
+        <v>240600.70000000007</v>
+      </c>
+      <c r="O8" s="8">
+        <f>+O15-SUM(O5:O7)</f>
+        <v>294866.78000000003</v>
+      </c>
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
@@ -1311,10 +1317,10 @@
       <c r="AI8" s="8"/>
       <c r="AJ8" s="8"/>
       <c r="AK8" s="8"/>
-      <c r="AL8" s="4"/>
-      <c r="AM8" s="4"/>
-      <c r="AN8" s="4"/>
-      <c r="AO8" s="4"/>
+      <c r="AL8" s="8"/>
+      <c r="AM8" s="8"/>
+      <c r="AN8" s="8"/>
+      <c r="AO8" s="8"/>
       <c r="AP8" s="4"/>
       <c r="AQ8" s="4"/>
       <c r="AR8" s="4"/>
@@ -1323,47 +1329,54 @@
       <c r="AU8" s="4"/>
       <c r="AV8" s="4"/>
       <c r="AW8" s="4"/>
-    </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX8" s="4"/>
+      <c r="AY8" s="4"/>
+      <c r="AZ8" s="4"/>
+      <c r="BA8" s="4"/>
+    </row>
+    <row r="9" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8">
-        <f>6%*G13</f>
-        <v>35558.639999999999</v>
+        <f>46%*G15</f>
+        <v>272616.24</v>
       </c>
       <c r="H9" s="8">
-        <f>6%*H13</f>
-        <v>40410.6</v>
+        <f>52%*H15</f>
+        <v>350225.2</v>
       </c>
       <c r="I9" s="8">
-        <f>7%*I13</f>
-        <v>53178.44</v>
+        <f>51%*I15</f>
+        <v>387442.92</v>
       </c>
       <c r="J9" s="8">
-        <f>5%*J13</f>
-        <v>43423.05</v>
+        <f>53%*J15</f>
+        <v>460284.33</v>
       </c>
       <c r="K9" s="8">
-        <f>5%*K13</f>
-        <v>41962.700000000004</v>
+        <f>59%*K15</f>
+        <v>495159.86</v>
       </c>
       <c r="L9" s="8">
-        <v>46689.600000000006</v>
+        <v>560275.19999999995</v>
       </c>
       <c r="M9" s="8">
-        <f>5%*M13</f>
-        <v>49495.9</v>
+        <f>57%*M15</f>
+        <v>564253.26</v>
       </c>
       <c r="N9" s="8">
-        <f>5%*N13</f>
-        <v>52304.5</v>
-      </c>
-      <c r="O9" s="8"/>
+        <f>55%*N15</f>
+        <v>575349.5</v>
+      </c>
+      <c r="O9" s="8">
+        <f>61%*O15</f>
+        <v>691802.83</v>
+      </c>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
@@ -1386,10 +1399,10 @@
       <c r="AI9" s="8"/>
       <c r="AJ9" s="8"/>
       <c r="AK9" s="8"/>
-      <c r="AL9" s="4"/>
-      <c r="AM9" s="4"/>
-      <c r="AN9" s="4"/>
-      <c r="AO9" s="4"/>
+      <c r="AL9" s="8"/>
+      <c r="AM9" s="8"/>
+      <c r="AN9" s="8"/>
+      <c r="AO9" s="8"/>
       <c r="AP9" s="4"/>
       <c r="AQ9" s="4"/>
       <c r="AR9" s="4"/>
@@ -1398,47 +1411,54 @@
       <c r="AU9" s="4"/>
       <c r="AV9" s="4"/>
       <c r="AW9" s="4"/>
-    </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX9" s="4"/>
+      <c r="AY9" s="4"/>
+      <c r="AZ9" s="4"/>
+      <c r="BA9" s="4"/>
+    </row>
+    <row r="10" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8">
-        <f>2%*G13</f>
-        <v>11852.880000000001</v>
+        <f>38%*G15</f>
+        <v>225204.72</v>
       </c>
       <c r="H10" s="8">
-        <f>5%*H13</f>
-        <v>33675.5</v>
+        <f>33%*H15</f>
+        <v>222258.30000000002</v>
       </c>
       <c r="I10" s="8">
-        <f>5%*I13</f>
-        <v>37984.6</v>
+        <f>34%*I15</f>
+        <v>258295.28000000003</v>
       </c>
       <c r="J10" s="8">
-        <f>4%*J13</f>
-        <v>34738.44</v>
+        <f>35%*J15</f>
+        <v>303961.34999999998</v>
       </c>
       <c r="K10" s="8">
-        <f>1%*K13</f>
-        <v>8392.5400000000009</v>
+        <f>28%*K15</f>
+        <v>234991.12000000002</v>
       </c>
       <c r="L10" s="8">
-        <v>46689.600000000006</v>
+        <v>252123.84000000003</v>
       </c>
       <c r="M10" s="8">
-        <f>5%*M13</f>
-        <v>49495.9</v>
+        <f>30%*M15</f>
+        <v>296975.39999999997</v>
       </c>
       <c r="N10" s="8">
-        <f>5%*N13</f>
-        <v>52304.5</v>
-      </c>
-      <c r="O10" s="8"/>
+        <f>32%*N15</f>
+        <v>334748.79999999999</v>
+      </c>
+      <c r="O10" s="8">
+        <f>26%*O15</f>
+        <v>294866.78000000003</v>
+      </c>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
@@ -1461,10 +1481,10 @@
       <c r="AI10" s="8"/>
       <c r="AJ10" s="8"/>
       <c r="AK10" s="8"/>
-      <c r="AL10" s="4"/>
-      <c r="AM10" s="4"/>
-      <c r="AN10" s="4"/>
-      <c r="AO10" s="4"/>
+      <c r="AL10" s="8"/>
+      <c r="AM10" s="8"/>
+      <c r="AN10" s="8"/>
+      <c r="AO10" s="8"/>
       <c r="AP10" s="4"/>
       <c r="AQ10" s="4"/>
       <c r="AR10" s="4"/>
@@ -1473,47 +1493,54 @@
       <c r="AU10" s="4"/>
       <c r="AV10" s="4"/>
       <c r="AW10" s="4"/>
-    </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX10" s="4"/>
+      <c r="AY10" s="4"/>
+      <c r="AZ10" s="4"/>
+      <c r="BA10" s="4"/>
+    </row>
+    <row r="11" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8">
-        <f>2%*G13</f>
-        <v>11852.880000000001</v>
+        <f>6%*G15</f>
+        <v>35558.639999999999</v>
       </c>
       <c r="H11" s="8">
-        <f>2%*H13</f>
-        <v>13470.2</v>
+        <f>6%*H15</f>
+        <v>40410.6</v>
       </c>
       <c r="I11" s="8">
-        <f>1%*I13</f>
-        <v>7596.92</v>
+        <f>7%*I15</f>
+        <v>53178.44</v>
       </c>
       <c r="J11" s="8">
-        <f>1%*J13</f>
-        <v>8684.61</v>
+        <f>5%*J15</f>
+        <v>43423.05</v>
       </c>
       <c r="K11" s="8">
-        <f>2%*K13</f>
-        <v>16785.080000000002</v>
+        <f>5%*K15</f>
+        <v>41962.700000000004</v>
       </c>
       <c r="L11" s="8">
-        <v>9337.92</v>
+        <v>46689.600000000006</v>
       </c>
       <c r="M11" s="8">
-        <f>1%*M13</f>
-        <v>9899.18</v>
+        <f>5%*M15</f>
+        <v>49495.9</v>
       </c>
       <c r="N11" s="8">
-        <f>1%*N13</f>
-        <v>10460.9</v>
-      </c>
-      <c r="O11" s="8"/>
+        <f>5%*N15</f>
+        <v>52304.5</v>
+      </c>
+      <c r="O11" s="8">
+        <f>6%*O15</f>
+        <v>68046.179999999993</v>
+      </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
@@ -1536,10 +1563,10 @@
       <c r="AI11" s="8"/>
       <c r="AJ11" s="8"/>
       <c r="AK11" s="8"/>
-      <c r="AL11" s="4"/>
-      <c r="AM11" s="4"/>
-      <c r="AN11" s="4"/>
-      <c r="AO11" s="4"/>
+      <c r="AL11" s="8"/>
+      <c r="AM11" s="8"/>
+      <c r="AN11" s="8"/>
+      <c r="AO11" s="8"/>
       <c r="AP11" s="4"/>
       <c r="AQ11" s="4"/>
       <c r="AR11" s="4"/>
@@ -1548,47 +1575,54 @@
       <c r="AU11" s="4"/>
       <c r="AV11" s="4"/>
       <c r="AW11" s="4"/>
-    </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX11" s="4"/>
+      <c r="AY11" s="4"/>
+      <c r="AZ11" s="4"/>
+      <c r="BA11" s="4"/>
+    </row>
+    <row r="12" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8">
-        <f>+G13-SUM(G7:G11)</f>
-        <v>35558.640000000014</v>
+        <f>2%*G15</f>
+        <v>11852.880000000001</v>
       </c>
       <c r="H12" s="8">
-        <f>2%*H13</f>
-        <v>13470.2</v>
+        <f>5%*H15</f>
+        <v>33675.5</v>
       </c>
       <c r="I12" s="8">
-        <f>2%*I13</f>
-        <v>15193.84</v>
+        <f>5%*I15</f>
+        <v>37984.6</v>
       </c>
       <c r="J12" s="8">
-        <f>2%*J13</f>
-        <v>17369.22</v>
+        <f>4%*J15</f>
+        <v>34738.44</v>
       </c>
       <c r="K12" s="8">
-        <f>+K13-SUM(K7:K11)</f>
-        <v>41962.70000000007</v>
+        <f>1%*K15</f>
+        <v>8392.5400000000009</v>
       </c>
       <c r="L12" s="8">
-        <v>18675.84</v>
+        <v>46689.600000000006</v>
       </c>
       <c r="M12" s="8">
-        <f>2%*M13</f>
-        <v>19798.36</v>
+        <f>5%*M15</f>
+        <v>49495.9</v>
       </c>
       <c r="N12" s="8">
-        <f>2%*N13</f>
-        <v>20921.8</v>
-      </c>
-      <c r="O12" s="8"/>
+        <f>5%*N15</f>
+        <v>52304.5</v>
+      </c>
+      <c r="O12" s="8">
+        <f>4%*O15</f>
+        <v>45364.12</v>
+      </c>
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
@@ -1611,10 +1645,10 @@
       <c r="AI12" s="8"/>
       <c r="AJ12" s="8"/>
       <c r="AK12" s="8"/>
-      <c r="AL12" s="4"/>
-      <c r="AM12" s="4"/>
-      <c r="AN12" s="4"/>
-      <c r="AO12" s="4"/>
+      <c r="AL12" s="8"/>
+      <c r="AM12" s="8"/>
+      <c r="AN12" s="8"/>
+      <c r="AO12" s="8"/>
       <c r="AP12" s="4"/>
       <c r="AQ12" s="4"/>
       <c r="AR12" s="4"/>
@@ -1623,42 +1657,54 @@
       <c r="AU12" s="4"/>
       <c r="AV12" s="4"/>
       <c r="AW12" s="4"/>
-    </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="B13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10">
-        <v>546733</v>
-      </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10">
-        <v>592644</v>
-      </c>
-      <c r="H13" s="10">
-        <v>673510</v>
-      </c>
-      <c r="I13" s="10">
-        <v>759692</v>
-      </c>
-      <c r="J13" s="10">
-        <v>868461</v>
-      </c>
-      <c r="K13" s="10">
-        <v>839254</v>
-      </c>
-      <c r="L13" s="10">
-        <v>933792</v>
-      </c>
-      <c r="M13" s="10">
-        <v>989918</v>
-      </c>
-      <c r="N13" s="10">
-        <v>1046090</v>
-      </c>
-      <c r="O13" s="8"/>
+      <c r="AX12" s="4"/>
+      <c r="AY12" s="4"/>
+      <c r="AZ12" s="4"/>
+      <c r="BA12" s="4"/>
+    </row>
+    <row r="13" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="B13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8">
+        <f>2%*G15</f>
+        <v>11852.880000000001</v>
+      </c>
+      <c r="H13" s="8">
+        <f>2%*H15</f>
+        <v>13470.2</v>
+      </c>
+      <c r="I13" s="8">
+        <f>1%*I15</f>
+        <v>7596.92</v>
+      </c>
+      <c r="J13" s="8">
+        <f>1%*J15</f>
+        <v>8684.61</v>
+      </c>
+      <c r="K13" s="8">
+        <f>2%*K15</f>
+        <v>16785.080000000002</v>
+      </c>
+      <c r="L13" s="8">
+        <v>9337.92</v>
+      </c>
+      <c r="M13" s="8">
+        <f>1%*M15</f>
+        <v>9899.18</v>
+      </c>
+      <c r="N13" s="8">
+        <f>1%*N15</f>
+        <v>10460.9</v>
+      </c>
+      <c r="O13" s="8">
+        <f>1%*O15</f>
+        <v>11341.03</v>
+      </c>
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
@@ -1681,10 +1727,10 @@
       <c r="AI13" s="8"/>
       <c r="AJ13" s="8"/>
       <c r="AK13" s="8"/>
-      <c r="AL13" s="4"/>
-      <c r="AM13" s="4"/>
-      <c r="AN13" s="4"/>
-      <c r="AO13" s="4"/>
+      <c r="AL13" s="8"/>
+      <c r="AM13" s="8"/>
+      <c r="AN13" s="8"/>
+      <c r="AO13" s="8"/>
       <c r="AP13" s="4"/>
       <c r="AQ13" s="4"/>
       <c r="AR13" s="4"/>
@@ -1693,42 +1739,54 @@
       <c r="AU13" s="4"/>
       <c r="AV13" s="4"/>
       <c r="AW13" s="4"/>
-    </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX13" s="4"/>
+      <c r="AY13" s="4"/>
+      <c r="AZ13" s="4"/>
+      <c r="BA13" s="4"/>
+    </row>
+    <row r="14" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="8">
-        <v>250090</v>
-      </c>
+      <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8">
-        <v>278139</v>
+        <f>+G15-SUM(G9:G13)</f>
+        <v>35558.640000000014</v>
       </c>
       <c r="H14" s="8">
-        <v>315385</v>
+        <f>2%*H15</f>
+        <v>13470.2</v>
       </c>
       <c r="I14" s="8">
-        <v>320347</v>
+        <f>2%*I15</f>
+        <v>15193.84</v>
       </c>
       <c r="J14" s="8">
-        <v>356082</v>
+        <f>2%*J15</f>
+        <v>17369.22</v>
       </c>
       <c r="K14" s="8">
-        <v>345859</v>
+        <f>+K15-SUM(K9:K13)</f>
+        <v>41962.70000000007</v>
       </c>
       <c r="L14" s="8">
-        <v>386423</v>
+        <v>18675.84</v>
       </c>
       <c r="M14" s="8">
-        <v>401375</v>
+        <f>2%*M15</f>
+        <v>19798.36</v>
       </c>
       <c r="N14" s="8">
-        <v>394103</v>
-      </c>
-      <c r="O14" s="8"/>
+        <f>2%*N15</f>
+        <v>20921.8</v>
+      </c>
+      <c r="O14" s="8">
+        <f>2%*O15</f>
+        <v>22682.06</v>
+      </c>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
@@ -1751,10 +1809,10 @@
       <c r="AI14" s="8"/>
       <c r="AJ14" s="8"/>
       <c r="AK14" s="8"/>
-      <c r="AL14" s="4"/>
-      <c r="AM14" s="4"/>
-      <c r="AN14" s="4"/>
-      <c r="AO14" s="4"/>
+      <c r="AL14" s="8"/>
+      <c r="AM14" s="8"/>
+      <c r="AN14" s="8"/>
+      <c r="AO14" s="8"/>
       <c r="AP14" s="4"/>
       <c r="AQ14" s="4"/>
       <c r="AR14" s="4"/>
@@ -1763,63 +1821,51 @@
       <c r="AU14" s="4"/>
       <c r="AV14" s="4"/>
       <c r="AW14" s="4"/>
-    </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="B15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="8">
-        <f t="shared" ref="C15:H15" si="0">+C13-C14</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="8">
-        <f t="shared" si="0"/>
-        <v>296643</v>
-      </c>
-      <c r="F15" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="8">
-        <f t="shared" si="0"/>
-        <v>314505</v>
-      </c>
-      <c r="H15" s="8">
-        <f t="shared" si="0"/>
-        <v>358125</v>
-      </c>
-      <c r="I15" s="8">
-        <f>+I13-I14</f>
-        <v>439345</v>
-      </c>
-      <c r="J15" s="8">
-        <f t="shared" ref="J15:N15" si="1">+J13-J14</f>
-        <v>512379</v>
-      </c>
-      <c r="K15" s="8">
-        <f t="shared" si="1"/>
-        <v>493395</v>
-      </c>
-      <c r="L15" s="8">
-        <f t="shared" si="1"/>
-        <v>547369</v>
-      </c>
-      <c r="M15" s="8">
-        <f t="shared" si="1"/>
-        <v>588543</v>
-      </c>
-      <c r="N15" s="8">
-        <f t="shared" si="1"/>
-        <v>651987</v>
-      </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
+      <c r="AX14" s="4"/>
+      <c r="AY14" s="4"/>
+      <c r="AZ14" s="4"/>
+      <c r="BA14" s="4"/>
+    </row>
+    <row r="15" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10">
+        <v>546733</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10">
+        <v>592644</v>
+      </c>
+      <c r="H15" s="10">
+        <v>673510</v>
+      </c>
+      <c r="I15" s="10">
+        <v>759692</v>
+      </c>
+      <c r="J15" s="10">
+        <v>868461</v>
+      </c>
+      <c r="K15" s="10">
+        <v>839254</v>
+      </c>
+      <c r="L15" s="10">
+        <v>933792</v>
+      </c>
+      <c r="M15" s="10">
+        <v>989918</v>
+      </c>
+      <c r="N15" s="10">
+        <v>1046090</v>
+      </c>
+      <c r="O15" s="10">
+        <v>1134103</v>
+      </c>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
       <c r="S15" s="8"/>
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
@@ -1839,10 +1885,10 @@
       <c r="AI15" s="8"/>
       <c r="AJ15" s="8"/>
       <c r="AK15" s="8"/>
-      <c r="AL15" s="4"/>
-      <c r="AM15" s="4"/>
-      <c r="AN15" s="4"/>
-      <c r="AO15" s="4"/>
+      <c r="AL15" s="8"/>
+      <c r="AM15" s="8"/>
+      <c r="AN15" s="8"/>
+      <c r="AO15" s="8"/>
       <c r="AP15" s="4"/>
       <c r="AQ15" s="4"/>
       <c r="AR15" s="4"/>
@@ -1851,42 +1897,48 @@
       <c r="AU15" s="4"/>
       <c r="AV15" s="4"/>
       <c r="AW15" s="4"/>
-    </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="AX15" s="4"/>
+      <c r="AY15" s="4"/>
+      <c r="AZ15" s="4"/>
+      <c r="BA15" s="4"/>
+    </row>
+    <row r="16" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8">
-        <v>51138</v>
+        <v>250090</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8">
-        <v>46109</v>
+        <v>278139</v>
       </c>
       <c r="H16" s="8">
-        <v>48058</v>
+        <v>315385</v>
       </c>
       <c r="I16" s="8">
-        <v>52783</v>
+        <v>320347</v>
       </c>
       <c r="J16" s="8">
-        <v>57232</v>
+        <v>356082</v>
       </c>
       <c r="K16" s="8">
-        <v>56547</v>
+        <v>345859</v>
       </c>
       <c r="L16" s="8">
-        <v>61280</v>
+        <v>386423</v>
       </c>
       <c r="M16" s="8">
-        <v>63743</v>
+        <v>401375</v>
       </c>
       <c r="N16" s="8">
-        <v>64857</v>
-      </c>
-      <c r="O16" s="8"/>
+        <v>394103</v>
+      </c>
+      <c r="O16" s="8">
+        <v>382808</v>
+      </c>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
@@ -1909,10 +1961,10 @@
       <c r="AI16" s="8"/>
       <c r="AJ16" s="8"/>
       <c r="AK16" s="8"/>
-      <c r="AL16" s="4"/>
-      <c r="AM16" s="4"/>
-      <c r="AN16" s="4"/>
-      <c r="AO16" s="4"/>
+      <c r="AL16" s="8"/>
+      <c r="AM16" s="8"/>
+      <c r="AN16" s="8"/>
+      <c r="AO16" s="8"/>
       <c r="AP16" s="4"/>
       <c r="AQ16" s="4"/>
       <c r="AR16" s="4"/>
@@ -1921,42 +1973,67 @@
       <c r="AU16" s="4"/>
       <c r="AV16" s="4"/>
       <c r="AW16" s="4"/>
-    </row>
-    <row r="17" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX16" s="4"/>
+      <c r="AY16" s="4"/>
+      <c r="AZ16" s="4"/>
+      <c r="BA16" s="4"/>
+    </row>
+    <row r="17" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+        <v>20</v>
+      </c>
+      <c r="C17" s="8">
+        <f t="shared" ref="C17:H17" si="0">+C15-C16</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="E17" s="8">
-        <v>17571</v>
-      </c>
-      <c r="F17" s="8"/>
+        <f t="shared" si="0"/>
+        <v>296643</v>
+      </c>
+      <c r="F17" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G17" s="8">
-        <v>19248</v>
+        <f t="shared" si="0"/>
+        <v>314505</v>
       </c>
       <c r="H17" s="8">
-        <v>22238</v>
+        <f t="shared" si="0"/>
+        <v>358125</v>
       </c>
       <c r="I17" s="8">
-        <v>26295</v>
+        <f>+I15-I16</f>
+        <v>439345</v>
       </c>
       <c r="J17" s="8">
-        <v>29108</v>
+        <f t="shared" ref="J17:O17" si="1">+J15-J16</f>
+        <v>512379</v>
       </c>
       <c r="K17" s="8">
-        <v>28639</v>
+        <f t="shared" si="1"/>
+        <v>493395</v>
       </c>
       <c r="L17" s="8">
-        <v>23228</v>
+        <f t="shared" si="1"/>
+        <v>547369</v>
       </c>
       <c r="M17" s="8">
-        <v>24022</v>
+        <f t="shared" si="1"/>
+        <v>588543</v>
       </c>
       <c r="N17" s="8">
-        <v>23333</v>
-      </c>
-      <c r="O17" s="8"/>
+        <f t="shared" si="1"/>
+        <v>651987</v>
+      </c>
+      <c r="O17" s="8">
+        <f t="shared" si="1"/>
+        <v>751295</v>
+      </c>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
@@ -1979,10 +2056,10 @@
       <c r="AI17" s="8"/>
       <c r="AJ17" s="8"/>
       <c r="AK17" s="8"/>
-      <c r="AL17" s="4"/>
-      <c r="AM17" s="4"/>
-      <c r="AN17" s="4"/>
-      <c r="AO17" s="4"/>
+      <c r="AL17" s="8"/>
+      <c r="AM17" s="8"/>
+      <c r="AN17" s="8"/>
+      <c r="AO17" s="8"/>
       <c r="AP17" s="4"/>
       <c r="AQ17" s="4"/>
       <c r="AR17" s="4"/>
@@ -1991,42 +2068,48 @@
       <c r="AU17" s="4"/>
       <c r="AV17" s="4"/>
       <c r="AW17" s="4"/>
-    </row>
-    <row r="18" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX17" s="4"/>
+      <c r="AY17" s="4"/>
+      <c r="AZ17" s="4"/>
+      <c r="BA17" s="4"/>
+    </row>
+    <row r="18" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8">
-        <v>131</v>
+        <v>51138</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8">
-        <v>-130</v>
+        <v>46109</v>
       </c>
       <c r="H18" s="8">
-        <v>-1273</v>
+        <v>48058</v>
       </c>
       <c r="I18" s="8">
-        <v>499</v>
+        <v>52783</v>
       </c>
       <c r="J18" s="8">
-        <v>-326</v>
+        <v>57232</v>
       </c>
       <c r="K18" s="8">
-        <v>-1128</v>
+        <v>56547</v>
       </c>
       <c r="L18" s="8">
-        <v>562</v>
+        <v>61280</v>
       </c>
       <c r="M18" s="8">
-        <v>-93</v>
+        <v>63743</v>
       </c>
       <c r="N18" s="8">
-        <v>1106</v>
-      </c>
-      <c r="O18" s="8"/>
+        <v>64857</v>
+      </c>
+      <c r="O18" s="8">
+        <v>67757</v>
+      </c>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
@@ -2049,10 +2132,10 @@
       <c r="AI18" s="8"/>
       <c r="AJ18" s="8"/>
       <c r="AK18" s="8"/>
-      <c r="AL18" s="4"/>
-      <c r="AM18" s="4"/>
-      <c r="AN18" s="4"/>
-      <c r="AO18" s="4"/>
+      <c r="AL18" s="8"/>
+      <c r="AM18" s="8"/>
+      <c r="AN18" s="8"/>
+      <c r="AO18" s="8"/>
       <c r="AP18" s="4"/>
       <c r="AQ18" s="4"/>
       <c r="AR18" s="4"/>
@@ -2061,60 +2144,48 @@
       <c r="AU18" s="4"/>
       <c r="AV18" s="4"/>
       <c r="AW18" s="4"/>
-    </row>
-    <row r="19" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX18" s="4"/>
+      <c r="AY18" s="4"/>
+      <c r="AZ18" s="4"/>
+      <c r="BA18" s="4"/>
+    </row>
+    <row r="19" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="8">
-        <f t="shared" ref="C19:G19" si="2">+C15-SUM(C16:C17)+C18</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="8">
-        <f t="shared" si="2"/>
-        <v>228065</v>
-      </c>
-      <c r="F19" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+        <v>17571</v>
+      </c>
+      <c r="F19" s="8"/>
       <c r="G19" s="8">
-        <f t="shared" si="2"/>
-        <v>249018</v>
+        <v>19248</v>
       </c>
       <c r="H19" s="8">
-        <f>+H15-SUM(H16:H17)+H18</f>
-        <v>286556</v>
+        <v>22238</v>
       </c>
       <c r="I19" s="8">
-        <f>+I15-SUM(I16:I17)+I18</f>
-        <v>360766</v>
+        <v>26295</v>
       </c>
       <c r="J19" s="8">
-        <f t="shared" ref="J19:N19" si="3">+J15-SUM(J16:J17)+J18</f>
-        <v>425713</v>
+        <v>29108</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="3"/>
-        <v>407081</v>
+        <v>28639</v>
       </c>
       <c r="L19" s="8">
-        <f t="shared" si="3"/>
-        <v>463423</v>
+        <v>23228</v>
       </c>
       <c r="M19" s="8">
-        <f t="shared" si="3"/>
-        <v>500685</v>
+        <v>24022</v>
       </c>
       <c r="N19" s="8">
-        <f t="shared" si="3"/>
-        <v>564903</v>
-      </c>
-      <c r="O19" s="8"/>
+        <v>23333</v>
+      </c>
+      <c r="O19" s="8">
+        <v>26249</v>
+      </c>
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
@@ -2137,10 +2208,10 @@
       <c r="AI19" s="8"/>
       <c r="AJ19" s="8"/>
       <c r="AK19" s="8"/>
-      <c r="AL19" s="4"/>
-      <c r="AM19" s="4"/>
-      <c r="AN19" s="4"/>
-      <c r="AO19" s="4"/>
+      <c r="AL19" s="8"/>
+      <c r="AM19" s="8"/>
+      <c r="AN19" s="8"/>
+      <c r="AO19" s="8"/>
       <c r="AP19" s="4"/>
       <c r="AQ19" s="4"/>
       <c r="AR19" s="4"/>
@@ -2149,42 +2220,48 @@
       <c r="AU19" s="4"/>
       <c r="AV19" s="4"/>
       <c r="AW19" s="4"/>
-    </row>
-    <row r="20" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX19" s="4"/>
+      <c r="AY19" s="4"/>
+      <c r="AZ19" s="4"/>
+      <c r="BA19" s="4"/>
+    </row>
+    <row r="20" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8">
-        <v>1167</v>
+        <v>131</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8">
-        <v>878</v>
+        <v>-130</v>
       </c>
       <c r="H20" s="8">
-        <v>1152</v>
+        <v>-1273</v>
       </c>
       <c r="I20" s="8">
-        <v>1561</v>
+        <v>499</v>
       </c>
       <c r="J20" s="8">
-        <v>289</v>
+        <v>-326</v>
       </c>
       <c r="K20" s="8">
-        <v>1368</v>
+        <v>-1128</v>
       </c>
       <c r="L20" s="8">
-        <v>1222</v>
+        <v>562</v>
       </c>
       <c r="M20" s="8">
-        <v>1424</v>
+        <v>-93</v>
       </c>
       <c r="N20" s="8">
-        <v>1483</v>
-      </c>
-      <c r="O20" s="8"/>
+        <v>1106</v>
+      </c>
+      <c r="O20" s="8">
+        <v>1677</v>
+      </c>
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
@@ -2207,10 +2284,10 @@
       <c r="AI20" s="8"/>
       <c r="AJ20" s="8"/>
       <c r="AK20" s="8"/>
-      <c r="AL20" s="4"/>
-      <c r="AM20" s="4"/>
-      <c r="AN20" s="4"/>
-      <c r="AO20" s="4"/>
+      <c r="AL20" s="8"/>
+      <c r="AM20" s="8"/>
+      <c r="AN20" s="8"/>
+      <c r="AO20" s="8"/>
       <c r="AP20" s="4"/>
       <c r="AQ20" s="4"/>
       <c r="AR20" s="4"/>
@@ -2219,42 +2296,67 @@
       <c r="AU20" s="4"/>
       <c r="AV20" s="4"/>
       <c r="AW20" s="4"/>
-    </row>
-    <row r="21" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX20" s="4"/>
+      <c r="AY20" s="4"/>
+      <c r="AZ20" s="4"/>
+      <c r="BA20" s="4"/>
+    </row>
+    <row r="21" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
+        <v>23</v>
+      </c>
+      <c r="C21" s="8">
+        <f t="shared" ref="C21:G21" si="2">+C17-SUM(C18:C19)+C20</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="E21" s="8">
-        <v>12483</v>
-      </c>
-      <c r="F21" s="8"/>
+        <f t="shared" si="2"/>
+        <v>228065</v>
+      </c>
+      <c r="F21" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G21" s="8">
-        <v>16661</v>
+        <f t="shared" si="2"/>
+        <v>249018</v>
       </c>
       <c r="H21" s="8">
-        <v>18341</v>
+        <f>+H17-SUM(H18:H19)+H20</f>
+        <v>286556</v>
       </c>
       <c r="I21" s="8">
-        <v>19966</v>
+        <f>+I17-SUM(I18:I19)+I20</f>
+        <v>360766</v>
       </c>
       <c r="J21" s="8">
-        <v>21750</v>
+        <f t="shared" ref="J21:O21" si="3">+J17-SUM(J18:J19)+J20</f>
+        <v>425713</v>
       </c>
       <c r="K21" s="8">
-        <v>22182</v>
+        <f t="shared" si="3"/>
+        <v>407081</v>
       </c>
       <c r="L21" s="8">
-        <v>21501</v>
+        <f t="shared" si="3"/>
+        <v>463423</v>
       </c>
       <c r="M21" s="8">
-        <v>23222</v>
+        <f t="shared" si="3"/>
+        <v>500685</v>
       </c>
       <c r="N21" s="8">
-        <v>26463</v>
-      </c>
-      <c r="O21" s="8"/>
+        <f t="shared" si="3"/>
+        <v>564903</v>
+      </c>
+      <c r="O21" s="8">
+        <f t="shared" si="3"/>
+        <v>658966</v>
+      </c>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
@@ -2277,10 +2379,10 @@
       <c r="AI21" s="8"/>
       <c r="AJ21" s="8"/>
       <c r="AK21" s="8"/>
-      <c r="AL21" s="4"/>
-      <c r="AM21" s="4"/>
-      <c r="AN21" s="4"/>
-      <c r="AO21" s="4"/>
+      <c r="AL21" s="8"/>
+      <c r="AM21" s="8"/>
+      <c r="AN21" s="8"/>
+      <c r="AO21" s="8"/>
       <c r="AP21" s="4"/>
       <c r="AQ21" s="4"/>
       <c r="AR21" s="4"/>
@@ -2289,42 +2391,48 @@
       <c r="AU21" s="4"/>
       <c r="AV21" s="4"/>
       <c r="AW21" s="4"/>
-    </row>
-    <row r="22" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX21" s="4"/>
+      <c r="AY21" s="4"/>
+      <c r="AZ21" s="4"/>
+      <c r="BA21" s="4"/>
+    </row>
+    <row r="22" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8">
-        <v>225</v>
+        <v>1167</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="8">
-        <v>-14</v>
+        <v>878</v>
       </c>
       <c r="H22" s="8">
-        <v>262</v>
+        <v>1152</v>
       </c>
       <c r="I22" s="8">
-        <v>1894</v>
+        <v>1561</v>
       </c>
       <c r="J22" s="8">
-        <v>46</v>
+        <v>289</v>
       </c>
       <c r="K22" s="8">
-        <v>264</v>
+        <v>1368</v>
       </c>
       <c r="L22" s="8">
-        <v>6890</v>
+        <v>1222</v>
       </c>
       <c r="M22" s="8">
-        <v>39</v>
+        <v>1424</v>
       </c>
       <c r="N22" s="8">
-        <v>-486</v>
-      </c>
-      <c r="O22" s="8"/>
+        <v>1483</v>
+      </c>
+      <c r="O22" s="8">
+        <v>1685</v>
+      </c>
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
@@ -2347,10 +2455,10 @@
       <c r="AI22" s="8"/>
       <c r="AJ22" s="8"/>
       <c r="AK22" s="8"/>
-      <c r="AL22" s="4"/>
-      <c r="AM22" s="4"/>
-      <c r="AN22" s="4"/>
-      <c r="AO22" s="4"/>
+      <c r="AL22" s="8"/>
+      <c r="AM22" s="8"/>
+      <c r="AN22" s="8"/>
+      <c r="AO22" s="8"/>
       <c r="AP22" s="4"/>
       <c r="AQ22" s="4"/>
       <c r="AR22" s="4"/>
@@ -2359,60 +2467,48 @@
       <c r="AU22" s="4"/>
       <c r="AV22" s="4"/>
       <c r="AW22" s="4"/>
-    </row>
-    <row r="23" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX22" s="4"/>
+      <c r="AY22" s="4"/>
+      <c r="AZ22" s="4"/>
+      <c r="BA22" s="4"/>
+    </row>
+    <row r="23" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="8">
-        <f t="shared" ref="C23:G23" si="4">+C19+SUM(C20:C22)</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="8">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
       <c r="E23" s="8">
-        <f t="shared" si="4"/>
-        <v>241940</v>
-      </c>
-      <c r="F23" s="8">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+        <v>12483</v>
+      </c>
+      <c r="F23" s="8"/>
       <c r="G23" s="8">
-        <f t="shared" si="4"/>
-        <v>266543</v>
+        <v>16661</v>
       </c>
       <c r="H23" s="8">
-        <f>+H19+SUM(H20:H22)</f>
-        <v>306311</v>
+        <v>18341</v>
       </c>
       <c r="I23" s="8">
-        <f t="shared" ref="I23:N23" si="5">+I19+SUM(I20:I22)</f>
-        <v>384187</v>
+        <v>19966</v>
       </c>
       <c r="J23" s="8">
-        <f t="shared" si="5"/>
-        <v>447798</v>
+        <v>21750</v>
       </c>
       <c r="K23" s="8">
-        <f t="shared" si="5"/>
-        <v>430895</v>
+        <v>22182</v>
       </c>
       <c r="L23" s="8">
-        <f t="shared" si="5"/>
-        <v>493036</v>
+        <v>21501</v>
       </c>
       <c r="M23" s="8">
-        <f t="shared" si="5"/>
-        <v>525370</v>
+        <v>23222</v>
       </c>
       <c r="N23" s="8">
-        <f t="shared" si="5"/>
-        <v>592363</v>
-      </c>
-      <c r="O23" s="8"/>
+        <v>26463</v>
+      </c>
+      <c r="O23" s="8">
+        <v>26146</v>
+      </c>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
@@ -2435,10 +2531,10 @@
       <c r="AI23" s="8"/>
       <c r="AJ23" s="8"/>
       <c r="AK23" s="8"/>
-      <c r="AL23" s="4"/>
-      <c r="AM23" s="4"/>
-      <c r="AN23" s="4"/>
-      <c r="AO23" s="4"/>
+      <c r="AL23" s="8"/>
+      <c r="AM23" s="8"/>
+      <c r="AN23" s="8"/>
+      <c r="AO23" s="8"/>
       <c r="AP23" s="4"/>
       <c r="AQ23" s="4"/>
       <c r="AR23" s="4"/>
@@ -2447,42 +2543,48 @@
       <c r="AU23" s="4"/>
       <c r="AV23" s="4"/>
       <c r="AW23" s="4"/>
-    </row>
-    <row r="24" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX23" s="4"/>
+      <c r="AY23" s="4"/>
+      <c r="AZ23" s="4"/>
+      <c r="BA23" s="4"/>
+    </row>
+    <row r="24" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8">
-        <v>31145</v>
+        <v>225</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8">
-        <v>41322</v>
+        <v>-14</v>
       </c>
       <c r="H24" s="8">
-        <v>58649</v>
+        <v>262</v>
       </c>
       <c r="I24" s="8">
-        <v>59107</v>
+        <v>1894</v>
       </c>
       <c r="J24" s="8">
-        <v>74329</v>
+        <v>46</v>
       </c>
       <c r="K24" s="8">
-        <v>70162</v>
+        <v>264</v>
       </c>
       <c r="L24" s="8">
-        <v>95543</v>
+        <v>6890</v>
       </c>
       <c r="M24" s="8">
-        <v>73614</v>
+        <v>39</v>
       </c>
       <c r="N24" s="8">
-        <v>86947</v>
-      </c>
-      <c r="O24" s="8"/>
+        <v>-486</v>
+      </c>
+      <c r="O24" s="8">
+        <v>1003</v>
+      </c>
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
@@ -2505,10 +2607,10 @@
       <c r="AI24" s="8"/>
       <c r="AJ24" s="8"/>
       <c r="AK24" s="8"/>
-      <c r="AL24" s="4"/>
-      <c r="AM24" s="4"/>
-      <c r="AN24" s="4"/>
-      <c r="AO24" s="4"/>
+      <c r="AL24" s="8"/>
+      <c r="AM24" s="8"/>
+      <c r="AN24" s="8"/>
+      <c r="AO24" s="8"/>
       <c r="AP24" s="4"/>
       <c r="AQ24" s="4"/>
       <c r="AR24" s="4"/>
@@ -2517,60 +2619,67 @@
       <c r="AU24" s="4"/>
       <c r="AV24" s="4"/>
       <c r="AW24" s="4"/>
-    </row>
-    <row r="25" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX24" s="4"/>
+      <c r="AY24" s="4"/>
+      <c r="AZ24" s="4"/>
+      <c r="BA24" s="4"/>
+    </row>
+    <row r="25" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C25" s="8">
-        <f t="shared" ref="C25:H25" si="6">+C23-C24</f>
+        <f t="shared" ref="C25:G25" si="4">+C21+SUM(C22:C24)</f>
         <v>0</v>
       </c>
       <c r="D25" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E25" s="8">
-        <f t="shared" si="6"/>
-        <v>210795</v>
+        <f t="shared" si="4"/>
+        <v>241940</v>
       </c>
       <c r="F25" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <f t="shared" si="6"/>
-        <v>225221</v>
+        <f t="shared" si="4"/>
+        <v>266543</v>
       </c>
       <c r="H25" s="8">
-        <f t="shared" si="6"/>
-        <v>247662</v>
+        <f>+H21+SUM(H22:H24)</f>
+        <v>306311</v>
       </c>
       <c r="I25" s="8">
-        <f>+I23-I24</f>
-        <v>325080</v>
+        <f t="shared" ref="I25:O25" si="5">+I21+SUM(I22:I24)</f>
+        <v>384187</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" ref="J25:N25" si="7">+J23-J24</f>
-        <v>373469</v>
+        <f t="shared" si="5"/>
+        <v>447798</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="7"/>
-        <v>360733</v>
+        <f t="shared" si="5"/>
+        <v>430895</v>
       </c>
       <c r="L25" s="8">
-        <f t="shared" si="7"/>
-        <v>397493</v>
+        <f t="shared" si="5"/>
+        <v>493036</v>
       </c>
       <c r="M25" s="8">
-        <f t="shared" si="7"/>
-        <v>451756</v>
+        <f t="shared" si="5"/>
+        <v>525370</v>
       </c>
       <c r="N25" s="8">
-        <f t="shared" si="7"/>
-        <v>505416</v>
-      </c>
-      <c r="O25" s="8"/>
+        <f t="shared" si="5"/>
+        <v>592363</v>
+      </c>
+      <c r="O25" s="8">
+        <f t="shared" si="5"/>
+        <v>687800</v>
+      </c>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
@@ -2593,10 +2702,10 @@
       <c r="AI25" s="8"/>
       <c r="AJ25" s="8"/>
       <c r="AK25" s="8"/>
-      <c r="AL25" s="4"/>
-      <c r="AM25" s="4"/>
-      <c r="AN25" s="4"/>
-      <c r="AO25" s="4"/>
+      <c r="AL25" s="8"/>
+      <c r="AM25" s="8"/>
+      <c r="AN25" s="8"/>
+      <c r="AO25" s="8"/>
       <c r="AP25" s="4"/>
       <c r="AQ25" s="4"/>
       <c r="AR25" s="4"/>
@@ -2605,42 +2714,48 @@
       <c r="AU25" s="4"/>
       <c r="AV25" s="4"/>
       <c r="AW25" s="4"/>
-    </row>
-    <row r="26" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX25" s="4"/>
+      <c r="AY25" s="4"/>
+      <c r="AZ25" s="4"/>
+      <c r="BA25" s="4"/>
+    </row>
+    <row r="26" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8">
-        <v>-205</v>
+        <v>31145</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8">
-        <v>-264</v>
+        <v>41322</v>
       </c>
       <c r="H26" s="8">
-        <v>-183</v>
+        <v>58649</v>
       </c>
       <c r="I26" s="8">
-        <v>-178</v>
+        <v>59107</v>
       </c>
       <c r="J26" s="8">
-        <v>-211</v>
+        <v>74329</v>
       </c>
       <c r="K26" s="8">
-        <v>-831</v>
+        <v>70162</v>
       </c>
       <c r="L26" s="8">
-        <v>0</v>
+        <v>95543</v>
       </c>
       <c r="M26" s="8">
-        <v>-547</v>
+        <v>73614</v>
       </c>
       <c r="N26" s="8">
-        <v>-328</v>
-      </c>
-      <c r="O26" s="8"/>
+        <v>86947</v>
+      </c>
+      <c r="O26" s="8">
+        <v>114999</v>
+      </c>
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
       <c r="R26" s="8"/>
@@ -2663,10 +2778,10 @@
       <c r="AI26" s="8"/>
       <c r="AJ26" s="8"/>
       <c r="AK26" s="8"/>
-      <c r="AL26" s="4"/>
-      <c r="AM26" s="4"/>
-      <c r="AN26" s="4"/>
-      <c r="AO26" s="4"/>
+      <c r="AL26" s="8"/>
+      <c r="AM26" s="8"/>
+      <c r="AN26" s="8"/>
+      <c r="AO26" s="8"/>
       <c r="AP26" s="4"/>
       <c r="AQ26" s="4"/>
       <c r="AR26" s="4"/>
@@ -2675,60 +2790,67 @@
       <c r="AU26" s="4"/>
       <c r="AV26" s="4"/>
       <c r="AW26" s="4"/>
-    </row>
-    <row r="27" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX26" s="4"/>
+      <c r="AY26" s="4"/>
+      <c r="AZ26" s="4"/>
+      <c r="BA26" s="4"/>
+    </row>
+    <row r="27" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C27" s="8">
-        <f t="shared" ref="C27:G27" si="8">+C25-C26</f>
+        <f t="shared" ref="C27:H27" si="6">+C25-C26</f>
         <v>0</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E27" s="8">
-        <f t="shared" si="8"/>
-        <v>211000</v>
+        <f t="shared" si="6"/>
+        <v>210795</v>
       </c>
       <c r="F27" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <f t="shared" si="8"/>
-        <v>225485</v>
+        <f t="shared" si="6"/>
+        <v>225221</v>
       </c>
       <c r="H27" s="8">
-        <f>+H25-H26</f>
-        <v>247845</v>
+        <f t="shared" si="6"/>
+        <v>247662</v>
       </c>
       <c r="I27" s="8">
-        <f t="shared" ref="I27:N27" si="9">+I25-I26</f>
-        <v>325258</v>
+        <f>+I25-I26</f>
+        <v>325080</v>
       </c>
       <c r="J27" s="8">
-        <f t="shared" si="9"/>
-        <v>373680</v>
+        <f t="shared" ref="J27:O27" si="7">+J25-J26</f>
+        <v>373469</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="9"/>
-        <v>361564</v>
+        <f t="shared" si="7"/>
+        <v>360733</v>
       </c>
       <c r="L27" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>397493</v>
       </c>
       <c r="M27" s="8">
-        <f t="shared" si="9"/>
-        <v>452303</v>
+        <f t="shared" si="7"/>
+        <v>451756</v>
       </c>
       <c r="N27" s="8">
-        <f t="shared" si="9"/>
-        <v>505744</v>
-      </c>
-      <c r="O27" s="8"/>
+        <f t="shared" si="7"/>
+        <v>505416</v>
+      </c>
+      <c r="O27" s="8">
+        <f t="shared" si="7"/>
+        <v>572801</v>
+      </c>
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
@@ -2751,10 +2873,10 @@
       <c r="AI27" s="8"/>
       <c r="AJ27" s="8"/>
       <c r="AK27" s="8"/>
-      <c r="AL27" s="4"/>
-      <c r="AM27" s="4"/>
-      <c r="AN27" s="4"/>
-      <c r="AO27" s="4"/>
+      <c r="AL27" s="8"/>
+      <c r="AM27" s="8"/>
+      <c r="AN27" s="8"/>
+      <c r="AO27" s="8"/>
       <c r="AP27" s="4"/>
       <c r="AQ27" s="4"/>
       <c r="AR27" s="4"/>
@@ -2763,21 +2885,48 @@
       <c r="AU27" s="4"/>
       <c r="AV27" s="4"/>
       <c r="AW27" s="4"/>
-    </row>
-    <row r="28" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX27" s="4"/>
+      <c r="AY27" s="4"/>
+      <c r="AZ27" s="4"/>
+      <c r="BA27" s="4"/>
+    </row>
+    <row r="28" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B28" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="E28" s="8">
+        <v>-205</v>
+      </c>
       <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
+      <c r="G28" s="8">
+        <v>-264</v>
+      </c>
+      <c r="H28" s="8">
+        <v>-183</v>
+      </c>
+      <c r="I28" s="8">
+        <v>-178</v>
+      </c>
+      <c r="J28" s="8">
+        <v>-211</v>
+      </c>
+      <c r="K28" s="8">
+        <v>-831</v>
+      </c>
+      <c r="L28" s="8">
+        <v>0</v>
+      </c>
+      <c r="M28" s="8">
+        <v>-547</v>
+      </c>
+      <c r="N28" s="8">
+        <v>-328</v>
+      </c>
+      <c r="O28" s="8">
+        <v>321</v>
+      </c>
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
@@ -2800,10 +2949,10 @@
       <c r="AI28" s="8"/>
       <c r="AJ28" s="8"/>
       <c r="AK28" s="8"/>
-      <c r="AL28" s="4"/>
-      <c r="AM28" s="4"/>
-      <c r="AN28" s="4"/>
-      <c r="AO28" s="4"/>
+      <c r="AL28" s="8"/>
+      <c r="AM28" s="8"/>
+      <c r="AN28" s="8"/>
+      <c r="AO28" s="8"/>
       <c r="AP28" s="4"/>
       <c r="AQ28" s="4"/>
       <c r="AR28" s="4"/>
@@ -2812,86 +2961,93 @@
       <c r="AU28" s="4"/>
       <c r="AV28" s="4"/>
       <c r="AW28" s="4"/>
-    </row>
-    <row r="29" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX28" s="4"/>
+      <c r="AY28" s="4"/>
+      <c r="AZ28" s="4"/>
+      <c r="BA28" s="4"/>
+    </row>
+    <row r="29" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="11" t="e">
-        <f t="shared" ref="C29:D29" si="10">+C27/C30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D29" s="11" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E29" s="11">
-        <f>+E27/E30</f>
-        <v>8.1376065409387177</v>
-      </c>
-      <c r="F29" s="11" t="e">
-        <f t="shared" ref="F29:N29" si="11">+F27/F30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G29" s="11">
-        <f t="shared" si="11"/>
-        <v>8.6959120709602775</v>
-      </c>
-      <c r="H29" s="11">
-        <f t="shared" si="11"/>
-        <v>9.557865103544021</v>
-      </c>
-      <c r="I29" s="11">
-        <f t="shared" si="11"/>
-        <v>12.54466214131441</v>
-      </c>
-      <c r="J29" s="11">
-        <f t="shared" si="11"/>
-        <v>14.411662617146824</v>
-      </c>
-      <c r="K29" s="11">
-        <f t="shared" si="11"/>
-        <v>13.944386594160978</v>
-      </c>
-      <c r="L29" s="11">
-        <f t="shared" si="11"/>
-        <v>15.330055150603572</v>
-      </c>
-      <c r="M29" s="11">
-        <f t="shared" si="11"/>
-        <v>17.443231777863478</v>
-      </c>
-      <c r="N29" s="11">
-        <f t="shared" si="11"/>
-        <v>19.503451467355674</v>
-      </c>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="4"/>
-      <c r="W29" s="4"/>
-      <c r="X29" s="4"/>
-      <c r="Y29" s="4"/>
-      <c r="Z29" s="4"/>
-      <c r="AA29" s="4"/>
-      <c r="AB29" s="4"/>
-      <c r="AC29" s="4"/>
-      <c r="AD29" s="4"/>
-      <c r="AE29" s="4"/>
-      <c r="AF29" s="4"/>
-      <c r="AG29" s="4"/>
-      <c r="AH29" s="4"/>
-      <c r="AI29" s="4"/>
-      <c r="AJ29" s="4"/>
-      <c r="AK29" s="4"/>
-      <c r="AL29" s="4"/>
-      <c r="AM29" s="4"/>
-      <c r="AN29" s="4"/>
-      <c r="AO29" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="C29" s="8">
+        <f t="shared" ref="C29:G29" si="8">+C27-C28</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <f t="shared" si="8"/>
+        <v>211000</v>
+      </c>
+      <c r="F29" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <f t="shared" si="8"/>
+        <v>225485</v>
+      </c>
+      <c r="H29" s="8">
+        <f>+H27-H28</f>
+        <v>247845</v>
+      </c>
+      <c r="I29" s="8">
+        <f t="shared" ref="I29:O29" si="9">+I27-I28</f>
+        <v>325258</v>
+      </c>
+      <c r="J29" s="8">
+        <f t="shared" si="9"/>
+        <v>373680</v>
+      </c>
+      <c r="K29" s="8">
+        <f t="shared" si="9"/>
+        <v>361564</v>
+      </c>
+      <c r="L29" s="8">
+        <f t="shared" si="9"/>
+        <v>397493</v>
+      </c>
+      <c r="M29" s="8">
+        <f t="shared" si="9"/>
+        <v>452303</v>
+      </c>
+      <c r="N29" s="8">
+        <f t="shared" si="9"/>
+        <v>505744</v>
+      </c>
+      <c r="O29" s="8">
+        <f t="shared" si="9"/>
+        <v>572480</v>
+      </c>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="8"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="8"/>
+      <c r="V29" s="8"/>
+      <c r="W29" s="8"/>
+      <c r="X29" s="8"/>
+      <c r="Y29" s="8"/>
+      <c r="Z29" s="8"/>
+      <c r="AA29" s="8"/>
+      <c r="AB29" s="8"/>
+      <c r="AC29" s="8"/>
+      <c r="AD29" s="8"/>
+      <c r="AE29" s="8"/>
+      <c r="AF29" s="8"/>
+      <c r="AG29" s="8"/>
+      <c r="AH29" s="8"/>
+      <c r="AI29" s="8"/>
+      <c r="AJ29" s="8"/>
+      <c r="AK29" s="8"/>
+      <c r="AL29" s="8"/>
+      <c r="AM29" s="8"/>
+      <c r="AN29" s="8"/>
+      <c r="AO29" s="8"/>
       <c r="AP29" s="4"/>
       <c r="AQ29" s="4"/>
       <c r="AR29" s="4"/>
@@ -2900,68 +3056,51 @@
       <c r="AU29" s="4"/>
       <c r="AV29" s="4"/>
       <c r="AW29" s="4"/>
-    </row>
-    <row r="30" spans="2:49" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4">
-        <v>25929</v>
-      </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4">
-        <v>25930</v>
-      </c>
-      <c r="H30" s="4">
-        <v>25931</v>
-      </c>
-      <c r="I30" s="4">
-        <v>25928</v>
-      </c>
-      <c r="J30" s="4">
-        <v>25929</v>
-      </c>
-      <c r="K30" s="4">
-        <v>25929</v>
-      </c>
-      <c r="L30" s="4">
-        <v>25929</v>
-      </c>
-      <c r="M30" s="4">
-        <v>25930</v>
-      </c>
-      <c r="N30" s="4">
-        <v>25931</v>
-      </c>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="4"/>
-      <c r="Z30" s="4"/>
-      <c r="AA30" s="4"/>
-      <c r="AB30" s="4"/>
-      <c r="AC30" s="4"/>
-      <c r="AD30" s="4"/>
-      <c r="AE30" s="4"/>
-      <c r="AF30" s="4"/>
-      <c r="AG30" s="4"/>
-      <c r="AH30" s="4"/>
-      <c r="AI30" s="4"/>
-      <c r="AJ30" s="4"/>
-      <c r="AK30" s="4"/>
-      <c r="AL30" s="4"/>
-      <c r="AM30" s="4"/>
-      <c r="AN30" s="4"/>
-      <c r="AO30" s="4"/>
+      <c r="AX29" s="4"/>
+      <c r="AY29" s="4"/>
+      <c r="AZ29" s="4"/>
+      <c r="BA29" s="4"/>
+    </row>
+    <row r="30" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8"/>
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="8"/>
+      <c r="V30" s="8"/>
+      <c r="W30" s="8"/>
+      <c r="X30" s="8"/>
+      <c r="Y30" s="8"/>
+      <c r="Z30" s="8"/>
+      <c r="AA30" s="8"/>
+      <c r="AB30" s="8"/>
+      <c r="AC30" s="8"/>
+      <c r="AD30" s="8"/>
+      <c r="AE30" s="8"/>
+      <c r="AF30" s="8"/>
+      <c r="AG30" s="8"/>
+      <c r="AH30" s="8"/>
+      <c r="AI30" s="8"/>
+      <c r="AJ30" s="8"/>
+      <c r="AK30" s="8"/>
+      <c r="AL30" s="8"/>
+      <c r="AM30" s="8"/>
+      <c r="AN30" s="8"/>
+      <c r="AO30" s="8"/>
       <c r="AP30" s="4"/>
       <c r="AQ30" s="4"/>
       <c r="AR30" s="4"/>
@@ -2970,24 +3109,70 @@
       <c r="AU30" s="4"/>
       <c r="AV30" s="4"/>
       <c r="AW30" s="4"/>
-    </row>
-    <row r="31" spans="2:49" x14ac:dyDescent="0.2">
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
+      <c r="AX30" s="4"/>
+      <c r="AY30" s="4"/>
+      <c r="AZ30" s="4"/>
+      <c r="BA30" s="4"/>
+    </row>
+    <row r="31" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B31" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="11" t="e">
+        <f t="shared" ref="C31:D31" si="10">+C29/C32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D31" s="11" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E31" s="11">
+        <f>+E29/E32</f>
+        <v>8.1376065409387177</v>
+      </c>
+      <c r="F31" s="11" t="e">
+        <f t="shared" ref="F31:O31" si="11">+F29/F32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G31" s="11">
+        <f t="shared" si="11"/>
+        <v>8.6959120709602775</v>
+      </c>
+      <c r="H31" s="11">
+        <f t="shared" si="11"/>
+        <v>9.557865103544021</v>
+      </c>
+      <c r="I31" s="11">
+        <f t="shared" si="11"/>
+        <v>12.54466214131441</v>
+      </c>
+      <c r="J31" s="11">
+        <f t="shared" si="11"/>
+        <v>14.411662617146824</v>
+      </c>
+      <c r="K31" s="11">
+        <f t="shared" si="11"/>
+        <v>13.944386594160978</v>
+      </c>
+      <c r="L31" s="11">
+        <f t="shared" si="11"/>
+        <v>15.330055150603572</v>
+      </c>
+      <c r="M31" s="11">
+        <f t="shared" si="11"/>
+        <v>17.443231777863478</v>
+      </c>
+      <c r="N31" s="11">
+        <f t="shared" si="11"/>
+        <v>19.503451467355674</v>
+      </c>
+      <c r="O31" s="11">
+        <f t="shared" si="11"/>
+        <v>22.077050634375844</v>
+      </c>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11"/>
       <c r="S31" s="4"/>
       <c r="T31" s="4"/>
       <c r="U31" s="4"/>
@@ -3019,48 +3204,48 @@
       <c r="AU31" s="4"/>
       <c r="AV31" s="4"/>
       <c r="AW31" s="4"/>
-    </row>
-    <row r="32" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX31" s="4"/>
+      <c r="AY31" s="4"/>
+      <c r="AZ31" s="4"/>
+      <c r="BA31" s="4"/>
+    </row>
+    <row r="32" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
+      <c r="E32" s="4">
+        <v>25929</v>
+      </c>
       <c r="F32" s="4"/>
-      <c r="G32" s="12" t="e">
-        <f t="shared" ref="G32:J32" si="12">+G13/C13-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H32" s="12" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I32" s="12">
-        <f t="shared" si="12"/>
-        <v>0.38951188239963574</v>
-      </c>
-      <c r="J32" s="12" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K32" s="12">
-        <f>+K13/G13-1</f>
-        <v>0.41611827673949286</v>
-      </c>
-      <c r="L32" s="12">
-        <f>+L13/H13-1</f>
-        <v>0.386456028863714</v>
-      </c>
-      <c r="M32" s="12">
-        <f>+M13/I13-1</f>
-        <v>0.30305176308293369</v>
-      </c>
-      <c r="N32" s="12">
-        <f>+N13/J13-1</f>
-        <v>0.20453307632697371</v>
-      </c>
-      <c r="O32" s="4"/>
+      <c r="G32" s="4">
+        <v>25930</v>
+      </c>
+      <c r="H32" s="4">
+        <v>25931</v>
+      </c>
+      <c r="I32" s="4">
+        <v>25928</v>
+      </c>
+      <c r="J32" s="4">
+        <v>25929</v>
+      </c>
+      <c r="K32" s="4">
+        <v>25929</v>
+      </c>
+      <c r="L32" s="4">
+        <v>25929</v>
+      </c>
+      <c r="M32" s="4">
+        <v>25930</v>
+      </c>
+      <c r="N32" s="4">
+        <v>25931</v>
+      </c>
+      <c r="O32" s="4">
+        <v>25931</v>
+      </c>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
       <c r="R32" s="4"/>
@@ -3095,59 +3280,24 @@
       <c r="AU32" s="4"/>
       <c r="AV32" s="4"/>
       <c r="AW32" s="4"/>
-    </row>
-    <row r="33" spans="2:49" x14ac:dyDescent="0.2">
-      <c r="B33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="13" t="e">
-        <f t="shared" ref="C33:H33" si="13">+C15/C13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D33" s="13" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E33" s="13">
-        <f t="shared" si="13"/>
-        <v>0.5425737974477487</v>
-      </c>
-      <c r="F33" s="13" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G33" s="13">
-        <f t="shared" si="13"/>
-        <v>0.53068115091015855</v>
-      </c>
-      <c r="H33" s="13">
-        <f t="shared" si="13"/>
-        <v>0.53172929874834818</v>
-      </c>
-      <c r="I33" s="13">
-        <f>+I15/I13</f>
-        <v>0.57831989806395223</v>
-      </c>
-      <c r="J33" s="13">
-        <f t="shared" ref="J33:K33" si="14">+J15/J13</f>
-        <v>0.58998504250622652</v>
-      </c>
-      <c r="K33" s="13">
-        <f t="shared" si="14"/>
-        <v>0.58789710862265776</v>
-      </c>
-      <c r="L33" s="13">
-        <f t="shared" ref="L33:M33" si="15">+L15/L13</f>
-        <v>0.58617872074294919</v>
-      </c>
-      <c r="M33" s="13">
-        <f t="shared" si="15"/>
-        <v>0.59453712327687747</v>
-      </c>
-      <c r="N33" s="13">
-        <f t="shared" ref="N33" si="16">+N15/N13</f>
-        <v>0.62326090489346042</v>
-      </c>
+      <c r="AX32" s="4"/>
+      <c r="AY32" s="4"/>
+      <c r="AZ32" s="4"/>
+      <c r="BA32" s="4"/>
+    </row>
+    <row r="33" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
@@ -3183,63 +3333,58 @@
       <c r="AU33" s="4"/>
       <c r="AV33" s="4"/>
       <c r="AW33" s="4"/>
-    </row>
-    <row r="34" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX33" s="4"/>
+      <c r="AY33" s="4"/>
+      <c r="AZ33" s="4"/>
+      <c r="BA33" s="4"/>
+    </row>
+    <row r="34" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="13" t="e">
-        <f t="shared" ref="C34:H34" si="17">+C19/C13</f>
+        <v>33</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="12" t="e">
+        <f t="shared" ref="G34:J34" si="12">+G15/C15-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D34" s="13" t="e">
-        <f t="shared" si="17"/>
+      <c r="H34" s="12" t="e">
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E34" s="13">
-        <f t="shared" si="17"/>
-        <v>0.41714145661593499</v>
-      </c>
-      <c r="F34" s="13" t="e">
-        <f t="shared" si="17"/>
+      <c r="I34" s="12">
+        <f t="shared" si="12"/>
+        <v>0.38951188239963574</v>
+      </c>
+      <c r="J34" s="12" t="e">
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G34" s="13">
-        <f t="shared" si="17"/>
-        <v>0.42018142426144534</v>
-      </c>
-      <c r="H34" s="13">
-        <f t="shared" si="17"/>
-        <v>0.42546658549984412</v>
-      </c>
-      <c r="I34" s="13">
-        <f>+I19/I13</f>
-        <v>0.47488455847896255</v>
-      </c>
-      <c r="J34" s="13">
-        <f t="shared" ref="J34:K34" si="18">+J19/J13</f>
-        <v>0.49019242084561082</v>
-      </c>
-      <c r="K34" s="13">
-        <f t="shared" si="18"/>
-        <v>0.48505100958708569</v>
-      </c>
-      <c r="L34" s="13">
-        <f t="shared" ref="L34:M34" si="19">+L19/L13</f>
-        <v>0.49628075631403995</v>
-      </c>
-      <c r="M34" s="13">
-        <f t="shared" si="19"/>
-        <v>0.50578431748892327</v>
-      </c>
-      <c r="N34" s="13">
-        <f t="shared" ref="N34" si="20">+N19/N13</f>
-        <v>0.54001376554598557</v>
-      </c>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
+      <c r="K34" s="12">
+        <f>+K15/G15-1</f>
+        <v>0.41611827673949286</v>
+      </c>
+      <c r="L34" s="12">
+        <f>+L15/H15-1</f>
+        <v>0.386456028863714</v>
+      </c>
+      <c r="M34" s="12">
+        <f>+M15/I15-1</f>
+        <v>0.30305176308293369</v>
+      </c>
+      <c r="N34" s="12">
+        <f>+N15/J15-1</f>
+        <v>0.20453307632697371</v>
+      </c>
+      <c r="O34" s="12">
+        <f>+O15/K15-1</f>
+        <v>0.35132272232244355</v>
+      </c>
+      <c r="P34" s="12"/>
+      <c r="Q34" s="12"/>
+      <c r="R34" s="12"/>
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
@@ -3271,63 +3416,70 @@
       <c r="AU34" s="4"/>
       <c r="AV34" s="4"/>
       <c r="AW34" s="4"/>
-    </row>
-    <row r="35" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX34" s="4"/>
+      <c r="AY34" s="4"/>
+      <c r="AZ34" s="4"/>
+      <c r="BA34" s="4"/>
+    </row>
+    <row r="35" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C35" s="13" t="e">
-        <f t="shared" ref="C35:H35" si="21">+C24/C23</f>
+        <f t="shared" ref="C35:H35" si="13">+C17/C15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D35" s="13" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E35" s="13">
-        <f t="shared" si="21"/>
-        <v>0.12873026370174423</v>
+        <f t="shared" si="13"/>
+        <v>0.5425737974477487</v>
       </c>
       <c r="F35" s="13" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G35" s="13">
-        <f t="shared" si="21"/>
-        <v>0.15502939488187648</v>
+        <f t="shared" si="13"/>
+        <v>0.53068115091015855</v>
       </c>
       <c r="H35" s="13">
-        <f t="shared" si="21"/>
-        <v>0.19146880131630925</v>
+        <f t="shared" si="13"/>
+        <v>0.53172929874834818</v>
       </c>
       <c r="I35" s="13">
-        <f>+I24/I23</f>
-        <v>0.15384955763729641</v>
+        <f>+I17/I15</f>
+        <v>0.57831989806395223</v>
       </c>
       <c r="J35" s="13">
-        <f t="shared" ref="J35:K35" si="22">+J24/J23</f>
-        <v>0.16598778913706627</v>
+        <f t="shared" ref="J35:K35" si="14">+J17/J15</f>
+        <v>0.58998504250622652</v>
       </c>
       <c r="K35" s="13">
-        <f t="shared" si="22"/>
-        <v>0.16282853131273281</v>
+        <f t="shared" si="14"/>
+        <v>0.58789710862265776</v>
       </c>
       <c r="L35" s="13">
-        <f t="shared" ref="L35:M35" si="23">+L24/L23</f>
-        <v>0.19378503800939484</v>
+        <f t="shared" ref="L35:M35" si="15">+L17/L15</f>
+        <v>0.58617872074294919</v>
       </c>
       <c r="M35" s="13">
-        <f t="shared" si="23"/>
-        <v>0.14011839275177493</v>
+        <f t="shared" si="15"/>
+        <v>0.59453712327687747</v>
       </c>
       <c r="N35" s="13">
-        <f t="shared" ref="N35" si="24">+N24/N23</f>
-        <v>0.14677993054934221</v>
-      </c>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
+        <f t="shared" ref="N35:O35" si="16">+N17/N15</f>
+        <v>0.62326090489346042</v>
+      </c>
+      <c r="O35" s="13">
+        <f t="shared" si="16"/>
+        <v>0.66245746638532832</v>
+      </c>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
       <c r="S35" s="4"/>
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
@@ -3359,24 +3511,70 @@
       <c r="AU35" s="4"/>
       <c r="AV35" s="4"/>
       <c r="AW35" s="4"/>
-    </row>
-    <row r="36" spans="2:49" x14ac:dyDescent="0.2">
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
+      <c r="AX35" s="4"/>
+      <c r="AY35" s="4"/>
+      <c r="AZ35" s="4"/>
+      <c r="BA35" s="4"/>
+    </row>
+    <row r="36" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="13" t="e">
+        <f t="shared" ref="C36:H36" si="17">+C21/C15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D36" s="13" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E36" s="13">
+        <f t="shared" si="17"/>
+        <v>0.41714145661593499</v>
+      </c>
+      <c r="F36" s="13" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G36" s="13">
+        <f t="shared" si="17"/>
+        <v>0.42018142426144534</v>
+      </c>
+      <c r="H36" s="13">
+        <f t="shared" si="17"/>
+        <v>0.42546658549984412</v>
+      </c>
+      <c r="I36" s="13">
+        <f>+I21/I15</f>
+        <v>0.47488455847896255</v>
+      </c>
+      <c r="J36" s="13">
+        <f t="shared" ref="J36:K36" si="18">+J21/J15</f>
+        <v>0.49019242084561082</v>
+      </c>
+      <c r="K36" s="13">
+        <f t="shared" si="18"/>
+        <v>0.48505100958708569</v>
+      </c>
+      <c r="L36" s="13">
+        <f t="shared" ref="L36:M36" si="19">+L21/L15</f>
+        <v>0.49628075631403995</v>
+      </c>
+      <c r="M36" s="13">
+        <f t="shared" si="19"/>
+        <v>0.50578431748892327</v>
+      </c>
+      <c r="N36" s="13">
+        <f t="shared" ref="N36:O36" si="20">+N21/N15</f>
+        <v>0.54001376554598557</v>
+      </c>
+      <c r="O36" s="13">
+        <f t="shared" si="20"/>
+        <v>0.58104598964997012</v>
+      </c>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
       <c r="S36" s="4"/>
       <c r="T36" s="4"/>
       <c r="U36" s="4"/>
@@ -3408,24 +3606,70 @@
       <c r="AU36" s="4"/>
       <c r="AV36" s="4"/>
       <c r="AW36" s="4"/>
-    </row>
-    <row r="37" spans="2:49" x14ac:dyDescent="0.2">
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
+      <c r="AX36" s="4"/>
+      <c r="AY36" s="4"/>
+      <c r="AZ36" s="4"/>
+      <c r="BA36" s="4"/>
+    </row>
+    <row r="37" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="13" t="e">
+        <f t="shared" ref="C37:H37" si="21">+C26/C25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D37" s="13" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E37" s="13">
+        <f t="shared" si="21"/>
+        <v>0.12873026370174423</v>
+      </c>
+      <c r="F37" s="13" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G37" s="13">
+        <f t="shared" si="21"/>
+        <v>0.15502939488187648</v>
+      </c>
+      <c r="H37" s="13">
+        <f t="shared" si="21"/>
+        <v>0.19146880131630925</v>
+      </c>
+      <c r="I37" s="13">
+        <f>+I26/I25</f>
+        <v>0.15384955763729641</v>
+      </c>
+      <c r="J37" s="13">
+        <f t="shared" ref="J37:K37" si="22">+J26/J25</f>
+        <v>0.16598778913706627</v>
+      </c>
+      <c r="K37" s="13">
+        <f t="shared" si="22"/>
+        <v>0.16282853131273281</v>
+      </c>
+      <c r="L37" s="13">
+        <f t="shared" ref="L37:M37" si="23">+L26/L25</f>
+        <v>0.19378503800939484</v>
+      </c>
+      <c r="M37" s="13">
+        <f t="shared" si="23"/>
+        <v>0.14011839275177493</v>
+      </c>
+      <c r="N37" s="13">
+        <f t="shared" ref="N37:O37" si="24">+N26/N25</f>
+        <v>0.14677993054934221</v>
+      </c>
+      <c r="O37" s="13">
+        <f t="shared" si="24"/>
+        <v>0.16719831346321606</v>
+      </c>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="13"/>
       <c r="S37" s="4"/>
       <c r="T37" s="4"/>
       <c r="U37" s="4"/>
@@ -3457,8 +3701,12 @@
       <c r="AU37" s="4"/>
       <c r="AV37" s="4"/>
       <c r="AW37" s="4"/>
-    </row>
-    <row r="38" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX37" s="4"/>
+      <c r="AY37" s="4"/>
+      <c r="AZ37" s="4"/>
+      <c r="BA37" s="4"/>
+    </row>
+    <row r="38" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -3506,8 +3754,12 @@
       <c r="AU38" s="4"/>
       <c r="AV38" s="4"/>
       <c r="AW38" s="4"/>
-    </row>
-    <row r="39" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX38" s="4"/>
+      <c r="AY38" s="4"/>
+      <c r="AZ38" s="4"/>
+      <c r="BA38" s="4"/>
+    </row>
+    <row r="39" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -3555,8 +3807,12 @@
       <c r="AU39" s="4"/>
       <c r="AV39" s="4"/>
       <c r="AW39" s="4"/>
-    </row>
-    <row r="40" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX39" s="4"/>
+      <c r="AY39" s="4"/>
+      <c r="AZ39" s="4"/>
+      <c r="BA39" s="4"/>
+    </row>
+    <row r="40" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -3604,8 +3860,12 @@
       <c r="AU40" s="4"/>
       <c r="AV40" s="4"/>
       <c r="AW40" s="4"/>
-    </row>
-    <row r="41" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX40" s="4"/>
+      <c r="AY40" s="4"/>
+      <c r="AZ40" s="4"/>
+      <c r="BA40" s="4"/>
+    </row>
+    <row r="41" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -3653,8 +3913,12 @@
       <c r="AU41" s="4"/>
       <c r="AV41" s="4"/>
       <c r="AW41" s="4"/>
-    </row>
-    <row r="42" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX41" s="4"/>
+      <c r="AY41" s="4"/>
+      <c r="AZ41" s="4"/>
+      <c r="BA41" s="4"/>
+    </row>
+    <row r="42" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -3702,8 +3966,12 @@
       <c r="AU42" s="4"/>
       <c r="AV42" s="4"/>
       <c r="AW42" s="4"/>
-    </row>
-    <row r="43" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX42" s="4"/>
+      <c r="AY42" s="4"/>
+      <c r="AZ42" s="4"/>
+      <c r="BA42" s="4"/>
+    </row>
+    <row r="43" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -3751,8 +4019,12 @@
       <c r="AU43" s="4"/>
       <c r="AV43" s="4"/>
       <c r="AW43" s="4"/>
-    </row>
-    <row r="44" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX43" s="4"/>
+      <c r="AY43" s="4"/>
+      <c r="AZ43" s="4"/>
+      <c r="BA43" s="4"/>
+    </row>
+    <row r="44" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -3800,8 +4072,12 @@
       <c r="AU44" s="4"/>
       <c r="AV44" s="4"/>
       <c r="AW44" s="4"/>
-    </row>
-    <row r="45" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX44" s="4"/>
+      <c r="AY44" s="4"/>
+      <c r="AZ44" s="4"/>
+      <c r="BA44" s="4"/>
+    </row>
+    <row r="45" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -3849,8 +4125,12 @@
       <c r="AU45" s="4"/>
       <c r="AV45" s="4"/>
       <c r="AW45" s="4"/>
-    </row>
-    <row r="46" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX45" s="4"/>
+      <c r="AY45" s="4"/>
+      <c r="AZ45" s="4"/>
+      <c r="BA45" s="4"/>
+    </row>
+    <row r="46" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -3898,8 +4178,12 @@
       <c r="AU46" s="4"/>
       <c r="AV46" s="4"/>
       <c r="AW46" s="4"/>
-    </row>
-    <row r="47" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX46" s="4"/>
+      <c r="AY46" s="4"/>
+      <c r="AZ46" s="4"/>
+      <c r="BA46" s="4"/>
+    </row>
+    <row r="47" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -3947,8 +4231,12 @@
       <c r="AU47" s="4"/>
       <c r="AV47" s="4"/>
       <c r="AW47" s="4"/>
-    </row>
-    <row r="48" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="AX47" s="4"/>
+      <c r="AY47" s="4"/>
+      <c r="AZ47" s="4"/>
+      <c r="BA47" s="4"/>
+    </row>
+    <row r="48" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -3996,8 +4284,12 @@
       <c r="AU48" s="4"/>
       <c r="AV48" s="4"/>
       <c r="AW48" s="4"/>
-    </row>
-    <row r="49" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX48" s="4"/>
+      <c r="AY48" s="4"/>
+      <c r="AZ48" s="4"/>
+      <c r="BA48" s="4"/>
+    </row>
+    <row r="49" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -4045,8 +4337,12 @@
       <c r="AU49" s="4"/>
       <c r="AV49" s="4"/>
       <c r="AW49" s="4"/>
-    </row>
-    <row r="50" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX49" s="4"/>
+      <c r="AY49" s="4"/>
+      <c r="AZ49" s="4"/>
+      <c r="BA49" s="4"/>
+    </row>
+    <row r="50" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -4094,8 +4390,12 @@
       <c r="AU50" s="4"/>
       <c r="AV50" s="4"/>
       <c r="AW50" s="4"/>
-    </row>
-    <row r="51" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX50" s="4"/>
+      <c r="AY50" s="4"/>
+      <c r="AZ50" s="4"/>
+      <c r="BA50" s="4"/>
+    </row>
+    <row r="51" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -4143,8 +4443,12 @@
       <c r="AU51" s="4"/>
       <c r="AV51" s="4"/>
       <c r="AW51" s="4"/>
-    </row>
-    <row r="52" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX51" s="4"/>
+      <c r="AY51" s="4"/>
+      <c r="AZ51" s="4"/>
+      <c r="BA51" s="4"/>
+    </row>
+    <row r="52" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -4192,8 +4496,12 @@
       <c r="AU52" s="4"/>
       <c r="AV52" s="4"/>
       <c r="AW52" s="4"/>
-    </row>
-    <row r="53" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX52" s="4"/>
+      <c r="AY52" s="4"/>
+      <c r="AZ52" s="4"/>
+      <c r="BA52" s="4"/>
+    </row>
+    <row r="53" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -4241,8 +4549,12 @@
       <c r="AU53" s="4"/>
       <c r="AV53" s="4"/>
       <c r="AW53" s="4"/>
-    </row>
-    <row r="54" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX53" s="4"/>
+      <c r="AY53" s="4"/>
+      <c r="AZ53" s="4"/>
+      <c r="BA53" s="4"/>
+    </row>
+    <row r="54" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -4290,8 +4602,12 @@
       <c r="AU54" s="4"/>
       <c r="AV54" s="4"/>
       <c r="AW54" s="4"/>
-    </row>
-    <row r="55" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX54" s="4"/>
+      <c r="AY54" s="4"/>
+      <c r="AZ54" s="4"/>
+      <c r="BA54" s="4"/>
+    </row>
+    <row r="55" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -4339,8 +4655,12 @@
       <c r="AU55" s="4"/>
       <c r="AV55" s="4"/>
       <c r="AW55" s="4"/>
-    </row>
-    <row r="56" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX55" s="4"/>
+      <c r="AY55" s="4"/>
+      <c r="AZ55" s="4"/>
+      <c r="BA55" s="4"/>
+    </row>
+    <row r="56" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -4388,8 +4708,12 @@
       <c r="AU56" s="4"/>
       <c r="AV56" s="4"/>
       <c r="AW56" s="4"/>
-    </row>
-    <row r="57" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX56" s="4"/>
+      <c r="AY56" s="4"/>
+      <c r="AZ56" s="4"/>
+      <c r="BA56" s="4"/>
+    </row>
+    <row r="57" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -4437,8 +4761,12 @@
       <c r="AU57" s="4"/>
       <c r="AV57" s="4"/>
       <c r="AW57" s="4"/>
-    </row>
-    <row r="58" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX57" s="4"/>
+      <c r="AY57" s="4"/>
+      <c r="AZ57" s="4"/>
+      <c r="BA57" s="4"/>
+    </row>
+    <row r="58" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -4486,8 +4814,12 @@
       <c r="AU58" s="4"/>
       <c r="AV58" s="4"/>
       <c r="AW58" s="4"/>
-    </row>
-    <row r="59" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX58" s="4"/>
+      <c r="AY58" s="4"/>
+      <c r="AZ58" s="4"/>
+      <c r="BA58" s="4"/>
+    </row>
+    <row r="59" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -4535,8 +4867,12 @@
       <c r="AU59" s="4"/>
       <c r="AV59" s="4"/>
       <c r="AW59" s="4"/>
-    </row>
-    <row r="60" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX59" s="4"/>
+      <c r="AY59" s="4"/>
+      <c r="AZ59" s="4"/>
+      <c r="BA59" s="4"/>
+    </row>
+    <row r="60" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -4584,8 +4920,12 @@
       <c r="AU60" s="4"/>
       <c r="AV60" s="4"/>
       <c r="AW60" s="4"/>
-    </row>
-    <row r="61" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX60" s="4"/>
+      <c r="AY60" s="4"/>
+      <c r="AZ60" s="4"/>
+      <c r="BA60" s="4"/>
+    </row>
+    <row r="61" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -4633,8 +4973,12 @@
       <c r="AU61" s="4"/>
       <c r="AV61" s="4"/>
       <c r="AW61" s="4"/>
-    </row>
-    <row r="62" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX61" s="4"/>
+      <c r="AY61" s="4"/>
+      <c r="AZ61" s="4"/>
+      <c r="BA61" s="4"/>
+    </row>
+    <row r="62" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -4682,8 +5026,12 @@
       <c r="AU62" s="4"/>
       <c r="AV62" s="4"/>
       <c r="AW62" s="4"/>
-    </row>
-    <row r="63" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX62" s="4"/>
+      <c r="AY62" s="4"/>
+      <c r="AZ62" s="4"/>
+      <c r="BA62" s="4"/>
+    </row>
+    <row r="63" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -4731,8 +5079,12 @@
       <c r="AU63" s="4"/>
       <c r="AV63" s="4"/>
       <c r="AW63" s="4"/>
-    </row>
-    <row r="64" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX63" s="4"/>
+      <c r="AY63" s="4"/>
+      <c r="AZ63" s="4"/>
+      <c r="BA63" s="4"/>
+    </row>
+    <row r="64" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -4780,8 +5132,12 @@
       <c r="AU64" s="4"/>
       <c r="AV64" s="4"/>
       <c r="AW64" s="4"/>
-    </row>
-    <row r="65" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX64" s="4"/>
+      <c r="AY64" s="4"/>
+      <c r="AZ64" s="4"/>
+      <c r="BA64" s="4"/>
+    </row>
+    <row r="65" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -4829,8 +5185,12 @@
       <c r="AU65" s="4"/>
       <c r="AV65" s="4"/>
       <c r="AW65" s="4"/>
-    </row>
-    <row r="66" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX65" s="4"/>
+      <c r="AY65" s="4"/>
+      <c r="AZ65" s="4"/>
+      <c r="BA65" s="4"/>
+    </row>
+    <row r="66" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -4878,8 +5238,12 @@
       <c r="AU66" s="4"/>
       <c r="AV66" s="4"/>
       <c r="AW66" s="4"/>
-    </row>
-    <row r="67" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX66" s="4"/>
+      <c r="AY66" s="4"/>
+      <c r="AZ66" s="4"/>
+      <c r="BA66" s="4"/>
+    </row>
+    <row r="67" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
@@ -4927,8 +5291,12 @@
       <c r="AU67" s="4"/>
       <c r="AV67" s="4"/>
       <c r="AW67" s="4"/>
-    </row>
-    <row r="68" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX67" s="4"/>
+      <c r="AY67" s="4"/>
+      <c r="AZ67" s="4"/>
+      <c r="BA67" s="4"/>
+    </row>
+    <row r="68" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -4976,8 +5344,12 @@
       <c r="AU68" s="4"/>
       <c r="AV68" s="4"/>
       <c r="AW68" s="4"/>
-    </row>
-    <row r="69" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX68" s="4"/>
+      <c r="AY68" s="4"/>
+      <c r="AZ68" s="4"/>
+      <c r="BA68" s="4"/>
+    </row>
+    <row r="69" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -5025,8 +5397,12 @@
       <c r="AU69" s="4"/>
       <c r="AV69" s="4"/>
       <c r="AW69" s="4"/>
-    </row>
-    <row r="70" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX69" s="4"/>
+      <c r="AY69" s="4"/>
+      <c r="AZ69" s="4"/>
+      <c r="BA69" s="4"/>
+    </row>
+    <row r="70" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -5074,8 +5450,12 @@
       <c r="AU70" s="4"/>
       <c r="AV70" s="4"/>
       <c r="AW70" s="4"/>
-    </row>
-    <row r="71" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX70" s="4"/>
+      <c r="AY70" s="4"/>
+      <c r="AZ70" s="4"/>
+      <c r="BA70" s="4"/>
+    </row>
+    <row r="71" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -5123,8 +5503,12 @@
       <c r="AU71" s="4"/>
       <c r="AV71" s="4"/>
       <c r="AW71" s="4"/>
-    </row>
-    <row r="72" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX71" s="4"/>
+      <c r="AY71" s="4"/>
+      <c r="AZ71" s="4"/>
+      <c r="BA71" s="4"/>
+    </row>
+    <row r="72" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -5172,8 +5556,12 @@
       <c r="AU72" s="4"/>
       <c r="AV72" s="4"/>
       <c r="AW72" s="4"/>
-    </row>
-    <row r="73" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX72" s="4"/>
+      <c r="AY72" s="4"/>
+      <c r="AZ72" s="4"/>
+      <c r="BA72" s="4"/>
+    </row>
+    <row r="73" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
@@ -5221,8 +5609,12 @@
       <c r="AU73" s="4"/>
       <c r="AV73" s="4"/>
       <c r="AW73" s="4"/>
-    </row>
-    <row r="74" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX73" s="4"/>
+      <c r="AY73" s="4"/>
+      <c r="AZ73" s="4"/>
+      <c r="BA73" s="4"/>
+    </row>
+    <row r="74" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -5270,8 +5662,12 @@
       <c r="AU74" s="4"/>
       <c r="AV74" s="4"/>
       <c r="AW74" s="4"/>
-    </row>
-    <row r="75" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX74" s="4"/>
+      <c r="AY74" s="4"/>
+      <c r="AZ74" s="4"/>
+      <c r="BA74" s="4"/>
+    </row>
+    <row r="75" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
@@ -5319,8 +5715,12 @@
       <c r="AU75" s="4"/>
       <c r="AV75" s="4"/>
       <c r="AW75" s="4"/>
-    </row>
-    <row r="76" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX75" s="4"/>
+      <c r="AY75" s="4"/>
+      <c r="AZ75" s="4"/>
+      <c r="BA75" s="4"/>
+    </row>
+    <row r="76" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -5368,8 +5768,12 @@
       <c r="AU76" s="4"/>
       <c r="AV76" s="4"/>
       <c r="AW76" s="4"/>
-    </row>
-    <row r="77" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX76" s="4"/>
+      <c r="AY76" s="4"/>
+      <c r="AZ76" s="4"/>
+      <c r="BA76" s="4"/>
+    </row>
+    <row r="77" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -5417,8 +5821,12 @@
       <c r="AU77" s="4"/>
       <c r="AV77" s="4"/>
       <c r="AW77" s="4"/>
-    </row>
-    <row r="78" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX77" s="4"/>
+      <c r="AY77" s="4"/>
+      <c r="AZ77" s="4"/>
+      <c r="BA77" s="4"/>
+    </row>
+    <row r="78" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
@@ -5466,8 +5874,12 @@
       <c r="AU78" s="4"/>
       <c r="AV78" s="4"/>
       <c r="AW78" s="4"/>
-    </row>
-    <row r="79" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX78" s="4"/>
+      <c r="AY78" s="4"/>
+      <c r="AZ78" s="4"/>
+      <c r="BA78" s="4"/>
+    </row>
+    <row r="79" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
@@ -5515,8 +5927,12 @@
       <c r="AU79" s="4"/>
       <c r="AV79" s="4"/>
       <c r="AW79" s="4"/>
-    </row>
-    <row r="80" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX79" s="4"/>
+      <c r="AY79" s="4"/>
+      <c r="AZ79" s="4"/>
+      <c r="BA79" s="4"/>
+    </row>
+    <row r="80" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -5564,8 +5980,12 @@
       <c r="AU80" s="4"/>
       <c r="AV80" s="4"/>
       <c r="AW80" s="4"/>
-    </row>
-    <row r="81" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX80" s="4"/>
+      <c r="AY80" s="4"/>
+      <c r="AZ80" s="4"/>
+      <c r="BA80" s="4"/>
+    </row>
+    <row r="81" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -5613,8 +6033,12 @@
       <c r="AU81" s="4"/>
       <c r="AV81" s="4"/>
       <c r="AW81" s="4"/>
-    </row>
-    <row r="82" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX81" s="4"/>
+      <c r="AY81" s="4"/>
+      <c r="AZ81" s="4"/>
+      <c r="BA81" s="4"/>
+    </row>
+    <row r="82" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
@@ -5662,8 +6086,12 @@
       <c r="AU82" s="4"/>
       <c r="AV82" s="4"/>
       <c r="AW82" s="4"/>
-    </row>
-    <row r="83" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX82" s="4"/>
+      <c r="AY82" s="4"/>
+      <c r="AZ82" s="4"/>
+      <c r="BA82" s="4"/>
+    </row>
+    <row r="83" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -5711,8 +6139,12 @@
       <c r="AU83" s="4"/>
       <c r="AV83" s="4"/>
       <c r="AW83" s="4"/>
-    </row>
-    <row r="84" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX83" s="4"/>
+      <c r="AY83" s="4"/>
+      <c r="AZ83" s="4"/>
+      <c r="BA83" s="4"/>
+    </row>
+    <row r="84" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -5760,8 +6192,12 @@
       <c r="AU84" s="4"/>
       <c r="AV84" s="4"/>
       <c r="AW84" s="4"/>
-    </row>
-    <row r="85" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX84" s="4"/>
+      <c r="AY84" s="4"/>
+      <c r="AZ84" s="4"/>
+      <c r="BA84" s="4"/>
+    </row>
+    <row r="85" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
@@ -5809,8 +6245,12 @@
       <c r="AU85" s="4"/>
       <c r="AV85" s="4"/>
       <c r="AW85" s="4"/>
-    </row>
-    <row r="86" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX85" s="4"/>
+      <c r="AY85" s="4"/>
+      <c r="AZ85" s="4"/>
+      <c r="BA85" s="4"/>
+    </row>
+    <row r="86" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -5858,8 +6298,12 @@
       <c r="AU86" s="4"/>
       <c r="AV86" s="4"/>
       <c r="AW86" s="4"/>
-    </row>
-    <row r="87" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX86" s="4"/>
+      <c r="AY86" s="4"/>
+      <c r="AZ86" s="4"/>
+      <c r="BA86" s="4"/>
+    </row>
+    <row r="87" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
@@ -5907,8 +6351,12 @@
       <c r="AU87" s="4"/>
       <c r="AV87" s="4"/>
       <c r="AW87" s="4"/>
-    </row>
-    <row r="88" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX87" s="4"/>
+      <c r="AY87" s="4"/>
+      <c r="AZ87" s="4"/>
+      <c r="BA87" s="4"/>
+    </row>
+    <row r="88" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
@@ -5956,8 +6404,12 @@
       <c r="AU88" s="4"/>
       <c r="AV88" s="4"/>
       <c r="AW88" s="4"/>
-    </row>
-    <row r="89" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX88" s="4"/>
+      <c r="AY88" s="4"/>
+      <c r="AZ88" s="4"/>
+      <c r="BA88" s="4"/>
+    </row>
+    <row r="89" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -6005,8 +6457,12 @@
       <c r="AU89" s="4"/>
       <c r="AV89" s="4"/>
       <c r="AW89" s="4"/>
-    </row>
-    <row r="90" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX89" s="4"/>
+      <c r="AY89" s="4"/>
+      <c r="AZ89" s="4"/>
+      <c r="BA89" s="4"/>
+    </row>
+    <row r="90" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -6054,8 +6510,12 @@
       <c r="AU90" s="4"/>
       <c r="AV90" s="4"/>
       <c r="AW90" s="4"/>
-    </row>
-    <row r="91" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX90" s="4"/>
+      <c r="AY90" s="4"/>
+      <c r="AZ90" s="4"/>
+      <c r="BA90" s="4"/>
+    </row>
+    <row r="91" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
@@ -6103,8 +6563,12 @@
       <c r="AU91" s="4"/>
       <c r="AV91" s="4"/>
       <c r="AW91" s="4"/>
-    </row>
-    <row r="92" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX91" s="4"/>
+      <c r="AY91" s="4"/>
+      <c r="AZ91" s="4"/>
+      <c r="BA91" s="4"/>
+    </row>
+    <row r="92" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -6152,8 +6616,12 @@
       <c r="AU92" s="4"/>
       <c r="AV92" s="4"/>
       <c r="AW92" s="4"/>
-    </row>
-    <row r="93" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX92" s="4"/>
+      <c r="AY92" s="4"/>
+      <c r="AZ92" s="4"/>
+      <c r="BA92" s="4"/>
+    </row>
+    <row r="93" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
@@ -6201,8 +6669,12 @@
       <c r="AU93" s="4"/>
       <c r="AV93" s="4"/>
       <c r="AW93" s="4"/>
-    </row>
-    <row r="94" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX93" s="4"/>
+      <c r="AY93" s="4"/>
+      <c r="AZ93" s="4"/>
+      <c r="BA93" s="4"/>
+    </row>
+    <row r="94" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
@@ -6250,8 +6722,12 @@
       <c r="AU94" s="4"/>
       <c r="AV94" s="4"/>
       <c r="AW94" s="4"/>
-    </row>
-    <row r="95" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX94" s="4"/>
+      <c r="AY94" s="4"/>
+      <c r="AZ94" s="4"/>
+      <c r="BA94" s="4"/>
+    </row>
+    <row r="95" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -6299,8 +6775,12 @@
       <c r="AU95" s="4"/>
       <c r="AV95" s="4"/>
       <c r="AW95" s="4"/>
-    </row>
-    <row r="96" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX95" s="4"/>
+      <c r="AY95" s="4"/>
+      <c r="AZ95" s="4"/>
+      <c r="BA95" s="4"/>
+    </row>
+    <row r="96" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
@@ -6348,8 +6828,12 @@
       <c r="AU96" s="4"/>
       <c r="AV96" s="4"/>
       <c r="AW96" s="4"/>
-    </row>
-    <row r="97" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX96" s="4"/>
+      <c r="AY96" s="4"/>
+      <c r="AZ96" s="4"/>
+      <c r="BA96" s="4"/>
+    </row>
+    <row r="97" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -6397,8 +6881,12 @@
       <c r="AU97" s="4"/>
       <c r="AV97" s="4"/>
       <c r="AW97" s="4"/>
-    </row>
-    <row r="98" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX97" s="4"/>
+      <c r="AY97" s="4"/>
+      <c r="AZ97" s="4"/>
+      <c r="BA97" s="4"/>
+    </row>
+    <row r="98" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
@@ -6446,8 +6934,12 @@
       <c r="AU98" s="4"/>
       <c r="AV98" s="4"/>
       <c r="AW98" s="4"/>
-    </row>
-    <row r="99" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX98" s="4"/>
+      <c r="AY98" s="4"/>
+      <c r="AZ98" s="4"/>
+      <c r="BA98" s="4"/>
+    </row>
+    <row r="99" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
@@ -6495,8 +6987,12 @@
       <c r="AU99" s="4"/>
       <c r="AV99" s="4"/>
       <c r="AW99" s="4"/>
-    </row>
-    <row r="100" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX99" s="4"/>
+      <c r="AY99" s="4"/>
+      <c r="AZ99" s="4"/>
+      <c r="BA99" s="4"/>
+    </row>
+    <row r="100" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -6544,8 +7040,12 @@
       <c r="AU100" s="4"/>
       <c r="AV100" s="4"/>
       <c r="AW100" s="4"/>
-    </row>
-    <row r="101" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX100" s="4"/>
+      <c r="AY100" s="4"/>
+      <c r="AZ100" s="4"/>
+      <c r="BA100" s="4"/>
+    </row>
+    <row r="101" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -6593,8 +7093,12 @@
       <c r="AU101" s="4"/>
       <c r="AV101" s="4"/>
       <c r="AW101" s="4"/>
-    </row>
-    <row r="102" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX101" s="4"/>
+      <c r="AY101" s="4"/>
+      <c r="AZ101" s="4"/>
+      <c r="BA101" s="4"/>
+    </row>
+    <row r="102" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -6642,8 +7146,12 @@
       <c r="AU102" s="4"/>
       <c r="AV102" s="4"/>
       <c r="AW102" s="4"/>
-    </row>
-    <row r="103" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX102" s="4"/>
+      <c r="AY102" s="4"/>
+      <c r="AZ102" s="4"/>
+      <c r="BA102" s="4"/>
+    </row>
+    <row r="103" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -6691,8 +7199,12 @@
       <c r="AU103" s="4"/>
       <c r="AV103" s="4"/>
       <c r="AW103" s="4"/>
-    </row>
-    <row r="104" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX103" s="4"/>
+      <c r="AY103" s="4"/>
+      <c r="AZ103" s="4"/>
+      <c r="BA103" s="4"/>
+    </row>
+    <row r="104" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
@@ -6740,8 +7252,12 @@
       <c r="AU104" s="4"/>
       <c r="AV104" s="4"/>
       <c r="AW104" s="4"/>
-    </row>
-    <row r="105" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX104" s="4"/>
+      <c r="AY104" s="4"/>
+      <c r="AZ104" s="4"/>
+      <c r="BA104" s="4"/>
+    </row>
+    <row r="105" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
@@ -6789,8 +7305,12 @@
       <c r="AU105" s="4"/>
       <c r="AV105" s="4"/>
       <c r="AW105" s="4"/>
-    </row>
-    <row r="106" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX105" s="4"/>
+      <c r="AY105" s="4"/>
+      <c r="AZ105" s="4"/>
+      <c r="BA105" s="4"/>
+    </row>
+    <row r="106" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
@@ -6838,8 +7358,12 @@
       <c r="AU106" s="4"/>
       <c r="AV106" s="4"/>
       <c r="AW106" s="4"/>
-    </row>
-    <row r="107" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX106" s="4"/>
+      <c r="AY106" s="4"/>
+      <c r="AZ106" s="4"/>
+      <c r="BA106" s="4"/>
+    </row>
+    <row r="107" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
@@ -6887,8 +7411,12 @@
       <c r="AU107" s="4"/>
       <c r="AV107" s="4"/>
       <c r="AW107" s="4"/>
-    </row>
-    <row r="108" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX107" s="4"/>
+      <c r="AY107" s="4"/>
+      <c r="AZ107" s="4"/>
+      <c r="BA107" s="4"/>
+    </row>
+    <row r="108" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
@@ -6936,8 +7464,12 @@
       <c r="AU108" s="4"/>
       <c r="AV108" s="4"/>
       <c r="AW108" s="4"/>
-    </row>
-    <row r="109" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX108" s="4"/>
+      <c r="AY108" s="4"/>
+      <c r="AZ108" s="4"/>
+      <c r="BA108" s="4"/>
+    </row>
+    <row r="109" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
@@ -6985,8 +7517,12 @@
       <c r="AU109" s="4"/>
       <c r="AV109" s="4"/>
       <c r="AW109" s="4"/>
-    </row>
-    <row r="110" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX109" s="4"/>
+      <c r="AY109" s="4"/>
+      <c r="AZ109" s="4"/>
+      <c r="BA109" s="4"/>
+    </row>
+    <row r="110" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
@@ -7034,8 +7570,12 @@
       <c r="AU110" s="4"/>
       <c r="AV110" s="4"/>
       <c r="AW110" s="4"/>
-    </row>
-    <row r="111" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX110" s="4"/>
+      <c r="AY110" s="4"/>
+      <c r="AZ110" s="4"/>
+      <c r="BA110" s="4"/>
+    </row>
+    <row r="111" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
@@ -7083,8 +7623,12 @@
       <c r="AU111" s="4"/>
       <c r="AV111" s="4"/>
       <c r="AW111" s="4"/>
-    </row>
-    <row r="112" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX111" s="4"/>
+      <c r="AY111" s="4"/>
+      <c r="AZ111" s="4"/>
+      <c r="BA111" s="4"/>
+    </row>
+    <row r="112" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
@@ -7132,8 +7676,12 @@
       <c r="AU112" s="4"/>
       <c r="AV112" s="4"/>
       <c r="AW112" s="4"/>
-    </row>
-    <row r="113" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX112" s="4"/>
+      <c r="AY112" s="4"/>
+      <c r="AZ112" s="4"/>
+      <c r="BA112" s="4"/>
+    </row>
+    <row r="113" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
@@ -7181,8 +7729,12 @@
       <c r="AU113" s="4"/>
       <c r="AV113" s="4"/>
       <c r="AW113" s="4"/>
-    </row>
-    <row r="114" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX113" s="4"/>
+      <c r="AY113" s="4"/>
+      <c r="AZ113" s="4"/>
+      <c r="BA113" s="4"/>
+    </row>
+    <row r="114" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
@@ -7230,8 +7782,12 @@
       <c r="AU114" s="4"/>
       <c r="AV114" s="4"/>
       <c r="AW114" s="4"/>
-    </row>
-    <row r="115" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX114" s="4"/>
+      <c r="AY114" s="4"/>
+      <c r="AZ114" s="4"/>
+      <c r="BA114" s="4"/>
+    </row>
+    <row r="115" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
@@ -7279,8 +7835,12 @@
       <c r="AU115" s="4"/>
       <c r="AV115" s="4"/>
       <c r="AW115" s="4"/>
-    </row>
-    <row r="116" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX115" s="4"/>
+      <c r="AY115" s="4"/>
+      <c r="AZ115" s="4"/>
+      <c r="BA115" s="4"/>
+    </row>
+    <row r="116" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
@@ -7328,8 +7888,12 @@
       <c r="AU116" s="4"/>
       <c r="AV116" s="4"/>
       <c r="AW116" s="4"/>
-    </row>
-    <row r="117" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX116" s="4"/>
+      <c r="AY116" s="4"/>
+      <c r="AZ116" s="4"/>
+      <c r="BA116" s="4"/>
+    </row>
+    <row r="117" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
@@ -7377,8 +7941,12 @@
       <c r="AU117" s="4"/>
       <c r="AV117" s="4"/>
       <c r="AW117" s="4"/>
-    </row>
-    <row r="118" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX117" s="4"/>
+      <c r="AY117" s="4"/>
+      <c r="AZ117" s="4"/>
+      <c r="BA117" s="4"/>
+    </row>
+    <row r="118" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
@@ -7426,8 +7994,12 @@
       <c r="AU118" s="4"/>
       <c r="AV118" s="4"/>
       <c r="AW118" s="4"/>
-    </row>
-    <row r="119" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX118" s="4"/>
+      <c r="AY118" s="4"/>
+      <c r="AZ118" s="4"/>
+      <c r="BA118" s="4"/>
+    </row>
+    <row r="119" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
@@ -7475,8 +8047,12 @@
       <c r="AU119" s="4"/>
       <c r="AV119" s="4"/>
       <c r="AW119" s="4"/>
-    </row>
-    <row r="120" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX119" s="4"/>
+      <c r="AY119" s="4"/>
+      <c r="AZ119" s="4"/>
+      <c r="BA119" s="4"/>
+    </row>
+    <row r="120" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
@@ -7524,8 +8100,12 @@
       <c r="AU120" s="4"/>
       <c r="AV120" s="4"/>
       <c r="AW120" s="4"/>
-    </row>
-    <row r="121" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX120" s="4"/>
+      <c r="AY120" s="4"/>
+      <c r="AZ120" s="4"/>
+      <c r="BA120" s="4"/>
+    </row>
+    <row r="121" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
@@ -7573,8 +8153,12 @@
       <c r="AU121" s="4"/>
       <c r="AV121" s="4"/>
       <c r="AW121" s="4"/>
-    </row>
-    <row r="122" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX121" s="4"/>
+      <c r="AY121" s="4"/>
+      <c r="AZ121" s="4"/>
+      <c r="BA121" s="4"/>
+    </row>
+    <row r="122" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
@@ -7622,8 +8206,12 @@
       <c r="AU122" s="4"/>
       <c r="AV122" s="4"/>
       <c r="AW122" s="4"/>
-    </row>
-    <row r="123" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX122" s="4"/>
+      <c r="AY122" s="4"/>
+      <c r="AZ122" s="4"/>
+      <c r="BA122" s="4"/>
+    </row>
+    <row r="123" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
@@ -7671,8 +8259,12 @@
       <c r="AU123" s="4"/>
       <c r="AV123" s="4"/>
       <c r="AW123" s="4"/>
-    </row>
-    <row r="124" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX123" s="4"/>
+      <c r="AY123" s="4"/>
+      <c r="AZ123" s="4"/>
+      <c r="BA123" s="4"/>
+    </row>
+    <row r="124" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
@@ -7720,8 +8312,12 @@
       <c r="AU124" s="4"/>
       <c r="AV124" s="4"/>
       <c r="AW124" s="4"/>
-    </row>
-    <row r="125" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX124" s="4"/>
+      <c r="AY124" s="4"/>
+      <c r="AZ124" s="4"/>
+      <c r="BA124" s="4"/>
+    </row>
+    <row r="125" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
@@ -7769,8 +8365,12 @@
       <c r="AU125" s="4"/>
       <c r="AV125" s="4"/>
       <c r="AW125" s="4"/>
-    </row>
-    <row r="126" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX125" s="4"/>
+      <c r="AY125" s="4"/>
+      <c r="AZ125" s="4"/>
+      <c r="BA125" s="4"/>
+    </row>
+    <row r="126" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
@@ -7818,8 +8418,12 @@
       <c r="AU126" s="4"/>
       <c r="AV126" s="4"/>
       <c r="AW126" s="4"/>
-    </row>
-    <row r="127" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX126" s="4"/>
+      <c r="AY126" s="4"/>
+      <c r="AZ126" s="4"/>
+      <c r="BA126" s="4"/>
+    </row>
+    <row r="127" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
@@ -7867,8 +8471,12 @@
       <c r="AU127" s="4"/>
       <c r="AV127" s="4"/>
       <c r="AW127" s="4"/>
-    </row>
-    <row r="128" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX127" s="4"/>
+      <c r="AY127" s="4"/>
+      <c r="AZ127" s="4"/>
+      <c r="BA127" s="4"/>
+    </row>
+    <row r="128" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
@@ -7916,8 +8524,12 @@
       <c r="AU128" s="4"/>
       <c r="AV128" s="4"/>
       <c r="AW128" s="4"/>
-    </row>
-    <row r="129" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX128" s="4"/>
+      <c r="AY128" s="4"/>
+      <c r="AZ128" s="4"/>
+      <c r="BA128" s="4"/>
+    </row>
+    <row r="129" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
@@ -7965,8 +8577,12 @@
       <c r="AU129" s="4"/>
       <c r="AV129" s="4"/>
       <c r="AW129" s="4"/>
-    </row>
-    <row r="130" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX129" s="4"/>
+      <c r="AY129" s="4"/>
+      <c r="AZ129" s="4"/>
+      <c r="BA129" s="4"/>
+    </row>
+    <row r="130" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
@@ -8014,8 +8630,12 @@
       <c r="AU130" s="4"/>
       <c r="AV130" s="4"/>
       <c r="AW130" s="4"/>
-    </row>
-    <row r="131" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX130" s="4"/>
+      <c r="AY130" s="4"/>
+      <c r="AZ130" s="4"/>
+      <c r="BA130" s="4"/>
+    </row>
+    <row r="131" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
@@ -8063,8 +8683,12 @@
       <c r="AU131" s="4"/>
       <c r="AV131" s="4"/>
       <c r="AW131" s="4"/>
-    </row>
-    <row r="132" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX131" s="4"/>
+      <c r="AY131" s="4"/>
+      <c r="AZ131" s="4"/>
+      <c r="BA131" s="4"/>
+    </row>
+    <row r="132" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
@@ -8112,8 +8736,12 @@
       <c r="AU132" s="4"/>
       <c r="AV132" s="4"/>
       <c r="AW132" s="4"/>
-    </row>
-    <row r="133" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX132" s="4"/>
+      <c r="AY132" s="4"/>
+      <c r="AZ132" s="4"/>
+      <c r="BA132" s="4"/>
+    </row>
+    <row r="133" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
@@ -8161,8 +8789,12 @@
       <c r="AU133" s="4"/>
       <c r="AV133" s="4"/>
       <c r="AW133" s="4"/>
-    </row>
-    <row r="134" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX133" s="4"/>
+      <c r="AY133" s="4"/>
+      <c r="AZ133" s="4"/>
+      <c r="BA133" s="4"/>
+    </row>
+    <row r="134" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
@@ -8210,8 +8842,12 @@
       <c r="AU134" s="4"/>
       <c r="AV134" s="4"/>
       <c r="AW134" s="4"/>
-    </row>
-    <row r="135" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX134" s="4"/>
+      <c r="AY134" s="4"/>
+      <c r="AZ134" s="4"/>
+      <c r="BA134" s="4"/>
+    </row>
+    <row r="135" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C135" s="4"/>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
@@ -8259,8 +8895,12 @@
       <c r="AU135" s="4"/>
       <c r="AV135" s="4"/>
       <c r="AW135" s="4"/>
-    </row>
-    <row r="136" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX135" s="4"/>
+      <c r="AY135" s="4"/>
+      <c r="AZ135" s="4"/>
+      <c r="BA135" s="4"/>
+    </row>
+    <row r="136" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C136" s="4"/>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
@@ -8308,8 +8948,12 @@
       <c r="AU136" s="4"/>
       <c r="AV136" s="4"/>
       <c r="AW136" s="4"/>
-    </row>
-    <row r="137" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX136" s="4"/>
+      <c r="AY136" s="4"/>
+      <c r="AZ136" s="4"/>
+      <c r="BA136" s="4"/>
+    </row>
+    <row r="137" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
@@ -8357,8 +9001,12 @@
       <c r="AU137" s="4"/>
       <c r="AV137" s="4"/>
       <c r="AW137" s="4"/>
-    </row>
-    <row r="138" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX137" s="4"/>
+      <c r="AY137" s="4"/>
+      <c r="AZ137" s="4"/>
+      <c r="BA137" s="4"/>
+    </row>
+    <row r="138" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
@@ -8406,8 +9054,12 @@
       <c r="AU138" s="4"/>
       <c r="AV138" s="4"/>
       <c r="AW138" s="4"/>
-    </row>
-    <row r="139" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX138" s="4"/>
+      <c r="AY138" s="4"/>
+      <c r="AZ138" s="4"/>
+      <c r="BA138" s="4"/>
+    </row>
+    <row r="139" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
@@ -8455,8 +9107,12 @@
       <c r="AU139" s="4"/>
       <c r="AV139" s="4"/>
       <c r="AW139" s="4"/>
-    </row>
-    <row r="140" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX139" s="4"/>
+      <c r="AY139" s="4"/>
+      <c r="AZ139" s="4"/>
+      <c r="BA139" s="4"/>
+    </row>
+    <row r="140" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C140" s="4"/>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
@@ -8504,8 +9160,12 @@
       <c r="AU140" s="4"/>
       <c r="AV140" s="4"/>
       <c r="AW140" s="4"/>
-    </row>
-    <row r="141" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX140" s="4"/>
+      <c r="AY140" s="4"/>
+      <c r="AZ140" s="4"/>
+      <c r="BA140" s="4"/>
+    </row>
+    <row r="141" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C141" s="4"/>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
@@ -8553,8 +9213,12 @@
       <c r="AU141" s="4"/>
       <c r="AV141" s="4"/>
       <c r="AW141" s="4"/>
-    </row>
-    <row r="142" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX141" s="4"/>
+      <c r="AY141" s="4"/>
+      <c r="AZ141" s="4"/>
+      <c r="BA141" s="4"/>
+    </row>
+    <row r="142" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C142" s="4"/>
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
@@ -8602,8 +9266,12 @@
       <c r="AU142" s="4"/>
       <c r="AV142" s="4"/>
       <c r="AW142" s="4"/>
-    </row>
-    <row r="143" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX142" s="4"/>
+      <c r="AY142" s="4"/>
+      <c r="AZ142" s="4"/>
+      <c r="BA142" s="4"/>
+    </row>
+    <row r="143" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
@@ -8651,8 +9319,12 @@
       <c r="AU143" s="4"/>
       <c r="AV143" s="4"/>
       <c r="AW143" s="4"/>
-    </row>
-    <row r="144" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX143" s="4"/>
+      <c r="AY143" s="4"/>
+      <c r="AZ143" s="4"/>
+      <c r="BA143" s="4"/>
+    </row>
+    <row r="144" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C144" s="4"/>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
@@ -8700,8 +9372,12 @@
       <c r="AU144" s="4"/>
       <c r="AV144" s="4"/>
       <c r="AW144" s="4"/>
-    </row>
-    <row r="145" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX144" s="4"/>
+      <c r="AY144" s="4"/>
+      <c r="AZ144" s="4"/>
+      <c r="BA144" s="4"/>
+    </row>
+    <row r="145" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
@@ -8749,8 +9425,12 @@
       <c r="AU145" s="4"/>
       <c r="AV145" s="4"/>
       <c r="AW145" s="4"/>
-    </row>
-    <row r="146" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX145" s="4"/>
+      <c r="AY145" s="4"/>
+      <c r="AZ145" s="4"/>
+      <c r="BA145" s="4"/>
+    </row>
+    <row r="146" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
@@ -8798,8 +9478,12 @@
       <c r="AU146" s="4"/>
       <c r="AV146" s="4"/>
       <c r="AW146" s="4"/>
-    </row>
-    <row r="147" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX146" s="4"/>
+      <c r="AY146" s="4"/>
+      <c r="AZ146" s="4"/>
+      <c r="BA146" s="4"/>
+    </row>
+    <row r="147" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
@@ -8847,8 +9531,12 @@
       <c r="AU147" s="4"/>
       <c r="AV147" s="4"/>
       <c r="AW147" s="4"/>
-    </row>
-    <row r="148" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX147" s="4"/>
+      <c r="AY147" s="4"/>
+      <c r="AZ147" s="4"/>
+      <c r="BA147" s="4"/>
+    </row>
+    <row r="148" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
@@ -8896,8 +9584,12 @@
       <c r="AU148" s="4"/>
       <c r="AV148" s="4"/>
       <c r="AW148" s="4"/>
-    </row>
-    <row r="149" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX148" s="4"/>
+      <c r="AY148" s="4"/>
+      <c r="AZ148" s="4"/>
+      <c r="BA148" s="4"/>
+    </row>
+    <row r="149" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
@@ -8945,8 +9637,12 @@
       <c r="AU149" s="4"/>
       <c r="AV149" s="4"/>
       <c r="AW149" s="4"/>
-    </row>
-    <row r="150" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX149" s="4"/>
+      <c r="AY149" s="4"/>
+      <c r="AZ149" s="4"/>
+      <c r="BA149" s="4"/>
+    </row>
+    <row r="150" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
@@ -8994,8 +9690,12 @@
       <c r="AU150" s="4"/>
       <c r="AV150" s="4"/>
       <c r="AW150" s="4"/>
-    </row>
-    <row r="151" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX150" s="4"/>
+      <c r="AY150" s="4"/>
+      <c r="AZ150" s="4"/>
+      <c r="BA150" s="4"/>
+    </row>
+    <row r="151" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
@@ -9043,8 +9743,12 @@
       <c r="AU151" s="4"/>
       <c r="AV151" s="4"/>
       <c r="AW151" s="4"/>
-    </row>
-    <row r="152" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX151" s="4"/>
+      <c r="AY151" s="4"/>
+      <c r="AZ151" s="4"/>
+      <c r="BA151" s="4"/>
+    </row>
+    <row r="152" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
@@ -9092,8 +9796,12 @@
       <c r="AU152" s="4"/>
       <c r="AV152" s="4"/>
       <c r="AW152" s="4"/>
-    </row>
-    <row r="153" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX152" s="4"/>
+      <c r="AY152" s="4"/>
+      <c r="AZ152" s="4"/>
+      <c r="BA152" s="4"/>
+    </row>
+    <row r="153" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
@@ -9141,8 +9849,12 @@
       <c r="AU153" s="4"/>
       <c r="AV153" s="4"/>
       <c r="AW153" s="4"/>
-    </row>
-    <row r="154" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX153" s="4"/>
+      <c r="AY153" s="4"/>
+      <c r="AZ153" s="4"/>
+      <c r="BA153" s="4"/>
+    </row>
+    <row r="154" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
@@ -9190,8 +9902,12 @@
       <c r="AU154" s="4"/>
       <c r="AV154" s="4"/>
       <c r="AW154" s="4"/>
-    </row>
-    <row r="155" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX154" s="4"/>
+      <c r="AY154" s="4"/>
+      <c r="AZ154" s="4"/>
+      <c r="BA154" s="4"/>
+    </row>
+    <row r="155" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
@@ -9239,8 +9955,12 @@
       <c r="AU155" s="4"/>
       <c r="AV155" s="4"/>
       <c r="AW155" s="4"/>
-    </row>
-    <row r="156" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX155" s="4"/>
+      <c r="AY155" s="4"/>
+      <c r="AZ155" s="4"/>
+      <c r="BA155" s="4"/>
+    </row>
+    <row r="156" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
@@ -9288,8 +10008,12 @@
       <c r="AU156" s="4"/>
       <c r="AV156" s="4"/>
       <c r="AW156" s="4"/>
-    </row>
-    <row r="157" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX156" s="4"/>
+      <c r="AY156" s="4"/>
+      <c r="AZ156" s="4"/>
+      <c r="BA156" s="4"/>
+    </row>
+    <row r="157" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
@@ -9337,8 +10061,12 @@
       <c r="AU157" s="4"/>
       <c r="AV157" s="4"/>
       <c r="AW157" s="4"/>
-    </row>
-    <row r="158" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX157" s="4"/>
+      <c r="AY157" s="4"/>
+      <c r="AZ157" s="4"/>
+      <c r="BA157" s="4"/>
+    </row>
+    <row r="158" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
@@ -9386,8 +10114,12 @@
       <c r="AU158" s="4"/>
       <c r="AV158" s="4"/>
       <c r="AW158" s="4"/>
-    </row>
-    <row r="159" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX158" s="4"/>
+      <c r="AY158" s="4"/>
+      <c r="AZ158" s="4"/>
+      <c r="BA158" s="4"/>
+    </row>
+    <row r="159" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
@@ -9435,8 +10167,12 @@
       <c r="AU159" s="4"/>
       <c r="AV159" s="4"/>
       <c r="AW159" s="4"/>
-    </row>
-    <row r="160" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX159" s="4"/>
+      <c r="AY159" s="4"/>
+      <c r="AZ159" s="4"/>
+      <c r="BA159" s="4"/>
+    </row>
+    <row r="160" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
@@ -9484,8 +10220,12 @@
       <c r="AU160" s="4"/>
       <c r="AV160" s="4"/>
       <c r="AW160" s="4"/>
-    </row>
-    <row r="161" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX160" s="4"/>
+      <c r="AY160" s="4"/>
+      <c r="AZ160" s="4"/>
+      <c r="BA160" s="4"/>
+    </row>
+    <row r="161" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
@@ -9533,8 +10273,12 @@
       <c r="AU161" s="4"/>
       <c r="AV161" s="4"/>
       <c r="AW161" s="4"/>
-    </row>
-    <row r="162" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX161" s="4"/>
+      <c r="AY161" s="4"/>
+      <c r="AZ161" s="4"/>
+      <c r="BA161" s="4"/>
+    </row>
+    <row r="162" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
@@ -9582,8 +10326,12 @@
       <c r="AU162" s="4"/>
       <c r="AV162" s="4"/>
       <c r="AW162" s="4"/>
-    </row>
-    <row r="163" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX162" s="4"/>
+      <c r="AY162" s="4"/>
+      <c r="AZ162" s="4"/>
+      <c r="BA162" s="4"/>
+    </row>
+    <row r="163" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
@@ -9631,8 +10379,12 @@
       <c r="AU163" s="4"/>
       <c r="AV163" s="4"/>
       <c r="AW163" s="4"/>
-    </row>
-    <row r="164" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX163" s="4"/>
+      <c r="AY163" s="4"/>
+      <c r="AZ163" s="4"/>
+      <c r="BA163" s="4"/>
+    </row>
+    <row r="164" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
@@ -9680,8 +10432,12 @@
       <c r="AU164" s="4"/>
       <c r="AV164" s="4"/>
       <c r="AW164" s="4"/>
-    </row>
-    <row r="165" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX164" s="4"/>
+      <c r="AY164" s="4"/>
+      <c r="AZ164" s="4"/>
+      <c r="BA164" s="4"/>
+    </row>
+    <row r="165" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
@@ -9729,8 +10485,12 @@
       <c r="AU165" s="4"/>
       <c r="AV165" s="4"/>
       <c r="AW165" s="4"/>
-    </row>
-    <row r="166" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX165" s="4"/>
+      <c r="AY165" s="4"/>
+      <c r="AZ165" s="4"/>
+      <c r="BA165" s="4"/>
+    </row>
+    <row r="166" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
@@ -9778,8 +10538,12 @@
       <c r="AU166" s="4"/>
       <c r="AV166" s="4"/>
       <c r="AW166" s="4"/>
-    </row>
-    <row r="167" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX166" s="4"/>
+      <c r="AY166" s="4"/>
+      <c r="AZ166" s="4"/>
+      <c r="BA166" s="4"/>
+    </row>
+    <row r="167" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
@@ -9827,8 +10591,12 @@
       <c r="AU167" s="4"/>
       <c r="AV167" s="4"/>
       <c r="AW167" s="4"/>
-    </row>
-    <row r="168" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX167" s="4"/>
+      <c r="AY167" s="4"/>
+      <c r="AZ167" s="4"/>
+      <c r="BA167" s="4"/>
+    </row>
+    <row r="168" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
@@ -9876,8 +10644,12 @@
       <c r="AU168" s="4"/>
       <c r="AV168" s="4"/>
       <c r="AW168" s="4"/>
-    </row>
-    <row r="169" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX168" s="4"/>
+      <c r="AY168" s="4"/>
+      <c r="AZ168" s="4"/>
+      <c r="BA168" s="4"/>
+    </row>
+    <row r="169" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
@@ -9925,8 +10697,12 @@
       <c r="AU169" s="4"/>
       <c r="AV169" s="4"/>
       <c r="AW169" s="4"/>
-    </row>
-    <row r="170" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX169" s="4"/>
+      <c r="AY169" s="4"/>
+      <c r="AZ169" s="4"/>
+      <c r="BA169" s="4"/>
+    </row>
+    <row r="170" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
@@ -9974,8 +10750,12 @@
       <c r="AU170" s="4"/>
       <c r="AV170" s="4"/>
       <c r="AW170" s="4"/>
-    </row>
-    <row r="171" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX170" s="4"/>
+      <c r="AY170" s="4"/>
+      <c r="AZ170" s="4"/>
+      <c r="BA170" s="4"/>
+    </row>
+    <row r="171" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
@@ -10023,8 +10803,12 @@
       <c r="AU171" s="4"/>
       <c r="AV171" s="4"/>
       <c r="AW171" s="4"/>
-    </row>
-    <row r="172" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX171" s="4"/>
+      <c r="AY171" s="4"/>
+      <c r="AZ171" s="4"/>
+      <c r="BA171" s="4"/>
+    </row>
+    <row r="172" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
@@ -10072,8 +10856,12 @@
       <c r="AU172" s="4"/>
       <c r="AV172" s="4"/>
       <c r="AW172" s="4"/>
-    </row>
-    <row r="173" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX172" s="4"/>
+      <c r="AY172" s="4"/>
+      <c r="AZ172" s="4"/>
+      <c r="BA172" s="4"/>
+    </row>
+    <row r="173" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
@@ -10121,8 +10909,12 @@
       <c r="AU173" s="4"/>
       <c r="AV173" s="4"/>
       <c r="AW173" s="4"/>
-    </row>
-    <row r="174" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX173" s="4"/>
+      <c r="AY173" s="4"/>
+      <c r="AZ173" s="4"/>
+      <c r="BA173" s="4"/>
+    </row>
+    <row r="174" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
@@ -10170,8 +10962,12 @@
       <c r="AU174" s="4"/>
       <c r="AV174" s="4"/>
       <c r="AW174" s="4"/>
-    </row>
-    <row r="175" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX174" s="4"/>
+      <c r="AY174" s="4"/>
+      <c r="AZ174" s="4"/>
+      <c r="BA174" s="4"/>
+    </row>
+    <row r="175" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
@@ -10219,8 +11015,12 @@
       <c r="AU175" s="4"/>
       <c r="AV175" s="4"/>
       <c r="AW175" s="4"/>
-    </row>
-    <row r="176" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX175" s="4"/>
+      <c r="AY175" s="4"/>
+      <c r="AZ175" s="4"/>
+      <c r="BA175" s="4"/>
+    </row>
+    <row r="176" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
@@ -10268,8 +11068,12 @@
       <c r="AU176" s="4"/>
       <c r="AV176" s="4"/>
       <c r="AW176" s="4"/>
-    </row>
-    <row r="177" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX176" s="4"/>
+      <c r="AY176" s="4"/>
+      <c r="AZ176" s="4"/>
+      <c r="BA176" s="4"/>
+    </row>
+    <row r="177" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
@@ -10317,8 +11121,12 @@
       <c r="AU177" s="4"/>
       <c r="AV177" s="4"/>
       <c r="AW177" s="4"/>
-    </row>
-    <row r="178" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX177" s="4"/>
+      <c r="AY177" s="4"/>
+      <c r="AZ177" s="4"/>
+      <c r="BA177" s="4"/>
+    </row>
+    <row r="178" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
@@ -10366,8 +11174,12 @@
       <c r="AU178" s="4"/>
       <c r="AV178" s="4"/>
       <c r="AW178" s="4"/>
-    </row>
-    <row r="179" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX178" s="4"/>
+      <c r="AY178" s="4"/>
+      <c r="AZ178" s="4"/>
+      <c r="BA178" s="4"/>
+    </row>
+    <row r="179" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
@@ -10415,8 +11227,12 @@
       <c r="AU179" s="4"/>
       <c r="AV179" s="4"/>
       <c r="AW179" s="4"/>
-    </row>
-    <row r="180" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX179" s="4"/>
+      <c r="AY179" s="4"/>
+      <c r="AZ179" s="4"/>
+      <c r="BA179" s="4"/>
+    </row>
+    <row r="180" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
@@ -10464,8 +11280,12 @@
       <c r="AU180" s="4"/>
       <c r="AV180" s="4"/>
       <c r="AW180" s="4"/>
-    </row>
-    <row r="181" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX180" s="4"/>
+      <c r="AY180" s="4"/>
+      <c r="AZ180" s="4"/>
+      <c r="BA180" s="4"/>
+    </row>
+    <row r="181" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
@@ -10513,8 +11333,12 @@
       <c r="AU181" s="4"/>
       <c r="AV181" s="4"/>
       <c r="AW181" s="4"/>
-    </row>
-    <row r="182" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX181" s="4"/>
+      <c r="AY181" s="4"/>
+      <c r="AZ181" s="4"/>
+      <c r="BA181" s="4"/>
+    </row>
+    <row r="182" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C182" s="4"/>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
@@ -10562,8 +11386,12 @@
       <c r="AU182" s="4"/>
       <c r="AV182" s="4"/>
       <c r="AW182" s="4"/>
-    </row>
-    <row r="183" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX182" s="4"/>
+      <c r="AY182" s="4"/>
+      <c r="AZ182" s="4"/>
+      <c r="BA182" s="4"/>
+    </row>
+    <row r="183" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
@@ -10611,8 +11439,12 @@
       <c r="AU183" s="4"/>
       <c r="AV183" s="4"/>
       <c r="AW183" s="4"/>
-    </row>
-    <row r="184" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX183" s="4"/>
+      <c r="AY183" s="4"/>
+      <c r="AZ183" s="4"/>
+      <c r="BA183" s="4"/>
+    </row>
+    <row r="184" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C184" s="4"/>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
@@ -10660,8 +11492,12 @@
       <c r="AU184" s="4"/>
       <c r="AV184" s="4"/>
       <c r="AW184" s="4"/>
-    </row>
-    <row r="185" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX184" s="4"/>
+      <c r="AY184" s="4"/>
+      <c r="AZ184" s="4"/>
+      <c r="BA184" s="4"/>
+    </row>
+    <row r="185" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C185" s="4"/>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
@@ -10709,8 +11545,12 @@
       <c r="AU185" s="4"/>
       <c r="AV185" s="4"/>
       <c r="AW185" s="4"/>
-    </row>
-    <row r="186" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX185" s="4"/>
+      <c r="AY185" s="4"/>
+      <c r="AZ185" s="4"/>
+      <c r="BA185" s="4"/>
+    </row>
+    <row r="186" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C186" s="4"/>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
@@ -10758,8 +11598,12 @@
       <c r="AU186" s="4"/>
       <c r="AV186" s="4"/>
       <c r="AW186" s="4"/>
-    </row>
-    <row r="187" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX186" s="4"/>
+      <c r="AY186" s="4"/>
+      <c r="AZ186" s="4"/>
+      <c r="BA186" s="4"/>
+    </row>
+    <row r="187" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -10807,8 +11651,12 @@
       <c r="AU187" s="4"/>
       <c r="AV187" s="4"/>
       <c r="AW187" s="4"/>
-    </row>
-    <row r="188" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX187" s="4"/>
+      <c r="AY187" s="4"/>
+      <c r="AZ187" s="4"/>
+      <c r="BA187" s="4"/>
+    </row>
+    <row r="188" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -10856,8 +11704,12 @@
       <c r="AU188" s="4"/>
       <c r="AV188" s="4"/>
       <c r="AW188" s="4"/>
-    </row>
-    <row r="189" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX188" s="4"/>
+      <c r="AY188" s="4"/>
+      <c r="AZ188" s="4"/>
+      <c r="BA188" s="4"/>
+    </row>
+    <row r="189" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
@@ -10905,8 +11757,12 @@
       <c r="AU189" s="4"/>
       <c r="AV189" s="4"/>
       <c r="AW189" s="4"/>
-    </row>
-    <row r="190" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX189" s="4"/>
+      <c r="AY189" s="4"/>
+      <c r="AZ189" s="4"/>
+      <c r="BA189" s="4"/>
+    </row>
+    <row r="190" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C190" s="4"/>
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
@@ -10954,8 +11810,12 @@
       <c r="AU190" s="4"/>
       <c r="AV190" s="4"/>
       <c r="AW190" s="4"/>
-    </row>
-    <row r="191" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX190" s="4"/>
+      <c r="AY190" s="4"/>
+      <c r="AZ190" s="4"/>
+      <c r="BA190" s="4"/>
+    </row>
+    <row r="191" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
@@ -11003,8 +11863,12 @@
       <c r="AU191" s="4"/>
       <c r="AV191" s="4"/>
       <c r="AW191" s="4"/>
-    </row>
-    <row r="192" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX191" s="4"/>
+      <c r="AY191" s="4"/>
+      <c r="AZ191" s="4"/>
+      <c r="BA191" s="4"/>
+    </row>
+    <row r="192" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
@@ -11052,8 +11916,12 @@
       <c r="AU192" s="4"/>
       <c r="AV192" s="4"/>
       <c r="AW192" s="4"/>
-    </row>
-    <row r="193" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX192" s="4"/>
+      <c r="AY192" s="4"/>
+      <c r="AZ192" s="4"/>
+      <c r="BA192" s="4"/>
+    </row>
+    <row r="193" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
@@ -11101,8 +11969,12 @@
       <c r="AU193" s="4"/>
       <c r="AV193" s="4"/>
       <c r="AW193" s="4"/>
-    </row>
-    <row r="194" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX193" s="4"/>
+      <c r="AY193" s="4"/>
+      <c r="AZ193" s="4"/>
+      <c r="BA193" s="4"/>
+    </row>
+    <row r="194" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C194" s="4"/>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
@@ -11150,8 +12022,12 @@
       <c r="AU194" s="4"/>
       <c r="AV194" s="4"/>
       <c r="AW194" s="4"/>
-    </row>
-    <row r="195" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX194" s="4"/>
+      <c r="AY194" s="4"/>
+      <c r="AZ194" s="4"/>
+      <c r="BA194" s="4"/>
+    </row>
+    <row r="195" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C195" s="4"/>
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
@@ -11199,8 +12075,12 @@
       <c r="AU195" s="4"/>
       <c r="AV195" s="4"/>
       <c r="AW195" s="4"/>
-    </row>
-    <row r="196" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX195" s="4"/>
+      <c r="AY195" s="4"/>
+      <c r="AZ195" s="4"/>
+      <c r="BA195" s="4"/>
+    </row>
+    <row r="196" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
@@ -11248,8 +12128,12 @@
       <c r="AU196" s="4"/>
       <c r="AV196" s="4"/>
       <c r="AW196" s="4"/>
-    </row>
-    <row r="197" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX196" s="4"/>
+      <c r="AY196" s="4"/>
+      <c r="AZ196" s="4"/>
+      <c r="BA196" s="4"/>
+    </row>
+    <row r="197" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C197" s="4"/>
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
@@ -11297,8 +12181,12 @@
       <c r="AU197" s="4"/>
       <c r="AV197" s="4"/>
       <c r="AW197" s="4"/>
-    </row>
-    <row r="198" spans="3:49" x14ac:dyDescent="0.2">
+      <c r="AX197" s="4"/>
+      <c r="AY197" s="4"/>
+      <c r="AZ197" s="4"/>
+      <c r="BA197" s="4"/>
+    </row>
+    <row r="198" spans="3:53" x14ac:dyDescent="0.2">
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
@@ -11346,6 +12234,116 @@
       <c r="AU198" s="4"/>
       <c r="AV198" s="4"/>
       <c r="AW198" s="4"/>
+      <c r="AX198" s="4"/>
+      <c r="AY198" s="4"/>
+      <c r="AZ198" s="4"/>
+      <c r="BA198" s="4"/>
+    </row>
+    <row r="199" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="C199" s="4"/>
+      <c r="D199" s="4"/>
+      <c r="E199" s="4"/>
+      <c r="F199" s="4"/>
+      <c r="G199" s="4"/>
+      <c r="H199" s="4"/>
+      <c r="I199" s="4"/>
+      <c r="J199" s="4"/>
+      <c r="K199" s="4"/>
+      <c r="L199" s="4"/>
+      <c r="M199" s="4"/>
+      <c r="N199" s="4"/>
+      <c r="O199" s="4"/>
+      <c r="P199" s="4"/>
+      <c r="Q199" s="4"/>
+      <c r="R199" s="4"/>
+      <c r="S199" s="4"/>
+      <c r="T199" s="4"/>
+      <c r="U199" s="4"/>
+      <c r="V199" s="4"/>
+      <c r="W199" s="4"/>
+      <c r="X199" s="4"/>
+      <c r="Y199" s="4"/>
+      <c r="Z199" s="4"/>
+      <c r="AA199" s="4"/>
+      <c r="AB199" s="4"/>
+      <c r="AC199" s="4"/>
+      <c r="AD199" s="4"/>
+      <c r="AE199" s="4"/>
+      <c r="AF199" s="4"/>
+      <c r="AG199" s="4"/>
+      <c r="AH199" s="4"/>
+      <c r="AI199" s="4"/>
+      <c r="AJ199" s="4"/>
+      <c r="AK199" s="4"/>
+      <c r="AL199" s="4"/>
+      <c r="AM199" s="4"/>
+      <c r="AN199" s="4"/>
+      <c r="AO199" s="4"/>
+      <c r="AP199" s="4"/>
+      <c r="AQ199" s="4"/>
+      <c r="AR199" s="4"/>
+      <c r="AS199" s="4"/>
+      <c r="AT199" s="4"/>
+      <c r="AU199" s="4"/>
+      <c r="AV199" s="4"/>
+      <c r="AW199" s="4"/>
+      <c r="AX199" s="4"/>
+      <c r="AY199" s="4"/>
+      <c r="AZ199" s="4"/>
+      <c r="BA199" s="4"/>
+    </row>
+    <row r="200" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="C200" s="4"/>
+      <c r="D200" s="4"/>
+      <c r="E200" s="4"/>
+      <c r="F200" s="4"/>
+      <c r="G200" s="4"/>
+      <c r="H200" s="4"/>
+      <c r="I200" s="4"/>
+      <c r="J200" s="4"/>
+      <c r="K200" s="4"/>
+      <c r="L200" s="4"/>
+      <c r="M200" s="4"/>
+      <c r="N200" s="4"/>
+      <c r="O200" s="4"/>
+      <c r="P200" s="4"/>
+      <c r="Q200" s="4"/>
+      <c r="R200" s="4"/>
+      <c r="S200" s="4"/>
+      <c r="T200" s="4"/>
+      <c r="U200" s="4"/>
+      <c r="V200" s="4"/>
+      <c r="W200" s="4"/>
+      <c r="X200" s="4"/>
+      <c r="Y200" s="4"/>
+      <c r="Z200" s="4"/>
+      <c r="AA200" s="4"/>
+      <c r="AB200" s="4"/>
+      <c r="AC200" s="4"/>
+      <c r="AD200" s="4"/>
+      <c r="AE200" s="4"/>
+      <c r="AF200" s="4"/>
+      <c r="AG200" s="4"/>
+      <c r="AH200" s="4"/>
+      <c r="AI200" s="4"/>
+      <c r="AJ200" s="4"/>
+      <c r="AK200" s="4"/>
+      <c r="AL200" s="4"/>
+      <c r="AM200" s="4"/>
+      <c r="AN200" s="4"/>
+      <c r="AO200" s="4"/>
+      <c r="AP200" s="4"/>
+      <c r="AQ200" s="4"/>
+      <c r="AR200" s="4"/>
+      <c r="AS200" s="4"/>
+      <c r="AT200" s="4"/>
+      <c r="AU200" s="4"/>
+      <c r="AV200" s="4"/>
+      <c r="AW200" s="4"/>
+      <c r="AX200" s="4"/>
+      <c r="AY200" s="4"/>
+      <c r="AZ200" s="4"/>
+      <c r="BA200" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/TSM.xlsx
+++ b/TSM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEF3176-1C8C-4DBF-A54C-E7571332DABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DC2995-AEE2-4E43-B9DB-DA1A7ACCBE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{D45F948B-0237-4CD1-A538-BE8EB16D26F7}"/>
   </bookViews>
@@ -36,8 +36,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={31F13264-8860-40C3-B9B7-A601213B1A4E}</author>
+  </authors>
+  <commentList>
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{31F13264-8860-40C3-B9B7-A601213B1A4E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    In kpcs 12 inch-equiv</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="68">
   <si>
     <t>TSMC</t>
   </si>
@@ -239,6 +257,9 @@
   <si>
     <t>Wafer Shipments</t>
   </si>
+  <si>
+    <t>2nm</t>
+  </si>
 </sst>
 </file>
 
@@ -248,13 +269,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -317,6 +344,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -337,33 +370,37 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -385,6 +422,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Oscar Settje" id="{A9E0310D-62AC-480D-B3B6-1F400CE316BD}" userId="7ff36870b9739543" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -702,6 +745,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B3" dT="2026-07-18T09:54:57.89" personId="{A9E0310D-62AC-480D-B3B6-1F400CE316BD}" id="{31F13264-8860-40C3-B9B7-A601213B1A4E}">
+    <text>In kpcs 12 inch-equiv</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5707962-9660-4B8C-96C2-5E923C455073}">
   <dimension ref="A1:I12"/>
@@ -726,7 +777,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="3">
-        <v>2030</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -734,10 +785,10 @@
         <v>3</v>
       </c>
       <c r="H3" s="4">
-        <v>25931</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>62</v>
+        <v>25932</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -749,7 +800,7 @@
       </c>
       <c r="H4" s="4">
         <f>+H2*H3</f>
-        <v>52639930</v>
+        <v>59384280</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -760,11 +811,11 @@
         <v>5</v>
       </c>
       <c r="H5" s="4">
-        <f>3035637+347964</f>
-        <v>3383601</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>62</v>
+        <f>3134218+383795</f>
+        <v>3518013</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -772,11 +823,11 @@
         <v>6</v>
       </c>
       <c r="H6" s="4">
-        <f>156242+860026</f>
-        <v>1016268</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>62</v>
+        <f>167410+815037</f>
+        <v>982447</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -785,7 +836,7 @@
       </c>
       <c r="H7" s="4">
         <f>+H4-H5+H6</f>
-        <v>50272597</v>
+        <v>56848714</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -812,8 +863,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6249646-B538-4C8E-8557-B9FADF837D81}">
-  <dimension ref="A1:BA200"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6249646-B538-4C8E-8557-B9FADF837D81}">
+  <dimension ref="A1:BA201"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="2" customWidth="1"/>
@@ -926,7 +977,9 @@
       <c r="O3" s="8">
         <v>4174</v>
       </c>
-      <c r="P3" s="8"/>
+      <c r="P3" s="8">
+        <v>4336</v>
+      </c>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
@@ -960,6 +1013,7 @@
       <c r="AU3" s="8"/>
     </row>
     <row r="4" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="B4" s="18"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -1007,49 +1061,44 @@
       <c r="AU4" s="8"/>
     </row>
     <row r="5" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
-        <v>52</v>
+      <c r="B5" s="20" t="s">
+        <v>67</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
-      <c r="G5" s="16">
-        <f>9%*G15</f>
-        <v>53337.96</v>
-      </c>
-      <c r="H5" s="16">
-        <f>15%*H15</f>
-        <v>101026.5</v>
+      <c r="G5" s="8">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0</v>
       </c>
       <c r="I5" s="8">
-        <f>20%*I15</f>
-        <v>151938.4</v>
+        <v>0</v>
       </c>
       <c r="J5" s="8">
-        <f>26%*J15</f>
-        <v>225799.86000000002</v>
+        <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f>22%*K15</f>
-        <v>184635.88</v>
+        <v>0</v>
       </c>
       <c r="L5" s="8">
-        <v>224110.07999999999</v>
+        <v>0</v>
       </c>
       <c r="M5" s="8">
-        <f>23%*M15</f>
-        <v>227681.14</v>
+        <v>0</v>
       </c>
       <c r="N5" s="8">
-        <f>28%*N15</f>
-        <v>292905.2</v>
+        <v>0</v>
       </c>
       <c r="O5" s="8">
-        <f>25%*O15</f>
-        <v>283525.75</v>
-      </c>
-      <c r="P5" s="8"/>
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <f>3%*P16</f>
+        <v>38111.43</v>
+      </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
       <c r="S5" s="8"/>
@@ -1075,63 +1124,60 @@
       <c r="AM5" s="8"/>
       <c r="AN5" s="8"/>
       <c r="AO5" s="8"/>
-      <c r="AP5" s="4"/>
-      <c r="AQ5" s="4"/>
-      <c r="AR5" s="4"/>
-      <c r="AS5" s="4"/>
-      <c r="AT5" s="4"/>
-      <c r="AU5" s="4"/>
-      <c r="AV5" s="4"/>
-      <c r="AW5" s="4"/>
-      <c r="AX5" s="4"/>
-      <c r="AY5" s="4"/>
-      <c r="AZ5" s="4"/>
-      <c r="BA5" s="4"/>
+      <c r="AP5" s="8"/>
+      <c r="AQ5" s="8"/>
+      <c r="AR5" s="8"/>
+      <c r="AS5" s="8"/>
+      <c r="AT5" s="8"/>
+      <c r="AU5" s="8"/>
     </row>
     <row r="6" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="B6" s="9" t="s">
-        <v>51</v>
+      <c r="B6" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
-      <c r="G6" s="8">
-        <f>37%*G15</f>
-        <v>219278.28</v>
-      </c>
-      <c r="H6" s="8">
-        <f>35%*H15</f>
-        <v>235728.49999999997</v>
+      <c r="G6" s="16">
+        <f>9%*G16</f>
+        <v>53337.96</v>
+      </c>
+      <c r="H6" s="16">
+        <f>15%*H16</f>
+        <v>101026.5</v>
       </c>
       <c r="I6" s="8">
-        <f>32%*I15</f>
-        <v>243101.44</v>
+        <f>20%*I16</f>
+        <v>151938.4</v>
       </c>
       <c r="J6" s="8">
-        <f>34%*J15</f>
-        <v>295276.74000000005</v>
+        <f>26%*J16</f>
+        <v>225799.86000000002</v>
       </c>
       <c r="K6" s="8">
-        <f>36%*K15</f>
-        <v>302131.44</v>
+        <f>22%*K16</f>
+        <v>184635.88</v>
       </c>
       <c r="L6" s="8">
-        <v>336165.12</v>
+        <v>224110.07999999999</v>
       </c>
       <c r="M6" s="8">
-        <f>37%*M15</f>
-        <v>366269.66</v>
+        <f>23%*M16</f>
+        <v>227681.14</v>
       </c>
       <c r="N6" s="8">
-        <f>35%*N15</f>
-        <v>366131.5</v>
+        <f>28%*N16</f>
+        <v>292905.2</v>
       </c>
       <c r="O6" s="8">
-        <f>36%*O15</f>
-        <v>408277.07999999996</v>
-      </c>
-      <c r="P6" s="8"/>
+        <f>25%*O16</f>
+        <v>283525.75</v>
+      </c>
+      <c r="P6" s="8">
+        <f>30%*P16</f>
+        <v>381114.3</v>
+      </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
       <c r="S6" s="8"/>
@@ -1171,49 +1217,52 @@
       <c r="BA6" s="4"/>
     </row>
     <row r="7" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="B7" s="2" t="s">
-        <v>53</v>
+      <c r="B7" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8">
-        <f>19%*G15</f>
-        <v>112602.36</v>
+        <f>37%*G16</f>
+        <v>219278.28</v>
       </c>
       <c r="H7" s="8">
-        <f>17%*H15</f>
-        <v>114496.70000000001</v>
+        <f>35%*H16</f>
+        <v>235728.49999999997</v>
       </c>
       <c r="I7" s="8">
-        <f>17%*I15</f>
-        <v>129147.64000000001</v>
+        <f>32%*I16</f>
+        <v>243101.44</v>
       </c>
       <c r="J7" s="8">
-        <f>14%*J15</f>
-        <v>121584.54000000001</v>
+        <f>34%*J16</f>
+        <v>295276.74000000005</v>
       </c>
       <c r="K7" s="8">
-        <f>15%*K15</f>
-        <v>125888.09999999999</v>
+        <f>36%*K16</f>
+        <v>302131.44</v>
       </c>
       <c r="L7" s="8">
-        <v>130730.88000000002</v>
+        <v>336165.12</v>
       </c>
       <c r="M7" s="8">
-        <f>14%*M15</f>
-        <v>138588.52000000002</v>
+        <f>37%*M16</f>
+        <v>366269.66</v>
       </c>
       <c r="N7" s="8">
-        <f>14%*N15</f>
-        <v>146452.6</v>
+        <f>35%*N16</f>
+        <v>366131.5</v>
       </c>
       <c r="O7" s="8">
-        <f>13%*O15</f>
-        <v>147433.39000000001</v>
-      </c>
-      <c r="P7" s="8"/>
+        <f>36%*O16</f>
+        <v>408277.07999999996</v>
+      </c>
+      <c r="P7" s="8">
+        <f>33%*P16</f>
+        <v>419225.73000000004</v>
+      </c>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
@@ -1254,48 +1303,51 @@
     </row>
     <row r="8" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8">
-        <f>+G15-SUM(G5:G7)</f>
-        <v>207425.40000000002</v>
+        <f>19%*G16</f>
+        <v>112602.36</v>
       </c>
       <c r="H8" s="8">
-        <f>+H15-SUM(H5:H7)</f>
-        <v>222258.3</v>
+        <f>17%*H16</f>
+        <v>114496.70000000001</v>
       </c>
       <c r="I8" s="8">
-        <f>+I15-SUM(I5:I7)</f>
-        <v>235504.52000000002</v>
+        <f>17%*I16</f>
+        <v>129147.64000000001</v>
       </c>
       <c r="J8" s="8">
-        <f>+J15-SUM(J5:J7)</f>
-        <v>225799.85999999987</v>
+        <f>14%*J16</f>
+        <v>121584.54000000001</v>
       </c>
       <c r="K8" s="8">
-        <f>+K15-SUM(K5:K7)</f>
-        <v>226598.57999999996</v>
+        <f>15%*K16</f>
+        <v>125888.09999999999</v>
       </c>
       <c r="L8" s="8">
-        <v>242785.92000000004</v>
+        <v>130730.88000000002</v>
       </c>
       <c r="M8" s="8">
-        <f>+M15-SUM(M5:M7)</f>
-        <v>257378.67999999993</v>
+        <f>14%*M16</f>
+        <v>138588.52000000002</v>
       </c>
       <c r="N8" s="8">
-        <f>+N15-SUM(N5:N7)</f>
-        <v>240600.70000000007</v>
+        <f>14%*N16</f>
+        <v>146452.6</v>
       </c>
       <c r="O8" s="8">
-        <f>+O15-SUM(O5:O7)</f>
-        <v>294866.78000000003</v>
-      </c>
-      <c r="P8" s="8"/>
+        <f>13%*O16</f>
+        <v>147433.39000000001</v>
+      </c>
+      <c r="P8" s="8">
+        <f>11%*P16</f>
+        <v>139741.91</v>
+      </c>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
       <c r="S8" s="8"/>
@@ -1336,48 +1388,51 @@
     </row>
     <row r="9" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8">
-        <f>46%*G15</f>
-        <v>272616.24</v>
+        <f>+G16-SUM(G6:G8)</f>
+        <v>207425.40000000002</v>
       </c>
       <c r="H9" s="8">
-        <f>52%*H15</f>
-        <v>350225.2</v>
+        <f>+H16-SUM(H6:H8)</f>
+        <v>222258.3</v>
       </c>
       <c r="I9" s="8">
-        <f>51%*I15</f>
-        <v>387442.92</v>
+        <f>+I16-SUM(I6:I8)</f>
+        <v>235504.52000000002</v>
       </c>
       <c r="J9" s="8">
-        <f>53%*J15</f>
-        <v>460284.33</v>
+        <f>+J16-SUM(J6:J8)</f>
+        <v>225799.85999999987</v>
       </c>
       <c r="K9" s="8">
-        <f>59%*K15</f>
-        <v>495159.86</v>
+        <f>+K16-SUM(K6:K8)</f>
+        <v>226598.57999999996</v>
       </c>
       <c r="L9" s="8">
-        <v>560275.19999999995</v>
+        <v>242785.92000000004</v>
       </c>
       <c r="M9" s="8">
-        <f>57%*M15</f>
-        <v>564253.26</v>
+        <f>+M16-SUM(M6:M8)</f>
+        <v>257378.67999999993</v>
       </c>
       <c r="N9" s="8">
-        <f>55%*N15</f>
-        <v>575349.5</v>
+        <f>+N16-SUM(N6:N8)</f>
+        <v>240600.70000000007</v>
       </c>
       <c r="O9" s="8">
-        <f>61%*O15</f>
-        <v>691802.83</v>
-      </c>
-      <c r="P9" s="8"/>
+        <f>+O16-SUM(O6:O8)</f>
+        <v>294866.78000000003</v>
+      </c>
+      <c r="P9" s="8">
+        <f>+P16-SUM(P5:P8)</f>
+        <v>292187.63</v>
+      </c>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
       <c r="S9" s="8"/>
@@ -1418,48 +1473,51 @@
     </row>
     <row r="10" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8">
-        <f>38%*G15</f>
-        <v>225204.72</v>
+        <f>46%*G16</f>
+        <v>272616.24</v>
       </c>
       <c r="H10" s="8">
-        <f>33%*H15</f>
-        <v>222258.30000000002</v>
+        <f>52%*H16</f>
+        <v>350225.2</v>
       </c>
       <c r="I10" s="8">
-        <f>34%*I15</f>
-        <v>258295.28000000003</v>
+        <f>51%*I16</f>
+        <v>387442.92</v>
       </c>
       <c r="J10" s="8">
-        <f>35%*J15</f>
-        <v>303961.34999999998</v>
+        <f>53%*J16</f>
+        <v>460284.33</v>
       </c>
       <c r="K10" s="8">
-        <f>28%*K15</f>
-        <v>234991.12000000002</v>
+        <f>59%*K16</f>
+        <v>495159.86</v>
       </c>
       <c r="L10" s="8">
-        <v>252123.84000000003</v>
+        <v>560275.19999999995</v>
       </c>
       <c r="M10" s="8">
-        <f>30%*M15</f>
-        <v>296975.39999999997</v>
+        <f>57%*M16</f>
+        <v>564253.26</v>
       </c>
       <c r="N10" s="8">
-        <f>32%*N15</f>
-        <v>334748.79999999999</v>
+        <f>55%*N16</f>
+        <v>575349.5</v>
       </c>
       <c r="O10" s="8">
-        <f>26%*O15</f>
-        <v>294866.78000000003</v>
-      </c>
-      <c r="P10" s="8"/>
+        <f>61%*O16</f>
+        <v>691802.83</v>
+      </c>
+      <c r="P10" s="8">
+        <f>66%*P16</f>
+        <v>838451.46000000008</v>
+      </c>
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
       <c r="S10" s="8"/>
@@ -1500,48 +1558,51 @@
     </row>
     <row r="11" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8">
-        <f>6%*G15</f>
-        <v>35558.639999999999</v>
+        <f>38%*G16</f>
+        <v>225204.72</v>
       </c>
       <c r="H11" s="8">
-        <f>6%*H15</f>
-        <v>40410.6</v>
+        <f>33%*H16</f>
+        <v>222258.30000000002</v>
       </c>
       <c r="I11" s="8">
-        <f>7%*I15</f>
-        <v>53178.44</v>
+        <f>34%*I16</f>
+        <v>258295.28000000003</v>
       </c>
       <c r="J11" s="8">
-        <f>5%*J15</f>
-        <v>43423.05</v>
+        <f>35%*J16</f>
+        <v>303961.34999999998</v>
       </c>
       <c r="K11" s="8">
-        <f>5%*K15</f>
-        <v>41962.700000000004</v>
+        <f>28%*K16</f>
+        <v>234991.12000000002</v>
       </c>
       <c r="L11" s="8">
-        <v>46689.600000000006</v>
+        <v>252123.84000000003</v>
       </c>
       <c r="M11" s="8">
-        <f>5%*M15</f>
-        <v>49495.9</v>
+        <f>30%*M16</f>
+        <v>296975.39999999997</v>
       </c>
       <c r="N11" s="8">
-        <f>5%*N15</f>
-        <v>52304.5</v>
+        <f>32%*N16</f>
+        <v>334748.79999999999</v>
       </c>
       <c r="O11" s="8">
-        <f>6%*O15</f>
-        <v>68046.179999999993</v>
-      </c>
-      <c r="P11" s="8"/>
+        <f>26%*O16</f>
+        <v>294866.78000000003</v>
+      </c>
+      <c r="P11" s="8">
+        <f>22%*P16</f>
+        <v>279483.82</v>
+      </c>
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
       <c r="S11" s="8"/>
@@ -1582,48 +1643,51 @@
     </row>
     <row r="12" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8">
-        <f>2%*G15</f>
-        <v>11852.880000000001</v>
+        <f>6%*G16</f>
+        <v>35558.639999999999</v>
       </c>
       <c r="H12" s="8">
-        <f>5%*H15</f>
-        <v>33675.5</v>
+        <f>6%*H16</f>
+        <v>40410.6</v>
       </c>
       <c r="I12" s="8">
-        <f>5%*I15</f>
-        <v>37984.6</v>
+        <f>7%*I16</f>
+        <v>53178.44</v>
       </c>
       <c r="J12" s="8">
-        <f>4%*J15</f>
-        <v>34738.44</v>
+        <f>5%*J16</f>
+        <v>43423.05</v>
       </c>
       <c r="K12" s="8">
-        <f>1%*K15</f>
-        <v>8392.5400000000009</v>
+        <f>5%*K16</f>
+        <v>41962.700000000004</v>
       </c>
       <c r="L12" s="8">
         <v>46689.600000000006</v>
       </c>
       <c r="M12" s="8">
-        <f>5%*M15</f>
+        <f>5%*M16</f>
         <v>49495.9</v>
       </c>
       <c r="N12" s="8">
-        <f>5%*N15</f>
+        <f>5%*N16</f>
         <v>52304.5</v>
       </c>
       <c r="O12" s="8">
-        <f>4%*O15</f>
-        <v>45364.12</v>
-      </c>
-      <c r="P12" s="8"/>
+        <f>6%*O16</f>
+        <v>68046.179999999993</v>
+      </c>
+      <c r="P12" s="8">
+        <f>5%*P16</f>
+        <v>63519.05</v>
+      </c>
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
       <c r="S12" s="8"/>
@@ -1664,48 +1728,51 @@
     </row>
     <row r="13" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8">
-        <f>2%*G15</f>
+        <f>2%*G16</f>
         <v>11852.880000000001</v>
       </c>
       <c r="H13" s="8">
-        <f>2%*H15</f>
-        <v>13470.2</v>
+        <f>5%*H16</f>
+        <v>33675.5</v>
       </c>
       <c r="I13" s="8">
-        <f>1%*I15</f>
-        <v>7596.92</v>
+        <f>5%*I16</f>
+        <v>37984.6</v>
       </c>
       <c r="J13" s="8">
-        <f>1%*J15</f>
-        <v>8684.61</v>
+        <f>4%*J16</f>
+        <v>34738.44</v>
       </c>
       <c r="K13" s="8">
-        <f>2%*K15</f>
-        <v>16785.080000000002</v>
+        <f>1%*K16</f>
+        <v>8392.5400000000009</v>
       </c>
       <c r="L13" s="8">
-        <v>9337.92</v>
+        <v>46689.600000000006</v>
       </c>
       <c r="M13" s="8">
-        <f>1%*M15</f>
-        <v>9899.18</v>
+        <f>5%*M16</f>
+        <v>49495.9</v>
       </c>
       <c r="N13" s="8">
-        <f>1%*N15</f>
-        <v>10460.9</v>
+        <f>5%*N16</f>
+        <v>52304.5</v>
       </c>
       <c r="O13" s="8">
-        <f>1%*O15</f>
-        <v>11341.03</v>
-      </c>
-      <c r="P13" s="8"/>
+        <f>4%*O16</f>
+        <v>45364.12</v>
+      </c>
+      <c r="P13" s="8">
+        <f>5%*P16</f>
+        <v>63519.05</v>
+      </c>
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
       <c r="S13" s="8"/>
@@ -1746,48 +1813,51 @@
     </row>
     <row r="14" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8">
-        <f>+G15-SUM(G9:G13)</f>
-        <v>35558.640000000014</v>
+        <f>2%*G16</f>
+        <v>11852.880000000001</v>
       </c>
       <c r="H14" s="8">
-        <f>2%*H15</f>
+        <f>2%*H16</f>
         <v>13470.2</v>
       </c>
       <c r="I14" s="8">
-        <f>2%*I15</f>
-        <v>15193.84</v>
+        <f>1%*I16</f>
+        <v>7596.92</v>
       </c>
       <c r="J14" s="8">
-        <f>2%*J15</f>
-        <v>17369.22</v>
+        <f>1%*J16</f>
+        <v>8684.61</v>
       </c>
       <c r="K14" s="8">
-        <f>+K15-SUM(K9:K13)</f>
-        <v>41962.70000000007</v>
+        <f>2%*K16</f>
+        <v>16785.080000000002</v>
       </c>
       <c r="L14" s="8">
-        <v>18675.84</v>
+        <v>9337.92</v>
       </c>
       <c r="M14" s="8">
-        <f>2%*M15</f>
-        <v>19798.36</v>
+        <f>1%*M16</f>
+        <v>9899.18</v>
       </c>
       <c r="N14" s="8">
-        <f>2%*N15</f>
-        <v>20921.8</v>
+        <f>1%*N16</f>
+        <v>10460.9</v>
       </c>
       <c r="O14" s="8">
-        <f>2%*O15</f>
-        <v>22682.06</v>
-      </c>
-      <c r="P14" s="8"/>
+        <f>1%*O16</f>
+        <v>11341.03</v>
+      </c>
+      <c r="P14" s="8">
+        <f>1%*P16</f>
+        <v>12703.81</v>
+      </c>
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
       <c r="S14" s="8"/>
@@ -1827,45 +1897,54 @@
       <c r="BA14" s="4"/>
     </row>
     <row r="15" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="B15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10">
-        <v>546733</v>
-      </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10">
-        <v>592644</v>
-      </c>
-      <c r="H15" s="10">
-        <v>673510</v>
-      </c>
-      <c r="I15" s="10">
-        <v>759692</v>
-      </c>
-      <c r="J15" s="10">
-        <v>868461</v>
-      </c>
-      <c r="K15" s="10">
-        <v>839254</v>
-      </c>
-      <c r="L15" s="10">
-        <v>933792</v>
-      </c>
-      <c r="M15" s="10">
-        <v>989918</v>
-      </c>
-      <c r="N15" s="10">
-        <v>1046090</v>
-      </c>
-      <c r="O15" s="10">
-        <v>1134103</v>
-      </c>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8">
+        <f>+G16-SUM(G10:G14)</f>
+        <v>35558.640000000014</v>
+      </c>
+      <c r="H15" s="8">
+        <f>2%*H16</f>
+        <v>13470.2</v>
+      </c>
+      <c r="I15" s="8">
+        <f>2%*I16</f>
+        <v>15193.84</v>
+      </c>
+      <c r="J15" s="8">
+        <f>2%*J16</f>
+        <v>17369.22</v>
+      </c>
+      <c r="K15" s="8">
+        <f>+K16-SUM(K10:K14)</f>
+        <v>41962.70000000007</v>
+      </c>
+      <c r="L15" s="8">
+        <v>18675.84</v>
+      </c>
+      <c r="M15" s="8">
+        <f>2%*M16</f>
+        <v>19798.36</v>
+      </c>
+      <c r="N15" s="8">
+        <f>2%*N16</f>
+        <v>20921.8</v>
+      </c>
+      <c r="O15" s="8">
+        <f>2%*O16</f>
+        <v>22682.06</v>
+      </c>
+      <c r="P15" s="8">
+        <f>2%*P16</f>
+        <v>25407.62</v>
+      </c>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
       <c r="S15" s="8"/>
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
@@ -1903,45 +1982,47 @@
       <c r="BA15" s="4"/>
     </row>
     <row r="16" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="B16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8">
-        <v>250090</v>
-      </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8">
-        <v>278139</v>
-      </c>
-      <c r="H16" s="8">
-        <v>315385</v>
-      </c>
-      <c r="I16" s="8">
-        <v>320347</v>
-      </c>
-      <c r="J16" s="8">
-        <v>356082</v>
-      </c>
-      <c r="K16" s="8">
-        <v>345859</v>
-      </c>
-      <c r="L16" s="8">
-        <v>386423</v>
-      </c>
-      <c r="M16" s="8">
-        <v>401375</v>
-      </c>
-      <c r="N16" s="8">
-        <v>394103</v>
-      </c>
-      <c r="O16" s="8">
-        <v>382808</v>
-      </c>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
+      <c r="B16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10">
+        <v>546733</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10">
+        <v>592644</v>
+      </c>
+      <c r="H16" s="10">
+        <v>673510</v>
+      </c>
+      <c r="I16" s="10">
+        <v>759692</v>
+      </c>
+      <c r="J16" s="10">
+        <v>868461</v>
+      </c>
+      <c r="K16" s="10">
+        <v>839254</v>
+      </c>
+      <c r="L16" s="10">
+        <v>933792</v>
+      </c>
+      <c r="M16" s="10">
+        <v>989918</v>
+      </c>
+      <c r="N16" s="10">
+        <v>1046090</v>
+      </c>
+      <c r="O16" s="10">
+        <v>1134103</v>
+      </c>
+      <c r="P16" s="10">
+        <v>1270381</v>
+      </c>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
       <c r="S16" s="8"/>
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
@@ -1980,61 +2061,44 @@
     </row>
     <row r="17" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="8">
-        <f t="shared" ref="C17:H17" si="0">+C15-C16</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="8">
-        <f t="shared" si="0"/>
-        <v>296643</v>
-      </c>
-      <c r="F17" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+        <v>250090</v>
+      </c>
+      <c r="F17" s="8"/>
       <c r="G17" s="8">
-        <f t="shared" si="0"/>
-        <v>314505</v>
+        <v>278139</v>
       </c>
       <c r="H17" s="8">
-        <f t="shared" si="0"/>
-        <v>358125</v>
+        <v>315385</v>
       </c>
       <c r="I17" s="8">
-        <f>+I15-I16</f>
-        <v>439345</v>
+        <v>320347</v>
       </c>
       <c r="J17" s="8">
-        <f t="shared" ref="J17:O17" si="1">+J15-J16</f>
-        <v>512379</v>
+        <v>356082</v>
       </c>
       <c r="K17" s="8">
-        <f t="shared" si="1"/>
-        <v>493395</v>
+        <v>345859</v>
       </c>
       <c r="L17" s="8">
-        <f t="shared" si="1"/>
-        <v>547369</v>
+        <v>386423</v>
       </c>
       <c r="M17" s="8">
-        <f t="shared" si="1"/>
-        <v>588543</v>
+        <v>401375</v>
       </c>
       <c r="N17" s="8">
-        <f t="shared" si="1"/>
-        <v>651987</v>
+        <v>394103</v>
       </c>
       <c r="O17" s="8">
-        <f t="shared" si="1"/>
-        <v>751295</v>
-      </c>
-      <c r="P17" s="8"/>
+        <v>382808</v>
+      </c>
+      <c r="P17" s="8">
+        <v>410070</v>
+      </c>
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
       <c r="S17" s="8"/>
@@ -2075,42 +2139,64 @@
     </row>
     <row r="18" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
+        <v>20</v>
+      </c>
+      <c r="C18" s="8">
+        <f t="shared" ref="C18:H18" si="0">+C16-C17</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="E18" s="8">
-        <v>51138</v>
-      </c>
-      <c r="F18" s="8"/>
+        <f t="shared" si="0"/>
+        <v>296643</v>
+      </c>
+      <c r="F18" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="G18" s="8">
-        <v>46109</v>
+        <f t="shared" si="0"/>
+        <v>314505</v>
       </c>
       <c r="H18" s="8">
-        <v>48058</v>
+        <f t="shared" si="0"/>
+        <v>358125</v>
       </c>
       <c r="I18" s="8">
-        <v>52783</v>
+        <f>+I16-I17</f>
+        <v>439345</v>
       </c>
       <c r="J18" s="8">
-        <v>57232</v>
+        <f t="shared" ref="J18:P18" si="1">+J16-J17</f>
+        <v>512379</v>
       </c>
       <c r="K18" s="8">
-        <v>56547</v>
+        <f t="shared" si="1"/>
+        <v>493395</v>
       </c>
       <c r="L18" s="8">
-        <v>61280</v>
+        <f t="shared" si="1"/>
+        <v>547369</v>
       </c>
       <c r="M18" s="8">
-        <v>63743</v>
+        <f t="shared" si="1"/>
+        <v>588543</v>
       </c>
       <c r="N18" s="8">
-        <v>64857</v>
+        <f t="shared" si="1"/>
+        <v>651987</v>
       </c>
       <c r="O18" s="8">
-        <v>67757</v>
-      </c>
-      <c r="P18" s="8"/>
+        <f t="shared" si="1"/>
+        <v>751295</v>
+      </c>
+      <c r="P18" s="8">
+        <f t="shared" si="1"/>
+        <v>860311</v>
+      </c>
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
       <c r="S18" s="8"/>
@@ -2151,42 +2237,44 @@
     </row>
     <row r="19" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8">
-        <v>17571</v>
+        <v>51138</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8">
-        <v>19248</v>
+        <v>46109</v>
       </c>
       <c r="H19" s="8">
-        <v>22238</v>
+        <v>48058</v>
       </c>
       <c r="I19" s="8">
-        <v>26295</v>
+        <v>52783</v>
       </c>
       <c r="J19" s="8">
-        <v>29108</v>
+        <v>57232</v>
       </c>
       <c r="K19" s="8">
-        <v>28639</v>
+        <v>56547</v>
       </c>
       <c r="L19" s="8">
-        <v>23228</v>
+        <v>61280</v>
       </c>
       <c r="M19" s="8">
-        <v>24022</v>
+        <v>63743</v>
       </c>
       <c r="N19" s="8">
-        <v>23333</v>
+        <v>64857</v>
       </c>
       <c r="O19" s="8">
-        <v>26249</v>
-      </c>
-      <c r="P19" s="8"/>
+        <v>67757</v>
+      </c>
+      <c r="P19" s="8">
+        <v>73146</v>
+      </c>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
       <c r="S19" s="8"/>
@@ -2227,42 +2315,44 @@
     </row>
     <row r="20" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8">
-        <v>131</v>
+        <v>17571</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8">
-        <v>-130</v>
+        <v>19248</v>
       </c>
       <c r="H20" s="8">
-        <v>-1273</v>
+        <v>22238</v>
       </c>
       <c r="I20" s="8">
-        <v>499</v>
+        <v>26295</v>
       </c>
       <c r="J20" s="8">
-        <v>-326</v>
+        <v>29108</v>
       </c>
       <c r="K20" s="8">
-        <v>-1128</v>
+        <v>28639</v>
       </c>
       <c r="L20" s="8">
-        <v>562</v>
+        <v>23228</v>
       </c>
       <c r="M20" s="8">
-        <v>-93</v>
+        <v>24022</v>
       </c>
       <c r="N20" s="8">
-        <v>1106</v>
+        <v>23333</v>
       </c>
       <c r="O20" s="8">
-        <v>1677</v>
-      </c>
-      <c r="P20" s="8"/>
+        <v>26249</v>
+      </c>
+      <c r="P20" s="8">
+        <v>25836</v>
+      </c>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
       <c r="S20" s="8"/>
@@ -2303,61 +2393,44 @@
     </row>
     <row r="21" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="8">
-        <f t="shared" ref="C21:G21" si="2">+C17-SUM(C18:C19)+C20</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
       <c r="E21" s="8">
-        <f t="shared" si="2"/>
-        <v>228065</v>
-      </c>
-      <c r="F21" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="F21" s="8"/>
       <c r="G21" s="8">
-        <f t="shared" si="2"/>
-        <v>249018</v>
+        <v>-130</v>
       </c>
       <c r="H21" s="8">
-        <f>+H17-SUM(H18:H19)+H20</f>
-        <v>286556</v>
+        <v>-1273</v>
       </c>
       <c r="I21" s="8">
-        <f>+I17-SUM(I18:I19)+I20</f>
-        <v>360766</v>
+        <v>499</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" ref="J21:O21" si="3">+J17-SUM(J18:J19)+J20</f>
-        <v>425713</v>
+        <v>-326</v>
       </c>
       <c r="K21" s="8">
-        <f t="shared" si="3"/>
-        <v>407081</v>
+        <v>-1128</v>
       </c>
       <c r="L21" s="8">
-        <f t="shared" si="3"/>
-        <v>463423</v>
+        <v>562</v>
       </c>
       <c r="M21" s="8">
-        <f t="shared" si="3"/>
-        <v>500685</v>
+        <v>-93</v>
       </c>
       <c r="N21" s="8">
-        <f t="shared" si="3"/>
-        <v>564903</v>
+        <v>1106</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" si="3"/>
-        <v>658966</v>
-      </c>
-      <c r="P21" s="8"/>
+        <v>1677</v>
+      </c>
+      <c r="P21" s="8">
+        <v>5274</v>
+      </c>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
       <c r="S21" s="8"/>
@@ -2398,42 +2471,64 @@
     </row>
     <row r="22" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
+        <v>23</v>
+      </c>
+      <c r="C22" s="8">
+        <f t="shared" ref="C22:G22" si="2">+C18-SUM(C19:C20)+C21</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="E22" s="8">
-        <v>1167</v>
-      </c>
-      <c r="F22" s="8"/>
+        <f t="shared" si="2"/>
+        <v>228065</v>
+      </c>
+      <c r="F22" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G22" s="8">
-        <v>878</v>
+        <f t="shared" si="2"/>
+        <v>249018</v>
       </c>
       <c r="H22" s="8">
-        <v>1152</v>
+        <f>+H18-SUM(H19:H20)+H21</f>
+        <v>286556</v>
       </c>
       <c r="I22" s="8">
-        <v>1561</v>
+        <f>+I18-SUM(I19:I20)+I21</f>
+        <v>360766</v>
       </c>
       <c r="J22" s="8">
-        <v>289</v>
+        <f t="shared" ref="J22:P22" si="3">+J18-SUM(J19:J20)+J21</f>
+        <v>425713</v>
       </c>
       <c r="K22" s="8">
-        <v>1368</v>
+        <f t="shared" si="3"/>
+        <v>407081</v>
       </c>
       <c r="L22" s="8">
-        <v>1222</v>
+        <f t="shared" si="3"/>
+        <v>463423</v>
       </c>
       <c r="M22" s="8">
-        <v>1424</v>
+        <f t="shared" si="3"/>
+        <v>500685</v>
       </c>
       <c r="N22" s="8">
-        <v>1483</v>
+        <f t="shared" si="3"/>
+        <v>564903</v>
       </c>
       <c r="O22" s="8">
-        <v>1685</v>
-      </c>
-      <c r="P22" s="8"/>
+        <f t="shared" si="3"/>
+        <v>658966</v>
+      </c>
+      <c r="P22" s="8">
+        <f t="shared" si="3"/>
+        <v>766603</v>
+      </c>
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
       <c r="S22" s="8"/>
@@ -2474,42 +2569,44 @@
     </row>
     <row r="23" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8">
-        <v>12483</v>
+        <v>1167</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="8">
-        <v>16661</v>
+        <v>878</v>
       </c>
       <c r="H23" s="8">
-        <v>18341</v>
+        <v>1152</v>
       </c>
       <c r="I23" s="8">
-        <v>19966</v>
+        <v>1561</v>
       </c>
       <c r="J23" s="8">
-        <v>21750</v>
+        <v>289</v>
       </c>
       <c r="K23" s="8">
-        <v>22182</v>
+        <v>1368</v>
       </c>
       <c r="L23" s="8">
-        <v>21501</v>
+        <v>1222</v>
       </c>
       <c r="M23" s="8">
-        <v>23222</v>
+        <v>1424</v>
       </c>
       <c r="N23" s="8">
-        <v>26463</v>
+        <v>1483</v>
       </c>
       <c r="O23" s="8">
-        <v>26146</v>
-      </c>
-      <c r="P23" s="8"/>
+        <v>1685</v>
+      </c>
+      <c r="P23" s="8">
+        <v>1438</v>
+      </c>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
       <c r="S23" s="8"/>
@@ -2550,42 +2647,44 @@
     </row>
     <row r="24" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8">
-        <v>225</v>
+        <v>12483</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8">
-        <v>-14</v>
+        <v>16661</v>
       </c>
       <c r="H24" s="8">
-        <v>262</v>
+        <v>18341</v>
       </c>
       <c r="I24" s="8">
-        <v>1894</v>
+        <v>19966</v>
       </c>
       <c r="J24" s="8">
-        <v>46</v>
+        <v>21750</v>
       </c>
       <c r="K24" s="8">
-        <v>264</v>
+        <v>22182</v>
       </c>
       <c r="L24" s="8">
-        <v>6890</v>
+        <v>21501</v>
       </c>
       <c r="M24" s="8">
-        <v>39</v>
+        <v>23222</v>
       </c>
       <c r="N24" s="8">
-        <v>-486</v>
+        <v>26463</v>
       </c>
       <c r="O24" s="8">
-        <v>1003</v>
-      </c>
-      <c r="P24" s="8"/>
+        <v>26146</v>
+      </c>
+      <c r="P24" s="8">
+        <v>26959</v>
+      </c>
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
       <c r="S24" s="8"/>
@@ -2626,61 +2725,44 @@
     </row>
     <row r="25" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="8">
-        <f t="shared" ref="C25:G25" si="4">+C21+SUM(C22:C24)</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="8">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
       <c r="E25" s="8">
-        <f t="shared" si="4"/>
-        <v>241940</v>
-      </c>
-      <c r="F25" s="8">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="F25" s="8"/>
       <c r="G25" s="8">
-        <f t="shared" si="4"/>
-        <v>266543</v>
+        <v>-14</v>
       </c>
       <c r="H25" s="8">
-        <f>+H21+SUM(H22:H24)</f>
-        <v>306311</v>
+        <v>262</v>
       </c>
       <c r="I25" s="8">
-        <f t="shared" ref="I25:O25" si="5">+I21+SUM(I22:I24)</f>
-        <v>384187</v>
+        <v>1894</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" si="5"/>
-        <v>447798</v>
+        <v>46</v>
       </c>
       <c r="K25" s="8">
-        <f t="shared" si="5"/>
-        <v>430895</v>
+        <v>264</v>
       </c>
       <c r="L25" s="8">
-        <f t="shared" si="5"/>
-        <v>493036</v>
+        <v>6890</v>
       </c>
       <c r="M25" s="8">
-        <f t="shared" si="5"/>
-        <v>525370</v>
+        <v>39</v>
       </c>
       <c r="N25" s="8">
-        <f t="shared" si="5"/>
-        <v>592363</v>
+        <v>-486</v>
       </c>
       <c r="O25" s="8">
-        <f t="shared" si="5"/>
-        <v>687800</v>
-      </c>
-      <c r="P25" s="8"/>
+        <v>1003</v>
+      </c>
+      <c r="P25" s="8">
+        <v>67430</v>
+      </c>
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
       <c r="S25" s="8"/>
@@ -2721,42 +2803,64 @@
     </row>
     <row r="26" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
+        <v>29</v>
+      </c>
+      <c r="C26" s="8">
+        <f t="shared" ref="C26:G26" si="4">+C22+SUM(C23:C25)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="E26" s="8">
-        <v>31145</v>
-      </c>
-      <c r="F26" s="8"/>
+        <f t="shared" si="4"/>
+        <v>241940</v>
+      </c>
+      <c r="F26" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="G26" s="8">
-        <v>41322</v>
+        <f t="shared" si="4"/>
+        <v>266543</v>
       </c>
       <c r="H26" s="8">
-        <v>58649</v>
+        <f>+H22+SUM(H23:H25)</f>
+        <v>306311</v>
       </c>
       <c r="I26" s="8">
-        <v>59107</v>
+        <f t="shared" ref="I26:P26" si="5">+I22+SUM(I23:I25)</f>
+        <v>384187</v>
       </c>
       <c r="J26" s="8">
-        <v>74329</v>
+        <f t="shared" si="5"/>
+        <v>447798</v>
       </c>
       <c r="K26" s="8">
-        <v>70162</v>
+        <f t="shared" si="5"/>
+        <v>430895</v>
       </c>
       <c r="L26" s="8">
-        <v>95543</v>
+        <f t="shared" si="5"/>
+        <v>493036</v>
       </c>
       <c r="M26" s="8">
-        <v>73614</v>
+        <f t="shared" si="5"/>
+        <v>525370</v>
       </c>
       <c r="N26" s="8">
-        <v>86947</v>
+        <f t="shared" si="5"/>
+        <v>592363</v>
       </c>
       <c r="O26" s="8">
-        <v>114999</v>
-      </c>
-      <c r="P26" s="8"/>
+        <f t="shared" si="5"/>
+        <v>687800</v>
+      </c>
+      <c r="P26" s="8">
+        <f t="shared" si="5"/>
+        <v>862430</v>
+      </c>
       <c r="Q26" s="8"/>
       <c r="R26" s="8"/>
       <c r="S26" s="8"/>
@@ -2797,61 +2901,44 @@
     </row>
     <row r="27" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="8">
-        <f t="shared" ref="C27:H27" si="6">+C25-C26</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="8">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="8">
-        <f t="shared" si="6"/>
-        <v>210795</v>
-      </c>
-      <c r="F27" s="8">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+        <v>31145</v>
+      </c>
+      <c r="F27" s="8"/>
       <c r="G27" s="8">
-        <f t="shared" si="6"/>
-        <v>225221</v>
+        <v>41322</v>
       </c>
       <c r="H27" s="8">
-        <f t="shared" si="6"/>
-        <v>247662</v>
+        <v>58649</v>
       </c>
       <c r="I27" s="8">
-        <f>+I25-I26</f>
-        <v>325080</v>
+        <v>59107</v>
       </c>
       <c r="J27" s="8">
-        <f t="shared" ref="J27:O27" si="7">+J25-J26</f>
-        <v>373469</v>
+        <v>74329</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="7"/>
-        <v>360733</v>
+        <v>70162</v>
       </c>
       <c r="L27" s="8">
-        <f t="shared" si="7"/>
-        <v>397493</v>
+        <v>95543</v>
       </c>
       <c r="M27" s="8">
-        <f t="shared" si="7"/>
-        <v>451756</v>
+        <v>73614</v>
       </c>
       <c r="N27" s="8">
-        <f t="shared" si="7"/>
-        <v>505416</v>
+        <v>86947</v>
       </c>
       <c r="O27" s="8">
-        <f t="shared" si="7"/>
-        <v>572801</v>
-      </c>
-      <c r="P27" s="8"/>
+        <v>114999</v>
+      </c>
+      <c r="P27" s="8">
+        <v>155649</v>
+      </c>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
       <c r="S27" s="8"/>
@@ -2892,42 +2979,64 @@
     </row>
     <row r="28" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
+        <v>31</v>
+      </c>
+      <c r="C28" s="8">
+        <f t="shared" ref="C28:H28" si="6">+C26-C27</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="E28" s="8">
-        <v>-205</v>
-      </c>
-      <c r="F28" s="8"/>
+        <f t="shared" si="6"/>
+        <v>210795</v>
+      </c>
+      <c r="F28" s="8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="G28" s="8">
-        <v>-264</v>
+        <f t="shared" si="6"/>
+        <v>225221</v>
       </c>
       <c r="H28" s="8">
-        <v>-183</v>
+        <f t="shared" si="6"/>
+        <v>247662</v>
       </c>
       <c r="I28" s="8">
-        <v>-178</v>
+        <f>+I26-I27</f>
+        <v>325080</v>
       </c>
       <c r="J28" s="8">
-        <v>-211</v>
+        <f t="shared" ref="J28:P28" si="7">+J26-J27</f>
+        <v>373469</v>
       </c>
       <c r="K28" s="8">
-        <v>-831</v>
+        <f t="shared" si="7"/>
+        <v>360733</v>
       </c>
       <c r="L28" s="8">
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>397493</v>
       </c>
       <c r="M28" s="8">
-        <v>-547</v>
+        <f t="shared" si="7"/>
+        <v>451756</v>
       </c>
       <c r="N28" s="8">
-        <v>-328</v>
+        <f t="shared" si="7"/>
+        <v>505416</v>
       </c>
       <c r="O28" s="8">
-        <v>321</v>
-      </c>
-      <c r="P28" s="8"/>
+        <f t="shared" si="7"/>
+        <v>572801</v>
+      </c>
+      <c r="P28" s="8">
+        <f t="shared" si="7"/>
+        <v>706781</v>
+      </c>
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
       <c r="S28" s="8"/>
@@ -2968,61 +3077,44 @@
     </row>
     <row r="29" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="8">
-        <f t="shared" ref="C29:G29" si="8">+C27-C28</f>
+        <v>26</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8">
+        <v>-205</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8">
+        <v>-264</v>
+      </c>
+      <c r="H29" s="8">
+        <v>-183</v>
+      </c>
+      <c r="I29" s="8">
+        <v>-178</v>
+      </c>
+      <c r="J29" s="8">
+        <v>-211</v>
+      </c>
+      <c r="K29" s="8">
+        <v>-831</v>
+      </c>
+      <c r="L29" s="8">
         <v>0</v>
       </c>
-      <c r="D29" s="8">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E29" s="8">
-        <f t="shared" si="8"/>
-        <v>211000</v>
-      </c>
-      <c r="F29" s="8">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="8">
-        <f t="shared" si="8"/>
-        <v>225485</v>
-      </c>
-      <c r="H29" s="8">
-        <f>+H27-H28</f>
-        <v>247845</v>
-      </c>
-      <c r="I29" s="8">
-        <f t="shared" ref="I29:O29" si="9">+I27-I28</f>
-        <v>325258</v>
-      </c>
-      <c r="J29" s="8">
-        <f t="shared" si="9"/>
-        <v>373680</v>
-      </c>
-      <c r="K29" s="8">
-        <f t="shared" si="9"/>
-        <v>361564</v>
-      </c>
-      <c r="L29" s="8">
-        <f t="shared" si="9"/>
-        <v>397493</v>
-      </c>
       <c r="M29" s="8">
-        <f t="shared" si="9"/>
-        <v>452303</v>
+        <v>-547</v>
       </c>
       <c r="N29" s="8">
-        <f t="shared" si="9"/>
-        <v>505744</v>
+        <v>-328</v>
       </c>
       <c r="O29" s="8">
-        <f t="shared" si="9"/>
-        <v>572480</v>
-      </c>
-      <c r="P29" s="8"/>
+        <v>321</v>
+      </c>
+      <c r="P29" s="8">
+        <v>219</v>
+      </c>
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
       <c r="S29" s="8"/>
@@ -3062,20 +3154,65 @@
       <c r="BA29" s="4"/>
     </row>
     <row r="30" spans="2:53" x14ac:dyDescent="0.2">
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8"/>
+      <c r="B30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="8">
+        <f t="shared" ref="C30:G30" si="8">+C28-C29</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="8">
+        <f t="shared" si="8"/>
+        <v>211000</v>
+      </c>
+      <c r="F30" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="8">
+        <f t="shared" si="8"/>
+        <v>225485</v>
+      </c>
+      <c r="H30" s="8">
+        <f>+H28-H29</f>
+        <v>247845</v>
+      </c>
+      <c r="I30" s="8">
+        <f t="shared" ref="I30:P30" si="9">+I28-I29</f>
+        <v>325258</v>
+      </c>
+      <c r="J30" s="8">
+        <f t="shared" si="9"/>
+        <v>373680</v>
+      </c>
+      <c r="K30" s="8">
+        <f t="shared" si="9"/>
+        <v>361564</v>
+      </c>
+      <c r="L30" s="8">
+        <f t="shared" si="9"/>
+        <v>397493</v>
+      </c>
+      <c r="M30" s="8">
+        <f t="shared" si="9"/>
+        <v>452303</v>
+      </c>
+      <c r="N30" s="8">
+        <f t="shared" si="9"/>
+        <v>505744</v>
+      </c>
+      <c r="O30" s="8">
+        <f t="shared" si="9"/>
+        <v>572480</v>
+      </c>
+      <c r="P30" s="8">
+        <f t="shared" si="9"/>
+        <v>706562</v>
+      </c>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
       <c r="S30" s="8"/>
@@ -3115,87 +3252,45 @@
       <c r="BA30" s="4"/>
     </row>
     <row r="31" spans="2:53" x14ac:dyDescent="0.2">
-      <c r="B31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="11" t="e">
-        <f t="shared" ref="C31:D31" si="10">+C29/C32</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D31" s="11" t="e">
-        <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E31" s="11">
-        <f>+E29/E32</f>
-        <v>8.1376065409387177</v>
-      </c>
-      <c r="F31" s="11" t="e">
-        <f t="shared" ref="F31:O31" si="11">+F29/F32</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G31" s="11">
-        <f t="shared" si="11"/>
-        <v>8.6959120709602775</v>
-      </c>
-      <c r="H31" s="11">
-        <f t="shared" si="11"/>
-        <v>9.557865103544021</v>
-      </c>
-      <c r="I31" s="11">
-        <f t="shared" si="11"/>
-        <v>12.54466214131441</v>
-      </c>
-      <c r="J31" s="11">
-        <f t="shared" si="11"/>
-        <v>14.411662617146824</v>
-      </c>
-      <c r="K31" s="11">
-        <f t="shared" si="11"/>
-        <v>13.944386594160978</v>
-      </c>
-      <c r="L31" s="11">
-        <f t="shared" si="11"/>
-        <v>15.330055150603572</v>
-      </c>
-      <c r="M31" s="11">
-        <f t="shared" si="11"/>
-        <v>17.443231777863478</v>
-      </c>
-      <c r="N31" s="11">
-        <f t="shared" si="11"/>
-        <v>19.503451467355674</v>
-      </c>
-      <c r="O31" s="11">
-        <f t="shared" si="11"/>
-        <v>22.077050634375844</v>
-      </c>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="11"/>
-      <c r="R31" s="11"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
-      <c r="Z31" s="4"/>
-      <c r="AA31" s="4"/>
-      <c r="AB31" s="4"/>
-      <c r="AC31" s="4"/>
-      <c r="AD31" s="4"/>
-      <c r="AE31" s="4"/>
-      <c r="AF31" s="4"/>
-      <c r="AG31" s="4"/>
-      <c r="AH31" s="4"/>
-      <c r="AI31" s="4"/>
-      <c r="AJ31" s="4"/>
-      <c r="AK31" s="4"/>
-      <c r="AL31" s="4"/>
-      <c r="AM31" s="4"/>
-      <c r="AN31" s="4"/>
-      <c r="AO31" s="4"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="8"/>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="8"/>
+      <c r="S31" s="8"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="8"/>
+      <c r="V31" s="8"/>
+      <c r="W31" s="8"/>
+      <c r="X31" s="8"/>
+      <c r="Y31" s="8"/>
+      <c r="Z31" s="8"/>
+      <c r="AA31" s="8"/>
+      <c r="AB31" s="8"/>
+      <c r="AC31" s="8"/>
+      <c r="AD31" s="8"/>
+      <c r="AE31" s="8"/>
+      <c r="AF31" s="8"/>
+      <c r="AG31" s="8"/>
+      <c r="AH31" s="8"/>
+      <c r="AI31" s="8"/>
+      <c r="AJ31" s="8"/>
+      <c r="AK31" s="8"/>
+      <c r="AL31" s="8"/>
+      <c r="AM31" s="8"/>
+      <c r="AN31" s="8"/>
+      <c r="AO31" s="8"/>
       <c r="AP31" s="4"/>
       <c r="AQ31" s="4"/>
       <c r="AR31" s="4"/>
@@ -3211,44 +3306,66 @@
     </row>
     <row r="32" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4">
-        <v>25929</v>
-      </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4">
-        <v>25930</v>
-      </c>
-      <c r="H32" s="4">
-        <v>25931</v>
-      </c>
-      <c r="I32" s="4">
-        <v>25928</v>
-      </c>
-      <c r="J32" s="4">
-        <v>25929</v>
-      </c>
-      <c r="K32" s="4">
-        <v>25929</v>
-      </c>
-      <c r="L32" s="4">
-        <v>25929</v>
-      </c>
-      <c r="M32" s="4">
-        <v>25930</v>
-      </c>
-      <c r="N32" s="4">
-        <v>25931</v>
-      </c>
-      <c r="O32" s="4">
-        <v>25931</v>
-      </c>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="C32" s="11" t="e">
+        <f t="shared" ref="C32:D32" si="10">+C30/C33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D32" s="11" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E32" s="11">
+        <f>+E30/E33</f>
+        <v>8.1376065409387177</v>
+      </c>
+      <c r="F32" s="11" t="e">
+        <f t="shared" ref="F32:P32" si="11">+F30/F33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G32" s="11">
+        <f t="shared" si="11"/>
+        <v>8.6959120709602775</v>
+      </c>
+      <c r="H32" s="11">
+        <f t="shared" si="11"/>
+        <v>9.557865103544021</v>
+      </c>
+      <c r="I32" s="11">
+        <f t="shared" si="11"/>
+        <v>12.54466214131441</v>
+      </c>
+      <c r="J32" s="11">
+        <f t="shared" si="11"/>
+        <v>14.411662617146824</v>
+      </c>
+      <c r="K32" s="11">
+        <f t="shared" si="11"/>
+        <v>13.944386594160978</v>
+      </c>
+      <c r="L32" s="11">
+        <f t="shared" si="11"/>
+        <v>15.330055150603572</v>
+      </c>
+      <c r="M32" s="11">
+        <f t="shared" si="11"/>
+        <v>17.443231777863478</v>
+      </c>
+      <c r="N32" s="11">
+        <f t="shared" si="11"/>
+        <v>19.503451467355674</v>
+      </c>
+      <c r="O32" s="11">
+        <f t="shared" si="11"/>
+        <v>22.077050634375844</v>
+      </c>
+      <c r="P32" s="11">
+        <f t="shared" si="11"/>
+        <v>27.246722196513961</v>
+      </c>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
       <c r="S32" s="4"/>
       <c r="T32" s="4"/>
       <c r="U32" s="4"/>
@@ -3286,20 +3403,45 @@
       <c r="BA32" s="4"/>
     </row>
     <row r="33" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="B33" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
+      <c r="E33" s="4">
+        <v>25929</v>
+      </c>
       <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
+      <c r="G33" s="4">
+        <v>25930</v>
+      </c>
+      <c r="H33" s="4">
+        <v>25931</v>
+      </c>
+      <c r="I33" s="4">
+        <v>25928</v>
+      </c>
+      <c r="J33" s="4">
+        <v>25929</v>
+      </c>
+      <c r="K33" s="4">
+        <v>25929</v>
+      </c>
+      <c r="L33" s="4">
+        <v>25929</v>
+      </c>
+      <c r="M33" s="4">
+        <v>25930</v>
+      </c>
+      <c r="N33" s="4">
+        <v>25931</v>
+      </c>
+      <c r="O33" s="4">
+        <v>25931</v>
+      </c>
+      <c r="P33" s="4">
+        <v>25932</v>
+      </c>
       <c r="Q33" s="4"/>
       <c r="R33" s="4"/>
       <c r="S33" s="4"/>
@@ -3339,52 +3481,22 @@
       <c r="BA33" s="4"/>
     </row>
     <row r="34" spans="2:53" x14ac:dyDescent="0.2">
-      <c r="B34" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="12" t="e">
-        <f t="shared" ref="G34:J34" si="12">+G15/C15-1</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H34" s="12" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I34" s="12">
-        <f t="shared" si="12"/>
-        <v>0.38951188239963574</v>
-      </c>
-      <c r="J34" s="12" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K34" s="12">
-        <f>+K15/G15-1</f>
-        <v>0.41611827673949286</v>
-      </c>
-      <c r="L34" s="12">
-        <f>+L15/H15-1</f>
-        <v>0.386456028863714</v>
-      </c>
-      <c r="M34" s="12">
-        <f>+M15/I15-1</f>
-        <v>0.30305176308293369</v>
-      </c>
-      <c r="N34" s="12">
-        <f>+N15/J15-1</f>
-        <v>0.20453307632697371</v>
-      </c>
-      <c r="O34" s="12">
-        <f>+O15/K15-1</f>
-        <v>0.35132272232244355</v>
-      </c>
-      <c r="P34" s="12"/>
-      <c r="Q34" s="12"/>
-      <c r="R34" s="12"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
@@ -3423,63 +3535,54 @@
     </row>
     <row r="35" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="13" t="e">
-        <f t="shared" ref="C35:H35" si="13">+C17/C15</f>
+        <v>33</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="12" t="e">
+        <f t="shared" ref="G35:J35" si="12">+G16/C16-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D35" s="13" t="e">
-        <f t="shared" si="13"/>
+      <c r="H35" s="12" t="e">
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E35" s="13">
-        <f t="shared" si="13"/>
-        <v>0.5425737974477487</v>
-      </c>
-      <c r="F35" s="13" t="e">
-        <f t="shared" si="13"/>
+      <c r="I35" s="12">
+        <f t="shared" si="12"/>
+        <v>0.38951188239963574</v>
+      </c>
+      <c r="J35" s="12" t="e">
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G35" s="13">
-        <f t="shared" si="13"/>
-        <v>0.53068115091015855</v>
-      </c>
-      <c r="H35" s="13">
-        <f t="shared" si="13"/>
-        <v>0.53172929874834818</v>
-      </c>
-      <c r="I35" s="13">
-        <f>+I17/I15</f>
-        <v>0.57831989806395223</v>
-      </c>
-      <c r="J35" s="13">
-        <f t="shared" ref="J35:K35" si="14">+J17/J15</f>
-        <v>0.58998504250622652</v>
-      </c>
-      <c r="K35" s="13">
-        <f t="shared" si="14"/>
-        <v>0.58789710862265776</v>
-      </c>
-      <c r="L35" s="13">
-        <f t="shared" ref="L35:M35" si="15">+L17/L15</f>
-        <v>0.58617872074294919</v>
-      </c>
-      <c r="M35" s="13">
-        <f t="shared" si="15"/>
-        <v>0.59453712327687747</v>
-      </c>
-      <c r="N35" s="13">
-        <f t="shared" ref="N35:O35" si="16">+N17/N15</f>
-        <v>0.62326090489346042</v>
-      </c>
-      <c r="O35" s="13">
-        <f t="shared" si="16"/>
-        <v>0.66245746638532832</v>
-      </c>
-      <c r="P35" s="13"/>
-      <c r="Q35" s="13"/>
-      <c r="R35" s="13"/>
+      <c r="K35" s="12">
+        <f>+K16/G16-1</f>
+        <v>0.41611827673949286</v>
+      </c>
+      <c r="L35" s="12">
+        <f>+L16/H16-1</f>
+        <v>0.386456028863714</v>
+      </c>
+      <c r="M35" s="12">
+        <f>+M16/I16-1</f>
+        <v>0.30305176308293369</v>
+      </c>
+      <c r="N35" s="12">
+        <f>+N16/J16-1</f>
+        <v>0.20453307632697371</v>
+      </c>
+      <c r="O35" s="12">
+        <f>+O16/K16-1</f>
+        <v>0.35132272232244355</v>
+      </c>
+      <c r="P35" s="12">
+        <f>+P16/L16-1</f>
+        <v>0.36045393406668724</v>
+      </c>
+      <c r="Q35" s="12"/>
+      <c r="R35" s="12"/>
       <c r="S35" s="4"/>
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
@@ -3518,61 +3621,64 @@
     </row>
     <row r="36" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36" s="13" t="e">
-        <f t="shared" ref="C36:H36" si="17">+C21/C15</f>
+        <f t="shared" ref="C36:H36" si="13">+C18/C16</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D36" s="13" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E36" s="13">
-        <f t="shared" si="17"/>
-        <v>0.41714145661593499</v>
+        <f t="shared" si="13"/>
+        <v>0.5425737974477487</v>
       </c>
       <c r="F36" s="13" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G36" s="13">
-        <f t="shared" si="17"/>
-        <v>0.42018142426144534</v>
+        <f t="shared" si="13"/>
+        <v>0.53068115091015855</v>
       </c>
       <c r="H36" s="13">
-        <f t="shared" si="17"/>
-        <v>0.42546658549984412</v>
+        <f t="shared" si="13"/>
+        <v>0.53172929874834818</v>
       </c>
       <c r="I36" s="13">
-        <f>+I21/I15</f>
-        <v>0.47488455847896255</v>
+        <f>+I18/I16</f>
+        <v>0.57831989806395223</v>
       </c>
       <c r="J36" s="13">
-        <f t="shared" ref="J36:K36" si="18">+J21/J15</f>
-        <v>0.49019242084561082</v>
+        <f t="shared" ref="J36:K36" si="14">+J18/J16</f>
+        <v>0.58998504250622652</v>
       </c>
       <c r="K36" s="13">
-        <f t="shared" si="18"/>
-        <v>0.48505100958708569</v>
+        <f t="shared" si="14"/>
+        <v>0.58789710862265776</v>
       </c>
       <c r="L36" s="13">
-        <f t="shared" ref="L36:M36" si="19">+L21/L15</f>
-        <v>0.49628075631403995</v>
+        <f t="shared" ref="L36:M36" si="15">+L18/L16</f>
+        <v>0.58617872074294919</v>
       </c>
       <c r="M36" s="13">
-        <f t="shared" si="19"/>
-        <v>0.50578431748892327</v>
+        <f t="shared" si="15"/>
+        <v>0.59453712327687747</v>
       </c>
       <c r="N36" s="13">
-        <f t="shared" ref="N36:O36" si="20">+N21/N15</f>
-        <v>0.54001376554598557</v>
+        <f t="shared" ref="N36:O36" si="16">+N18/N16</f>
+        <v>0.62326090489346042</v>
       </c>
       <c r="O36" s="13">
-        <f t="shared" si="20"/>
-        <v>0.58104598964997012</v>
-      </c>
-      <c r="P36" s="13"/>
+        <f t="shared" si="16"/>
+        <v>0.66245746638532832</v>
+      </c>
+      <c r="P36" s="13">
+        <f t="shared" ref="P36" si="17">+P18/P16</f>
+        <v>0.67720707409824299</v>
+      </c>
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
       <c r="S36" s="4"/>
@@ -3613,61 +3719,64 @@
     </row>
     <row r="37" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" s="13" t="e">
-        <f t="shared" ref="C37:H37" si="21">+C26/C25</f>
+        <f t="shared" ref="C37:H37" si="18">+C22/C16</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D37" s="13" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E37" s="13">
+        <f t="shared" si="18"/>
+        <v>0.41714145661593499</v>
+      </c>
+      <c r="F37" s="13" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G37" s="13">
+        <f t="shared" si="18"/>
+        <v>0.42018142426144534</v>
+      </c>
+      <c r="H37" s="13">
+        <f t="shared" si="18"/>
+        <v>0.42546658549984412</v>
+      </c>
+      <c r="I37" s="13">
+        <f>+I22/I16</f>
+        <v>0.47488455847896255</v>
+      </c>
+      <c r="J37" s="13">
+        <f t="shared" ref="J37:K37" si="19">+J22/J16</f>
+        <v>0.49019242084561082</v>
+      </c>
+      <c r="K37" s="13">
+        <f t="shared" si="19"/>
+        <v>0.48505100958708569</v>
+      </c>
+      <c r="L37" s="13">
+        <f t="shared" ref="L37:M37" si="20">+L22/L16</f>
+        <v>0.49628075631403995</v>
+      </c>
+      <c r="M37" s="13">
+        <f t="shared" si="20"/>
+        <v>0.50578431748892327</v>
+      </c>
+      <c r="N37" s="13">
+        <f t="shared" ref="N37:O37" si="21">+N22/N16</f>
+        <v>0.54001376554598557</v>
+      </c>
+      <c r="O37" s="13">
         <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E37" s="13">
-        <f t="shared" si="21"/>
-        <v>0.12873026370174423</v>
-      </c>
-      <c r="F37" s="13" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G37" s="13">
-        <f t="shared" si="21"/>
-        <v>0.15502939488187648</v>
-      </c>
-      <c r="H37" s="13">
-        <f t="shared" si="21"/>
-        <v>0.19146880131630925</v>
-      </c>
-      <c r="I37" s="13">
-        <f>+I26/I25</f>
-        <v>0.15384955763729641</v>
-      </c>
-      <c r="J37" s="13">
-        <f t="shared" ref="J37:K37" si="22">+J26/J25</f>
-        <v>0.16598778913706627</v>
-      </c>
-      <c r="K37" s="13">
-        <f t="shared" si="22"/>
-        <v>0.16282853131273281</v>
-      </c>
-      <c r="L37" s="13">
-        <f t="shared" ref="L37:M37" si="23">+L26/L25</f>
-        <v>0.19378503800939484</v>
-      </c>
-      <c r="M37" s="13">
-        <f t="shared" si="23"/>
-        <v>0.14011839275177493</v>
-      </c>
-      <c r="N37" s="13">
-        <f t="shared" ref="N37:O37" si="24">+N26/N25</f>
-        <v>0.14677993054934221</v>
-      </c>
-      <c r="O37" s="13">
-        <f t="shared" si="24"/>
-        <v>0.16719831346321606</v>
-      </c>
-      <c r="P37" s="13"/>
+        <v>0.58104598964997012</v>
+      </c>
+      <c r="P37" s="13">
+        <f t="shared" ref="P37" si="22">+P22/P16</f>
+        <v>0.60344337643588808</v>
+      </c>
       <c r="Q37" s="13"/>
       <c r="R37" s="13"/>
       <c r="S37" s="4"/>
@@ -3707,22 +3816,67 @@
       <c r="BA37" s="4"/>
     </row>
     <row r="38" spans="2:53" x14ac:dyDescent="0.2">
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
+      <c r="B38" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="13" t="e">
+        <f t="shared" ref="C38:H38" si="23">+C27/C26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D38" s="13" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E38" s="13">
+        <f t="shared" si="23"/>
+        <v>0.12873026370174423</v>
+      </c>
+      <c r="F38" s="13" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G38" s="13">
+        <f t="shared" si="23"/>
+        <v>0.15502939488187648</v>
+      </c>
+      <c r="H38" s="13">
+        <f t="shared" si="23"/>
+        <v>0.19146880131630925</v>
+      </c>
+      <c r="I38" s="13">
+        <f>+I27/I26</f>
+        <v>0.15384955763729641</v>
+      </c>
+      <c r="J38" s="13">
+        <f t="shared" ref="J38:K38" si="24">+J27/J26</f>
+        <v>0.16598778913706627</v>
+      </c>
+      <c r="K38" s="13">
+        <f t="shared" si="24"/>
+        <v>0.16282853131273281</v>
+      </c>
+      <c r="L38" s="13">
+        <f t="shared" ref="L38:M38" si="25">+L27/L26</f>
+        <v>0.19378503800939484</v>
+      </c>
+      <c r="M38" s="13">
+        <f t="shared" si="25"/>
+        <v>0.14011839275177493</v>
+      </c>
+      <c r="N38" s="13">
+        <f t="shared" ref="N38:O38" si="26">+N27/N26</f>
+        <v>0.14677993054934221</v>
+      </c>
+      <c r="O38" s="13">
+        <f t="shared" si="26"/>
+        <v>0.16719831346321606</v>
+      </c>
+      <c r="P38" s="13">
+        <f t="shared" ref="P38" si="27">+P27/P26</f>
+        <v>0.18047725612513479</v>
+      </c>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="13"/>
       <c r="S38" s="4"/>
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
@@ -12345,10 +12499,64 @@
       <c r="AZ200" s="4"/>
       <c r="BA200" s="4"/>
     </row>
+    <row r="201" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="C201" s="4"/>
+      <c r="D201" s="4"/>
+      <c r="E201" s="4"/>
+      <c r="F201" s="4"/>
+      <c r="G201" s="4"/>
+      <c r="H201" s="4"/>
+      <c r="I201" s="4"/>
+      <c r="J201" s="4"/>
+      <c r="K201" s="4"/>
+      <c r="L201" s="4"/>
+      <c r="M201" s="4"/>
+      <c r="N201" s="4"/>
+      <c r="O201" s="4"/>
+      <c r="P201" s="4"/>
+      <c r="Q201" s="4"/>
+      <c r="R201" s="4"/>
+      <c r="S201" s="4"/>
+      <c r="T201" s="4"/>
+      <c r="U201" s="4"/>
+      <c r="V201" s="4"/>
+      <c r="W201" s="4"/>
+      <c r="X201" s="4"/>
+      <c r="Y201" s="4"/>
+      <c r="Z201" s="4"/>
+      <c r="AA201" s="4"/>
+      <c r="AB201" s="4"/>
+      <c r="AC201" s="4"/>
+      <c r="AD201" s="4"/>
+      <c r="AE201" s="4"/>
+      <c r="AF201" s="4"/>
+      <c r="AG201" s="4"/>
+      <c r="AH201" s="4"/>
+      <c r="AI201" s="4"/>
+      <c r="AJ201" s="4"/>
+      <c r="AK201" s="4"/>
+      <c r="AL201" s="4"/>
+      <c r="AM201" s="4"/>
+      <c r="AN201" s="4"/>
+      <c r="AO201" s="4"/>
+      <c r="AP201" s="4"/>
+      <c r="AQ201" s="4"/>
+      <c r="AR201" s="4"/>
+      <c r="AS201" s="4"/>
+      <c r="AT201" s="4"/>
+      <c r="AU201" s="4"/>
+      <c r="AV201" s="4"/>
+      <c r="AW201" s="4"/>
+      <c r="AX201" s="4"/>
+      <c r="AY201" s="4"/>
+      <c r="AZ201" s="4"/>
+      <c r="BA201" s="4"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{0C8241C6-0EFE-43C8-8BF5-BDBE8F4D8D90}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>